--- a/stock_trading_journal.xlsx
+++ b/stock_trading_journal.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ChienVH\Code\Document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F61EEE07-9B57-49DB-BC8F-92081B841B99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CFD3348-F228-47EE-87A8-81807280512B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,6 @@
     <sheet name="Note" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -38,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1482" uniqueCount="1138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1492" uniqueCount="1148">
   <si>
     <t>Ngày giao dịch</t>
   </si>
@@ -3232,9 +3231,6 @@
     <t>30/1/2026</t>
   </si>
   <si>
-    <t>HDC</t>
-  </si>
-  <si>
     <t>HHS</t>
   </si>
   <si>
@@ -3400,9 +3396,6 @@
     <t>239.747</t>
   </si>
   <si>
-    <t>đã đặt mua 800 giá 35.8</t>
-  </si>
-  <si>
     <t>5/3/2026</t>
   </si>
   <si>
@@ -3433,25 +3426,61 @@
     <t>tiếp tục giảm quá yếu so với thị trường</t>
   </si>
   <si>
-    <t>sắp xuống đáy thuế quan</t>
-  </si>
-  <si>
     <t>11/3/2026</t>
   </si>
   <si>
     <t>214.823</t>
   </si>
   <si>
-    <t>nến đóng trần</t>
-  </si>
-  <si>
-    <t>tham chiếu, yếu hơn thị trường</t>
-  </si>
-  <si>
-    <t>hồi phục vol nhỏ</t>
-  </si>
-  <si>
-    <t>hồi phục nhưng yếu hơn so với thị trường</t>
+    <t>12/3/2026</t>
+  </si>
+  <si>
+    <t>208.402</t>
+  </si>
+  <si>
+    <t>13/3/2026</t>
+  </si>
+  <si>
+    <t>NLG</t>
+  </si>
+  <si>
+    <t>VIB</t>
+  </si>
+  <si>
+    <t>203.397</t>
+  </si>
+  <si>
+    <t>-23.067</t>
+  </si>
+  <si>
+    <t>16/3/2026</t>
+  </si>
+  <si>
+    <t>202.549</t>
+  </si>
+  <si>
+    <t>17/3/2026</t>
+  </si>
+  <si>
+    <t>209.871</t>
+  </si>
+  <si>
+    <t>vẫn giữ được ma200</t>
+  </si>
+  <si>
+    <t>nến tăng tốt nhưng vol nhỏ theo dõi thêm</t>
+  </si>
+  <si>
+    <t>yếu rất yếu so với ngành</t>
+  </si>
+  <si>
+    <t>ngừng rơi, có dấu hiệu tạo đáy</t>
+  </si>
+  <si>
+    <t>18/3/2026</t>
+  </si>
+  <si>
+    <t>207.208</t>
   </si>
 </sst>
 </file>
@@ -4071,7 +4100,7 @@
     <row r="4" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="22"/>
       <c r="B4" s="28" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="C4" s="22"/>
       <c r="D4" s="22"/>
@@ -4203,7 +4232,7 @@
     <row r="17" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="22"/>
       <c r="B17" s="28" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="C17" s="41"/>
       <c r="D17" s="41"/>
@@ -4233,7 +4262,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F80FBEA-61B1-4D5E-A59E-30CA607BFEAD}">
-  <dimension ref="A1:E202"/>
+  <dimension ref="A1:E207"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16.44140625" style="27" bestFit="1" customWidth="1"/>
@@ -6005,7 +6034,7 @@
         <v>920</v>
       </c>
       <c r="C138" s="27">
-        <f t="shared" ref="C138:C202" si="18">B138-B137</f>
+        <f t="shared" ref="C138:C207" si="18">B138-B137</f>
         <v>-4.5640000000000214</v>
       </c>
       <c r="D138" s="27" t="s">
@@ -6554,22 +6583,22 @@
         <v>1063</v>
       </c>
       <c r="B180" s="27" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="C180" s="27">
         <f t="shared" si="18"/>
         <v>5.1079999999999757</v>
       </c>
       <c r="D180" s="27" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="181" spans="1:5" s="35" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A181" s="29" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B181" s="29" t="s">
         <v>1069</v>
-      </c>
-      <c r="B181" s="29" t="s">
-        <v>1070</v>
       </c>
       <c r="C181" s="29">
         <f t="shared" si="18"/>
@@ -6580,10 +6609,10 @@
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A182" s="27" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B182" s="27" t="s">
         <v>1071</v>
-      </c>
-      <c r="B182" s="27" t="s">
-        <v>1072</v>
       </c>
       <c r="C182" s="27">
         <f t="shared" si="18"/>
@@ -6592,10 +6621,10 @@
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A183" s="27" t="s">
+        <v>1072</v>
+      </c>
+      <c r="B183" s="27" t="s">
         <v>1073</v>
-      </c>
-      <c r="B183" s="27" t="s">
-        <v>1074</v>
       </c>
       <c r="C183" s="27">
         <f t="shared" si="18"/>
@@ -6604,25 +6633,25 @@
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A184" s="27" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B184" s="27" t="s">
         <v>1077</v>
-      </c>
-      <c r="B184" s="27" t="s">
-        <v>1078</v>
       </c>
       <c r="C184" s="27">
         <f t="shared" si="18"/>
         <v>-14.457000000000022</v>
       </c>
       <c r="D184" s="27" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="185" spans="1:5" s="35" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A185" s="29" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B185" s="29" t="s">
         <v>1082</v>
-      </c>
-      <c r="B185" s="29" t="s">
-        <v>1083</v>
       </c>
       <c r="C185" s="29">
         <f t="shared" si="18"/>
@@ -6633,10 +6662,10 @@
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A186" s="27" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B186" s="27" t="s">
         <v>1084</v>
-      </c>
-      <c r="B186" s="27" t="s">
-        <v>1085</v>
       </c>
       <c r="C186" s="27">
         <f t="shared" si="18"/>
@@ -6645,10 +6674,10 @@
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A187" s="27" t="s">
+        <v>1085</v>
+      </c>
+      <c r="B187" s="27" t="s">
         <v>1086</v>
-      </c>
-      <c r="B187" s="27" t="s">
-        <v>1087</v>
       </c>
       <c r="C187" s="27">
         <f t="shared" si="18"/>
@@ -6657,10 +6686,10 @@
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A188" s="27" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B188" s="27" t="s">
         <v>1088</v>
-      </c>
-      <c r="B188" s="27" t="s">
-        <v>1089</v>
       </c>
       <c r="C188" s="27">
         <f t="shared" si="18"/>
@@ -6669,25 +6698,25 @@
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A189" s="27" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="B189" s="27" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="C189" s="27">
         <f t="shared" si="18"/>
         <v>2.0679999999999836</v>
       </c>
       <c r="D189" s="27" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="190" spans="1:5" s="35" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A190" s="29" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B190" s="29" t="s">
         <v>1094</v>
-      </c>
-      <c r="B190" s="29" t="s">
-        <v>1095</v>
       </c>
       <c r="C190" s="29">
         <f t="shared" si="18"/>
@@ -6698,10 +6727,10 @@
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A191" s="27" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B191" s="27" t="s">
         <v>1096</v>
-      </c>
-      <c r="B191" s="27" t="s">
-        <v>1097</v>
       </c>
       <c r="C191" s="27">
         <f t="shared" si="18"/>
@@ -6710,24 +6739,24 @@
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A192" s="27" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="B192" s="27" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="C192" s="27" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="E192" s="27" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A193" s="27" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="B193" s="27" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="C193" s="27">
         <f t="shared" si="18"/>
@@ -6736,25 +6765,25 @@
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A194" s="27" t="s">
+        <v>1110</v>
+      </c>
+      <c r="B194" s="27" t="s">
         <v>1111</v>
-      </c>
-      <c r="B194" s="27" t="s">
-        <v>1112</v>
       </c>
       <c r="C194" s="27">
         <f t="shared" si="18"/>
         <v>-3.0240000000000009</v>
       </c>
       <c r="D194" s="27" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="195" spans="1:5" s="35" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A195" s="29" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B195" s="29" t="s">
         <v>1114</v>
-      </c>
-      <c r="B195" s="29" t="s">
-        <v>1115</v>
       </c>
       <c r="C195" s="29">
         <f t="shared" si="18"/>
@@ -6765,10 +6794,10 @@
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A196" s="27" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B196" s="27" t="s">
         <v>1116</v>
-      </c>
-      <c r="B196" s="27" t="s">
-        <v>1117</v>
       </c>
       <c r="C196" s="27">
         <f t="shared" si="18"/>
@@ -6777,10 +6806,10 @@
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A197" s="27" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B197" s="27" t="s">
         <v>1118</v>
-      </c>
-      <c r="B197" s="27" t="s">
-        <v>1119</v>
       </c>
       <c r="C197" s="27">
         <f t="shared" si="18"/>
@@ -6789,10 +6818,10 @@
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A198" s="27" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
       <c r="B198" s="27" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
       <c r="C198" s="27">
         <f t="shared" si="18"/>
@@ -6801,25 +6830,25 @@
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A199" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B199" s="27" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="C199" s="27">
         <f t="shared" si="18"/>
         <v>-12.381</v>
       </c>
       <c r="D199" s="27" t="s">
-        <v>1125</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="200" spans="1:5" s="35" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A200" s="29" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="B200" s="29" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
       <c r="C200" s="29">
         <f t="shared" si="18"/>
@@ -6830,10 +6859,10 @@
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A201" s="27" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="B201" s="27" t="s">
-        <v>1129</v>
+        <v>1127</v>
       </c>
       <c r="C201" s="27">
         <f t="shared" si="18"/>
@@ -6842,14 +6871,79 @@
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A202" s="27" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
       <c r="B202" s="27" t="s">
-        <v>1133</v>
+        <v>1130</v>
       </c>
       <c r="C202" s="27">
         <f t="shared" si="18"/>
         <v>9.7230000000000132</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A203" s="27" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B203" s="27" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C203" s="27">
+        <f t="shared" si="18"/>
+        <v>-6.4210000000000207</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A204" s="27" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B204" s="27" t="s">
+        <v>1136</v>
+      </c>
+      <c r="C204" s="27">
+        <f t="shared" si="18"/>
+        <v>-5.0049999999999955</v>
+      </c>
+      <c r="D204" s="27" t="s">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5" s="35" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A205" s="29" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B205" s="29" t="s">
+        <v>1139</v>
+      </c>
+      <c r="C205" s="29">
+        <f t="shared" si="18"/>
+        <v>-0.84799999999998477</v>
+      </c>
+      <c r="D205" s="29"/>
+      <c r="E205" s="29"/>
+    </row>
+    <row r="206" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A206" s="27" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B206" s="27" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C206" s="27">
+        <f t="shared" si="18"/>
+        <v>7.3220000000000027</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A207" s="27" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B207" s="27" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C207" s="27">
+        <f t="shared" si="18"/>
+        <v>-2.6630000000000109</v>
       </c>
     </row>
   </sheetData>
@@ -19075,7 +19169,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F70DC592-D4E4-4D13-ADCA-E681C1A017AC}">
-  <dimension ref="A1:O170"/>
+  <dimension ref="A1:O169"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="18" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.5546875" style="8" customWidth="1"/>
@@ -19151,11 +19245,11 @@
         <v>42.2</v>
       </c>
       <c r="F2" s="10">
-        <v>45.25</v>
+        <v>43.7</v>
       </c>
       <c r="G2" s="10">
         <f t="shared" ref="G2" si="0">ROUND((F2 - E2) / E2 * 100, 2)</f>
-        <v>7.23</v>
+        <v>3.55</v>
       </c>
       <c r="H2" s="7" t="s">
         <v>993</v>
@@ -19167,7 +19261,7 @@
         <v>784</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>1134</v>
+        <v>1142</v>
       </c>
       <c r="L2" s="10" t="s">
         <v>1043</v>
@@ -19188,11 +19282,11 @@
         <v>63.86</v>
       </c>
       <c r="F3" s="12">
-        <v>60.4</v>
+        <v>60.5</v>
       </c>
       <c r="G3" s="12">
         <f t="shared" ref="G3" si="1">ROUND((F3 - E3) / E3 * 100, 2)</f>
-        <v>-5.42</v>
+        <v>-5.26</v>
       </c>
       <c r="H3" s="13" t="s">
         <v>1003</v>
@@ -19200,10 +19294,10 @@
       <c r="I3" s="13"/>
       <c r="J3" s="37"/>
       <c r="K3" s="13" t="s">
-        <v>1135</v>
+        <v>1143</v>
       </c>
       <c r="L3" s="13" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="4" spans="1:12" s="12" customFormat="1" ht="36" x14ac:dyDescent="0.3">
@@ -19221,11 +19315,11 @@
         <v>27.21</v>
       </c>
       <c r="F4" s="12">
-        <v>22.65</v>
+        <v>21.45</v>
       </c>
       <c r="G4" s="12">
         <f t="shared" ref="G4" si="2">ROUND((F4 - E4) / E4 * 100, 2)</f>
-        <v>-16.760000000000002</v>
+        <v>-21.17</v>
       </c>
       <c r="H4" s="13" t="s">
         <v>1025</v>
@@ -19233,7 +19327,7 @@
       <c r="I4" s="13"/>
       <c r="J4" s="37"/>
       <c r="K4" s="13" t="s">
-        <v>1136</v>
+        <v>1144</v>
       </c>
       <c r="L4" s="13" t="s">
         <v>1050</v>
@@ -19254,11 +19348,11 @@
         <v>20.67</v>
       </c>
       <c r="F5" s="12">
-        <v>16.899999999999999</v>
+        <v>16.149999999999999</v>
       </c>
       <c r="G5" s="12">
         <f>ROUND((F5 - E5) / E5 * 100, 2)</f>
-        <v>-18.239999999999998</v>
+        <v>-21.87</v>
       </c>
       <c r="H5" s="13" t="s">
         <v>1016</v>
@@ -19266,7 +19360,7 @@
       <c r="I5" s="13"/>
       <c r="J5" s="37"/>
       <c r="K5" s="13" t="s">
-        <v>1137</v>
+        <v>1144</v>
       </c>
       <c r="L5" s="12" t="s">
         <v>1051</v>
@@ -19277,21 +19371,21 @@
         <v>736</v>
       </c>
       <c r="B6" s="32" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="D6" s="32"/>
       <c r="E6" s="12">
         <v>12.707000000000001</v>
       </c>
       <c r="F6" s="12">
-        <v>10.75</v>
+        <v>10.9</v>
       </c>
       <c r="G6" s="12">
         <f>ROUND((F6 - E6) / E6 * 100, 2)</f>
-        <v>-15.4</v>
+        <v>-14.22</v>
       </c>
       <c r="H6" s="13" t="s">
         <v>835</v>
@@ -19299,290 +19393,319 @@
       <c r="I6" s="13"/>
       <c r="J6" s="37"/>
       <c r="K6" s="13" t="s">
-        <v>1131</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
         <v>953</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>1120</v>
-      </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
-        <v>422</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>1061</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
-        <v>41</v>
+        <v>1064</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>1061</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
-        <v>629</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
-        <v>1064</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
-        <v>1065</v>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="12" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B24" s="32" t="s">
+        <v>822</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>1089</v>
+      </c>
+      <c r="D24" s="32"/>
+      <c r="E24" s="12">
+        <v>24.52</v>
+      </c>
+      <c r="F24" s="12">
+        <v>23</v>
+      </c>
+      <c r="G24" s="12">
+        <f t="shared" ref="G24:G29" si="3">ROUND((F24 - E24) / E24 * 100, 2)</f>
+        <v>-6.2</v>
+      </c>
+      <c r="H24" s="13" t="s">
+        <v>1090</v>
+      </c>
+      <c r="I24" s="13">
+        <v>32.5</v>
+      </c>
+      <c r="J24" s="37" t="s">
+        <v>784</v>
+      </c>
+      <c r="K24" s="13" t="s">
+        <v>1128</v>
       </c>
     </row>
     <row r="25" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A25" s="12" t="s">
-        <v>1032</v>
+        <v>1062</v>
       </c>
       <c r="B25" s="32" t="s">
-        <v>822</v>
-      </c>
-      <c r="C25" s="12" t="s">
-        <v>1090</v>
+        <v>1074</v>
+      </c>
+      <c r="C25" s="16">
+        <v>46175</v>
       </c>
       <c r="D25" s="32"/>
       <c r="E25" s="12">
-        <v>24.52</v>
+        <v>89.6</v>
       </c>
       <c r="F25" s="12">
-        <v>23</v>
+        <v>85.1</v>
       </c>
       <c r="G25" s="12">
-        <f>ROUND((F25 - E25) / E25 * 100, 2)</f>
-        <v>-6.2</v>
+        <f t="shared" si="3"/>
+        <v>-5.0199999999999996</v>
       </c>
       <c r="H25" s="13" t="s">
-        <v>1091</v>
-      </c>
-      <c r="I25" s="13">
-        <v>32.5</v>
-      </c>
+        <v>1075</v>
+      </c>
+      <c r="I25" s="13"/>
       <c r="J25" s="37" t="s">
         <v>784</v>
       </c>
       <c r="K25" s="13" t="s">
-        <v>1130</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="12" t="s">
-        <v>1062</v>
-      </c>
-      <c r="B26" s="32" t="s">
-        <v>1075</v>
-      </c>
-      <c r="C26" s="16">
-        <v>46175</v>
-      </c>
-      <c r="D26" s="32"/>
-      <c r="E26" s="12">
-        <v>89.6</v>
-      </c>
-      <c r="F26" s="12">
-        <v>85.1</v>
-      </c>
-      <c r="G26" s="12">
-        <f>ROUND((F26 - E26) / E26 * 100, 2)</f>
-        <v>-5.0199999999999996</v>
-      </c>
-      <c r="H26" s="13" t="s">
-        <v>1076</v>
-      </c>
-      <c r="I26" s="13"/>
-      <c r="J26" s="37" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" s="10" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="10" t="s">
+        <v>953</v>
+      </c>
+      <c r="B26" s="31" t="s">
+        <v>731</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>1054</v>
+      </c>
+      <c r="D26" s="31" t="s">
+        <v>1113</v>
+      </c>
+      <c r="E26" s="10">
+        <v>30.475000000000001</v>
+      </c>
+      <c r="F26" s="10">
+        <v>35</v>
+      </c>
+      <c r="G26" s="10">
+        <f t="shared" si="3"/>
+        <v>14.85</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>1055</v>
+      </c>
+      <c r="I26" s="7">
+        <v>35</v>
+      </c>
+      <c r="J26" s="38" t="s">
         <v>784</v>
       </c>
-      <c r="K26" s="13" t="s">
-        <v>757</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" s="10" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="10" t="s">
-        <v>953</v>
-      </c>
-      <c r="B27" s="31" t="s">
-        <v>731</v>
-      </c>
-      <c r="C27" s="15" t="s">
-        <v>1054</v>
-      </c>
-      <c r="D27" s="31" t="s">
-        <v>1114</v>
-      </c>
-      <c r="E27" s="10">
-        <v>30.475000000000001</v>
-      </c>
-      <c r="F27" s="10">
-        <v>35</v>
-      </c>
-      <c r="G27" s="10">
-        <f>ROUND((F27 - E27) / E27 * 100, 2)</f>
-        <v>14.85</v>
-      </c>
-      <c r="H27" s="7" t="s">
-        <v>1055</v>
-      </c>
-      <c r="I27" s="7">
-        <v>35</v>
-      </c>
-      <c r="J27" s="38" t="s">
+      <c r="K26" s="7" t="s">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" s="12" customFormat="1" ht="36" x14ac:dyDescent="0.3">
+      <c r="A27" s="12" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B27" s="32" t="s">
+        <v>824</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D27" s="32" t="s">
+        <v>1081</v>
+      </c>
+      <c r="E27" s="12">
+        <v>17.715</v>
+      </c>
+      <c r="F27" s="12">
+        <v>16.850000000000001</v>
+      </c>
+      <c r="G27" s="12">
+        <f t="shared" si="3"/>
+        <v>-4.88</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>1067</v>
+      </c>
+      <c r="I27" s="13"/>
+      <c r="J27" s="37" t="s">
         <v>784</v>
       </c>
-      <c r="K27" s="7" t="s">
-        <v>1098</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" s="12" customFormat="1" ht="36" x14ac:dyDescent="0.3">
-      <c r="A28" s="12" t="s">
-        <v>1058</v>
-      </c>
-      <c r="B28" s="32" t="s">
-        <v>824</v>
-      </c>
-      <c r="C28" s="16" t="s">
-        <v>1063</v>
-      </c>
-      <c r="D28" s="32" t="s">
-        <v>1082</v>
-      </c>
-      <c r="E28" s="12">
-        <v>17.715</v>
-      </c>
-      <c r="F28" s="12">
-        <v>16.850000000000001</v>
-      </c>
-      <c r="G28" s="12">
-        <f>ROUND((F28 - E28) / E28 * 100, 2)</f>
-        <v>-4.88</v>
-      </c>
-      <c r="H28" s="13" t="s">
-        <v>1068</v>
-      </c>
-      <c r="I28" s="13"/>
-      <c r="J28" s="37" t="s">
+      <c r="K27" s="13" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" s="42" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="42" t="s">
+        <v>515</v>
+      </c>
+      <c r="B28" s="43" t="s">
+        <v>822</v>
+      </c>
+      <c r="C28" s="44" t="s">
+        <v>829</v>
+      </c>
+      <c r="D28" s="43" t="s">
+        <v>1059</v>
+      </c>
+      <c r="E28" s="42">
+        <v>37.700000000000003</v>
+      </c>
+      <c r="F28" s="42">
+        <v>40.299999999999997</v>
+      </c>
+      <c r="G28" s="42">
+        <f t="shared" si="3"/>
+        <v>6.9</v>
+      </c>
+      <c r="H28" s="45" t="s">
+        <v>819</v>
+      </c>
+      <c r="I28" s="45">
+        <v>49.9</v>
+      </c>
+      <c r="J28" s="46" t="s">
         <v>784</v>
       </c>
-      <c r="K28" s="13" t="s">
-        <v>1080</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" s="42" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="42" t="s">
-        <v>515</v>
-      </c>
-      <c r="B29" s="43" t="s">
-        <v>822</v>
-      </c>
-      <c r="C29" s="44" t="s">
-        <v>829</v>
-      </c>
-      <c r="D29" s="43" t="s">
-        <v>1059</v>
-      </c>
-      <c r="E29" s="42">
-        <v>37.700000000000003</v>
-      </c>
-      <c r="F29" s="42">
-        <v>40.299999999999997</v>
-      </c>
-      <c r="G29" s="42">
-        <f>ROUND((F29 - E29) / E29 * 100, 2)</f>
-        <v>6.9</v>
-      </c>
-      <c r="H29" s="45" t="s">
-        <v>819</v>
-      </c>
-      <c r="I29" s="45">
-        <v>49.9</v>
-      </c>
-      <c r="J29" s="46" t="s">
+      <c r="K28" s="45" t="s">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B29" s="32" t="s">
+        <v>493</v>
+      </c>
+      <c r="C29" s="16">
+        <v>45992</v>
+      </c>
+      <c r="D29" s="32" t="s">
+        <v>1048</v>
+      </c>
+      <c r="E29" s="12">
+        <v>32.5</v>
+      </c>
+      <c r="F29" s="12">
+        <v>30.85</v>
+      </c>
+      <c r="G29" s="12">
+        <f t="shared" si="3"/>
+        <v>-5.08</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>1016</v>
+      </c>
+      <c r="I29" s="13">
+        <v>37.5</v>
+      </c>
+      <c r="J29" s="37" t="s">
         <v>784</v>
       </c>
-      <c r="K29" s="45" t="s">
-        <v>1057</v>
+      <c r="K29" s="13" t="s">
+        <v>752</v>
       </c>
     </row>
     <row r="30" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A30" s="12" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B30" s="32" t="s">
-        <v>493</v>
-      </c>
-      <c r="C30" s="16">
-        <v>45992</v>
+        <v>830</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>1019</v>
       </c>
       <c r="D30" s="32" t="s">
-        <v>1048</v>
+        <v>1031</v>
       </c>
       <c r="E30" s="12">
-        <v>32.5</v>
+        <v>43.35</v>
       </c>
       <c r="F30" s="12">
-        <v>30.85</v>
+        <v>41.15</v>
       </c>
       <c r="G30" s="12">
-        <f>ROUND((F30 - E30) / E30 * 100, 2)</f>
-        <v>-5.08</v>
+        <f t="shared" ref="G30" si="4">ROUND((F30 - E30) / E30 * 100, 2)</f>
+        <v>-5.07</v>
       </c>
       <c r="H30" s="13" t="s">
-        <v>1016</v>
-      </c>
-      <c r="I30" s="13">
-        <v>37.5</v>
-      </c>
+        <v>1020</v>
+      </c>
+      <c r="I30" s="13"/>
       <c r="J30" s="37" t="s">
         <v>784</v>
       </c>
       <c r="K30" s="13" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="B31" s="32" t="s">
-        <v>830</v>
-      </c>
-      <c r="C31" s="16" t="s">
-        <v>1019</v>
-      </c>
-      <c r="D31" s="32" t="s">
-        <v>1031</v>
-      </c>
-      <c r="E31" s="12">
-        <v>43.35</v>
-      </c>
-      <c r="F31" s="12">
-        <v>41.15</v>
-      </c>
-      <c r="G31" s="12">
-        <f t="shared" ref="G31" si="3">ROUND((F31 - E31) / E31 * 100, 2)</f>
-        <v>-5.07</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>1020</v>
-      </c>
-      <c r="I31" s="13"/>
-      <c r="J31" s="37" t="s">
-        <v>784</v>
-      </c>
-      <c r="K31" s="13" t="s">
         <v>1029</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" s="10" customFormat="1" ht="36" x14ac:dyDescent="0.3">
+      <c r="A31" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B31" s="31" t="s">
+        <v>528</v>
+      </c>
+      <c r="C31" s="15">
+        <v>45809</v>
+      </c>
+      <c r="D31" s="31" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E31" s="10">
+        <v>66.653000000000006</v>
+      </c>
+      <c r="F31" s="10">
+        <v>67</v>
+      </c>
+      <c r="G31" s="10">
+        <f>ROUND((F31 - E31) / E31 * 100, 2)</f>
+        <v>0.52</v>
+      </c>
+      <c r="H31" s="7" t="s">
+        <v>1000</v>
+      </c>
+      <c r="I31" s="7"/>
+      <c r="J31" s="38"/>
+      <c r="K31" s="7" t="s">
+        <v>1015</v>
       </c>
     </row>
     <row r="32" spans="1:11" s="10" customFormat="1" ht="36" x14ac:dyDescent="0.3">
@@ -19602,11 +19725,11 @@
         <v>66.653000000000006</v>
       </c>
       <c r="F32" s="10">
-        <v>67</v>
+        <v>67.599999999999994</v>
       </c>
       <c r="G32" s="10">
-        <f>ROUND((F32 - E32) / E32 * 100, 2)</f>
-        <v>0.52</v>
+        <f t="shared" ref="G32" si="5">ROUND((F32 - E32) / E32 * 100, 2)</f>
+        <v>1.42</v>
       </c>
       <c r="H32" s="7" t="s">
         <v>1000</v>
@@ -19617,269 +19740,271 @@
         <v>1015</v>
       </c>
     </row>
-    <row r="33" spans="1:11" s="10" customFormat="1" ht="36" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
-        <v>35</v>
+        <v>768</v>
       </c>
       <c r="B33" s="31" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="C33" s="15">
-        <v>45809</v>
+        <v>46003</v>
       </c>
       <c r="D33" s="31" t="s">
-        <v>1018</v>
+        <v>1014</v>
       </c>
       <c r="E33" s="10">
-        <v>66.653000000000006</v>
+        <v>92.1</v>
       </c>
       <c r="F33" s="10">
-        <v>67.599999999999994</v>
+        <v>92.6</v>
       </c>
       <c r="G33" s="10">
-        <f t="shared" ref="G33" si="4">ROUND((F33 - E33) / E33 * 100, 2)</f>
-        <v>1.42</v>
+        <f t="shared" ref="G33" si="6">ROUND((F33 - E33) / E33 * 100, 2)</f>
+        <v>0.54</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>1000</v>
-      </c>
-      <c r="I33" s="7"/>
+        <v>951</v>
+      </c>
+      <c r="I33" s="7">
+        <v>108</v>
+      </c>
       <c r="J33" s="38"/>
       <c r="K33" s="7" t="s">
-        <v>1015</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="10" t="s">
-        <v>768</v>
-      </c>
-      <c r="B34" s="31" t="s">
-        <v>533</v>
-      </c>
-      <c r="C34" s="15">
-        <v>46003</v>
-      </c>
-      <c r="D34" s="31" t="s">
-        <v>1014</v>
-      </c>
-      <c r="E34" s="10">
-        <v>92.1</v>
-      </c>
-      <c r="F34" s="10">
-        <v>92.6</v>
-      </c>
-      <c r="G34" s="10">
-        <f t="shared" ref="G34" si="5">ROUND((F34 - E34) / E34 * 100, 2)</f>
-        <v>0.54</v>
-      </c>
-      <c r="H34" s="7" t="s">
-        <v>951</v>
-      </c>
-      <c r="I34" s="7">
-        <v>108</v>
-      </c>
-      <c r="J34" s="38"/>
-      <c r="K34" s="7" t="s">
         <v>1012</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B34" s="32" t="s">
+        <v>587</v>
+      </c>
+      <c r="C34" s="16">
+        <v>45669</v>
+      </c>
+      <c r="D34" s="32"/>
+      <c r="E34" s="12">
+        <v>48.85</v>
+      </c>
+      <c r="F34" s="12">
+        <v>48.5</v>
+      </c>
+      <c r="G34" s="12">
+        <f t="shared" ref="G34" si="7">ROUND((F34 - E34) / E34 * 100, 2)</f>
+        <v>-0.72</v>
+      </c>
+      <c r="H34" s="13" t="s">
+        <v>923</v>
+      </c>
+      <c r="I34" s="13">
+        <v>59.5</v>
+      </c>
+      <c r="J34" s="37" t="s">
+        <v>784</v>
+      </c>
+      <c r="K34" s="13" t="s">
+        <v>1006</v>
       </c>
     </row>
     <row r="35" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A35" s="12" t="s">
-        <v>20</v>
+        <v>780</v>
       </c>
       <c r="B35" s="32" t="s">
-        <v>587</v>
+        <v>894</v>
       </c>
       <c r="C35" s="16">
-        <v>45669</v>
-      </c>
-      <c r="D35" s="32"/>
+        <v>45942</v>
+      </c>
+      <c r="D35" s="32" t="s">
+        <v>999</v>
+      </c>
       <c r="E35" s="12">
-        <v>48.85</v>
+        <v>11</v>
       </c>
       <c r="F35" s="12">
-        <v>48.5</v>
+        <v>9.9499999999999993</v>
       </c>
       <c r="G35" s="12">
-        <f t="shared" ref="G35" si="6">ROUND((F35 - E35) / E35 * 100, 2)</f>
-        <v>-0.72</v>
+        <f>ROUND((F35 - E35) / E35 * 100, 2)</f>
+        <v>-9.5500000000000007</v>
       </c>
       <c r="H35" s="13" t="s">
-        <v>923</v>
-      </c>
-      <c r="I35" s="13">
-        <v>59.5</v>
-      </c>
+        <v>947</v>
+      </c>
+      <c r="I35" s="13"/>
       <c r="J35" s="37" t="s">
-        <v>784</v>
+        <v>997</v>
       </c>
       <c r="K35" s="13" t="s">
-        <v>1006</v>
+        <v>996</v>
       </c>
     </row>
     <row r="36" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A36" s="12" t="s">
-        <v>780</v>
+        <v>30</v>
       </c>
       <c r="B36" s="32" t="s">
-        <v>894</v>
-      </c>
-      <c r="C36" s="16">
-        <v>45942</v>
+        <v>994</v>
+      </c>
+      <c r="C36" s="12" t="s">
+        <v>973</v>
       </c>
       <c r="D36" s="32" t="s">
         <v>999</v>
       </c>
       <c r="E36" s="12">
-        <v>11</v>
+        <v>34.270000000000003</v>
       </c>
       <c r="F36" s="12">
-        <v>9.9499999999999993</v>
+        <v>31.3</v>
       </c>
       <c r="G36" s="12">
         <f>ROUND((F36 - E36) / E36 * 100, 2)</f>
-        <v>-9.5500000000000007</v>
+        <v>-8.67</v>
       </c>
       <c r="H36" s="13" t="s">
-        <v>947</v>
+        <v>974</v>
       </c>
       <c r="I36" s="13"/>
       <c r="J36" s="37" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="K36" s="13" t="s">
-        <v>996</v>
+        <v>752</v>
       </c>
     </row>
     <row r="37" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A37" s="12" t="s">
-        <v>30</v>
+        <v>953</v>
       </c>
       <c r="B37" s="32" t="s">
-        <v>994</v>
-      </c>
-      <c r="C37" s="12" t="s">
-        <v>973</v>
+        <v>954</v>
+      </c>
+      <c r="C37" s="16">
+        <v>46003</v>
       </c>
       <c r="D37" s="32" t="s">
-        <v>999</v>
+        <v>985</v>
       </c>
       <c r="E37" s="12">
-        <v>34.270000000000003</v>
+        <v>28.75</v>
       </c>
       <c r="F37" s="12">
-        <v>31.3</v>
+        <v>27.35</v>
       </c>
       <c r="G37" s="12">
         <f>ROUND((F37 - E37) / E37 * 100, 2)</f>
-        <v>-8.67</v>
+        <v>-4.87</v>
       </c>
       <c r="H37" s="13" t="s">
-        <v>974</v>
-      </c>
-      <c r="I37" s="13"/>
+        <v>955</v>
+      </c>
+      <c r="I37" s="13">
+        <v>32.200000000000003</v>
+      </c>
       <c r="J37" s="37" t="s">
-        <v>998</v>
+        <v>784</v>
       </c>
       <c r="K37" s="13" t="s">
-        <v>752</v>
+        <v>757</v>
       </c>
     </row>
     <row r="38" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A38" s="12" t="s">
-        <v>953</v>
+        <v>34</v>
       </c>
       <c r="B38" s="32" t="s">
-        <v>954</v>
-      </c>
-      <c r="C38" s="16">
-        <v>46003</v>
+        <v>718</v>
+      </c>
+      <c r="C38" s="12" t="s">
+        <v>966</v>
       </c>
       <c r="D38" s="32" t="s">
-        <v>985</v>
+        <v>980</v>
       </c>
       <c r="E38" s="12">
-        <v>28.75</v>
+        <v>27.872</v>
       </c>
       <c r="F38" s="12">
-        <v>27.35</v>
+        <v>26.5</v>
       </c>
       <c r="G38" s="12">
         <f>ROUND((F38 - E38) / E38 * 100, 2)</f>
-        <v>-4.87</v>
+        <v>-4.92</v>
       </c>
       <c r="H38" s="13" t="s">
-        <v>955</v>
-      </c>
-      <c r="I38" s="13">
-        <v>32.200000000000003</v>
-      </c>
+        <v>967</v>
+      </c>
+      <c r="I38" s="13"/>
       <c r="J38" s="37" t="s">
         <v>784</v>
       </c>
       <c r="K38" s="13" t="s">
-        <v>757</v>
+        <v>970</v>
       </c>
     </row>
     <row r="39" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A39" s="12" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="B39" s="32" t="s">
-        <v>718</v>
-      </c>
-      <c r="C39" s="12" t="s">
-        <v>966</v>
+        <v>529</v>
+      </c>
+      <c r="C39" s="16">
+        <v>45881</v>
       </c>
       <c r="D39" s="32" t="s">
-        <v>980</v>
+        <v>958</v>
       </c>
       <c r="E39" s="12">
-        <v>27.872</v>
+        <v>4.8040000000000003</v>
       </c>
       <c r="F39" s="12">
-        <v>26.5</v>
+        <v>4.5599999999999996</v>
       </c>
       <c r="G39" s="12">
         <f>ROUND((F39 - E39) / E39 * 100, 2)</f>
-        <v>-4.92</v>
+        <v>-5.08</v>
       </c>
       <c r="H39" s="13" t="s">
-        <v>967</v>
+        <v>938</v>
       </c>
       <c r="I39" s="13"/>
       <c r="J39" s="37" t="s">
         <v>784</v>
       </c>
       <c r="K39" s="13" t="s">
-        <v>970</v>
+        <v>752</v>
       </c>
     </row>
     <row r="40" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A40" s="12" t="s">
-        <v>41</v>
+        <v>736</v>
       </c>
       <c r="B40" s="32" t="s">
-        <v>529</v>
-      </c>
-      <c r="C40" s="16">
-        <v>45881</v>
+        <v>754</v>
+      </c>
+      <c r="C40" s="12" t="s">
+        <v>907</v>
       </c>
       <c r="D40" s="32" t="s">
         <v>958</v>
       </c>
       <c r="E40" s="12">
-        <v>4.8040000000000003</v>
+        <v>12.41</v>
       </c>
       <c r="F40" s="12">
-        <v>4.5599999999999996</v>
+        <v>11.8</v>
       </c>
       <c r="G40" s="12">
-        <f>ROUND((F40 - E40) / E40 * 100, 2)</f>
-        <v>-5.08</v>
+        <f t="shared" ref="G40" si="8">ROUND((F40 - E40) / E40 * 100, 2)</f>
+        <v>-4.92</v>
       </c>
       <c r="H40" s="13" t="s">
-        <v>938</v>
+        <v>893</v>
       </c>
       <c r="I40" s="13"/>
       <c r="J40" s="37" t="s">
@@ -19891,608 +20016,613 @@
     </row>
     <row r="41" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A41" s="12" t="s">
-        <v>736</v>
+        <v>396</v>
       </c>
       <c r="B41" s="32" t="s">
-        <v>754</v>
-      </c>
-      <c r="C41" s="12" t="s">
-        <v>907</v>
+        <v>930</v>
+      </c>
+      <c r="C41" s="16">
+        <v>45759</v>
       </c>
       <c r="D41" s="32" t="s">
-        <v>958</v>
+        <v>952</v>
       </c>
       <c r="E41" s="12">
-        <v>12.41</v>
+        <v>29.524000000000001</v>
       </c>
       <c r="F41" s="12">
-        <v>11.8</v>
+        <v>26.4</v>
       </c>
       <c r="G41" s="12">
-        <f t="shared" ref="G41" si="7">ROUND((F41 - E41) / E41 * 100, 2)</f>
-        <v>-4.92</v>
+        <f>ROUND((F41 - E41) / E41 * 100, 2)</f>
+        <v>-10.58</v>
       </c>
       <c r="H41" s="13" t="s">
-        <v>893</v>
+        <v>931</v>
       </c>
       <c r="I41" s="13"/>
-      <c r="J41" s="37" t="s">
-        <v>784</v>
-      </c>
+      <c r="J41" s="37"/>
       <c r="K41" s="13" t="s">
-        <v>752</v>
+        <v>944</v>
       </c>
     </row>
     <row r="42" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A42" s="12" t="s">
-        <v>396</v>
+        <v>11</v>
       </c>
       <c r="B42" s="32" t="s">
-        <v>930</v>
-      </c>
-      <c r="C42" s="16">
-        <v>45759</v>
+        <v>587</v>
+      </c>
+      <c r="C42" s="16" t="s">
+        <v>836</v>
       </c>
       <c r="D42" s="32" t="s">
         <v>952</v>
       </c>
       <c r="E42" s="12">
-        <v>29.524000000000001</v>
+        <v>93.1</v>
       </c>
       <c r="F42" s="12">
-        <v>26.4</v>
+        <v>93</v>
       </c>
       <c r="G42" s="12">
         <f>ROUND((F42 - E42) / E42 * 100, 2)</f>
-        <v>-10.58</v>
+        <v>-0.11</v>
       </c>
       <c r="H42" s="13" t="s">
-        <v>931</v>
-      </c>
-      <c r="I42" s="13"/>
-      <c r="J42" s="37"/>
+        <v>760</v>
+      </c>
+      <c r="I42" s="13">
+        <v>107</v>
+      </c>
+      <c r="J42" s="37" t="s">
+        <v>945</v>
+      </c>
       <c r="K42" s="13" t="s">
-        <v>944</v>
+        <v>949</v>
       </c>
     </row>
     <row r="43" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A43" s="12" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B43" s="32" t="s">
-        <v>587</v>
-      </c>
-      <c r="C43" s="16" t="s">
-        <v>836</v>
+        <v>908</v>
+      </c>
+      <c r="C43" s="12" t="s">
+        <v>907</v>
       </c>
       <c r="D43" s="32" t="s">
         <v>952</v>
       </c>
       <c r="E43" s="12">
-        <v>93.1</v>
+        <v>28.93</v>
       </c>
       <c r="F43" s="12">
-        <v>93</v>
+        <v>27.5</v>
       </c>
       <c r="G43" s="12">
-        <f>ROUND((F43 - E43) / E43 * 100, 2)</f>
-        <v>-0.11</v>
+        <f t="shared" ref="G43" si="9">ROUND((F43 - E43) / E43 * 100, 2)</f>
+        <v>-4.9400000000000004</v>
       </c>
       <c r="H43" s="13" t="s">
-        <v>760</v>
+        <v>893</v>
       </c>
       <c r="I43" s="13">
-        <v>107</v>
+        <v>33.799999999999997</v>
       </c>
       <c r="J43" s="37" t="s">
-        <v>945</v>
+        <v>784</v>
       </c>
       <c r="K43" s="13" t="s">
-        <v>949</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="B44" s="32" t="s">
-        <v>908</v>
-      </c>
-      <c r="C44" s="12" t="s">
-        <v>907</v>
+        <v>811</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="10" t="s">
+        <v>780</v>
+      </c>
+      <c r="B44" s="31" t="s">
+        <v>894</v>
+      </c>
+      <c r="C44" s="10" t="s">
+        <v>892</v>
       </c>
       <c r="D44" s="32" t="s">
-        <v>952</v>
-      </c>
-      <c r="E44" s="12">
-        <v>28.93</v>
-      </c>
-      <c r="F44" s="12">
-        <v>27.5</v>
-      </c>
-      <c r="G44" s="12">
-        <f t="shared" ref="G44" si="8">ROUND((F44 - E44) / E44 * 100, 2)</f>
-        <v>-4.9400000000000004</v>
-      </c>
-      <c r="H44" s="13" t="s">
+        <v>942</v>
+      </c>
+      <c r="E44" s="10">
+        <v>10.507999999999999</v>
+      </c>
+      <c r="F44" s="10">
+        <v>11.25</v>
+      </c>
+      <c r="G44" s="10">
+        <f t="shared" ref="G44" si="10">ROUND((F44 - E44) / E44 * 100, 2)</f>
+        <v>7.06</v>
+      </c>
+      <c r="H44" s="7" t="s">
         <v>893</v>
       </c>
-      <c r="I44" s="13">
-        <v>33.799999999999997</v>
-      </c>
-      <c r="J44" s="37" t="s">
+      <c r="I44" s="7">
+        <v>11.6</v>
+      </c>
+      <c r="J44" s="38" t="s">
         <v>784</v>
       </c>
-      <c r="K44" s="13" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="10" t="s">
-        <v>780</v>
-      </c>
-      <c r="B45" s="31" t="s">
-        <v>894</v>
-      </c>
-      <c r="C45" s="10" t="s">
-        <v>892</v>
+      <c r="K44" s="7" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B45" s="32" t="s">
+        <v>493</v>
+      </c>
+      <c r="C45" s="12" t="s">
+        <v>912</v>
       </c>
       <c r="D45" s="32" t="s">
         <v>942</v>
       </c>
-      <c r="E45" s="10">
-        <v>10.507999999999999</v>
-      </c>
-      <c r="F45" s="10">
-        <v>11.25</v>
-      </c>
-      <c r="G45" s="10">
-        <f t="shared" ref="G45" si="9">ROUND((F45 - E45) / E45 * 100, 2)</f>
-        <v>7.06</v>
-      </c>
-      <c r="H45" s="7" t="s">
-        <v>893</v>
-      </c>
-      <c r="I45" s="7">
-        <v>11.6</v>
-      </c>
-      <c r="J45" s="38" t="s">
+      <c r="E45" s="12">
+        <v>43.435000000000002</v>
+      </c>
+      <c r="F45" s="12">
+        <v>41.25</v>
+      </c>
+      <c r="G45" s="12">
+        <f>ROUND((F45 - E45) / E45 * 100, 2)</f>
+        <v>-5.03</v>
+      </c>
+      <c r="H45" s="13" t="s">
+        <v>915</v>
+      </c>
+      <c r="I45" s="13">
+        <v>48.5</v>
+      </c>
+      <c r="J45" s="37" t="s">
         <v>784</v>
       </c>
-      <c r="K45" s="7" t="s">
-        <v>940</v>
+      <c r="K45" s="13" t="s">
+        <v>941</v>
       </c>
     </row>
     <row r="46" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A46" s="12" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B46" s="32" t="s">
-        <v>493</v>
+        <v>625</v>
       </c>
       <c r="C46" s="12" t="s">
         <v>912</v>
       </c>
       <c r="D46" s="32" t="s">
-        <v>942</v>
+        <v>937</v>
       </c>
       <c r="E46" s="12">
-        <v>43.435000000000002</v>
+        <v>45.936999999999998</v>
       </c>
       <c r="F46" s="12">
-        <v>41.25</v>
+        <v>43.65</v>
       </c>
       <c r="G46" s="12">
         <f>ROUND((F46 - E46) / E46 * 100, 2)</f>
-        <v>-5.03</v>
+        <v>-4.9800000000000004</v>
       </c>
       <c r="H46" s="13" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="I46" s="13">
-        <v>48.5</v>
+        <v>52.5</v>
       </c>
       <c r="J46" s="37" t="s">
         <v>784</v>
       </c>
       <c r="K46" s="13" t="s">
-        <v>941</v>
+        <v>936</v>
       </c>
     </row>
     <row r="47" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A47" s="12" t="s">
-        <v>22</v>
+        <v>735</v>
       </c>
       <c r="B47" s="32" t="s">
-        <v>625</v>
-      </c>
-      <c r="C47" s="12" t="s">
-        <v>912</v>
+        <v>822</v>
+      </c>
+      <c r="C47" s="16">
+        <v>45819</v>
       </c>
       <c r="D47" s="32" t="s">
-        <v>937</v>
+        <v>922</v>
       </c>
       <c r="E47" s="12">
-        <v>45.936999999999998</v>
+        <v>31.475000000000001</v>
       </c>
       <c r="F47" s="12">
-        <v>43.65</v>
+        <v>30.8</v>
       </c>
       <c r="G47" s="12">
-        <f>ROUND((F47 - E47) / E47 * 100, 2)</f>
-        <v>-4.9800000000000004</v>
+        <f t="shared" ref="G47" si="11">ROUND((F47 - E47) / E47 * 100, 2)</f>
+        <v>-2.14</v>
       </c>
       <c r="H47" s="13" t="s">
-        <v>914</v>
+        <v>835</v>
       </c>
       <c r="I47" s="13">
-        <v>52.5</v>
+        <v>35.35</v>
       </c>
       <c r="J47" s="37" t="s">
         <v>784</v>
       </c>
       <c r="K47" s="13" t="s">
-        <v>936</v>
+        <v>918</v>
       </c>
     </row>
     <row r="48" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A48" s="12" t="s">
-        <v>735</v>
+        <v>107</v>
       </c>
       <c r="B48" s="32" t="s">
-        <v>822</v>
+        <v>879</v>
       </c>
       <c r="C48" s="16">
-        <v>45819</v>
-      </c>
-      <c r="D48" s="32" t="s">
-        <v>922</v>
+        <v>45941</v>
+      </c>
+      <c r="D48" s="16" t="s">
+        <v>911</v>
       </c>
       <c r="E48" s="12">
-        <v>31.475000000000001</v>
+        <v>16.914999999999999</v>
       </c>
       <c r="F48" s="12">
-        <v>30.8</v>
+        <v>16.05</v>
       </c>
       <c r="G48" s="12">
-        <f t="shared" ref="G48" si="10">ROUND((F48 - E48) / E48 * 100, 2)</f>
-        <v>-2.14</v>
+        <f t="shared" ref="G48:G61" si="12">ROUND((F48 - E48) / E48 * 100, 2)</f>
+        <v>-5.1100000000000003</v>
       </c>
       <c r="H48" s="13" t="s">
-        <v>835</v>
+        <v>843</v>
       </c>
       <c r="I48" s="13">
-        <v>35.35</v>
+        <v>19.5</v>
       </c>
       <c r="J48" s="37" t="s">
         <v>784</v>
       </c>
       <c r="K48" s="13" t="s">
-        <v>918</v>
+        <v>909</v>
       </c>
     </row>
     <row r="49" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A49" s="12" t="s">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="B49" s="32" t="s">
-        <v>879</v>
-      </c>
-      <c r="C49" s="16">
-        <v>45941</v>
+        <v>489</v>
+      </c>
+      <c r="C49" s="12" t="s">
+        <v>892</v>
       </c>
       <c r="D49" s="16" t="s">
         <v>911</v>
       </c>
       <c r="E49" s="12">
-        <v>16.914999999999999</v>
+        <v>21.016999999999999</v>
       </c>
       <c r="F49" s="12">
-        <v>16.05</v>
+        <v>19.95</v>
       </c>
       <c r="G49" s="12">
-        <f t="shared" ref="G49:G62" si="11">ROUND((F49 - E49) / E49 * 100, 2)</f>
-        <v>-5.1100000000000003</v>
+        <f t="shared" si="12"/>
+        <v>-5.08</v>
       </c>
       <c r="H49" s="13" t="s">
-        <v>843</v>
+        <v>893</v>
       </c>
       <c r="I49" s="13">
-        <v>19.5</v>
+        <v>24.6</v>
       </c>
       <c r="J49" s="37" t="s">
         <v>784</v>
       </c>
       <c r="K49" s="13" t="s">
-        <v>909</v>
+        <v>758</v>
       </c>
     </row>
     <row r="50" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A50" s="12" t="s">
-        <v>10</v>
+        <v>842</v>
       </c>
       <c r="B50" s="32" t="s">
-        <v>489</v>
-      </c>
-      <c r="C50" s="12" t="s">
-        <v>892</v>
-      </c>
-      <c r="D50" s="16" t="s">
-        <v>911</v>
-      </c>
+        <v>731</v>
+      </c>
+      <c r="C50" s="16" t="s">
+        <v>841</v>
+      </c>
+      <c r="D50" s="32"/>
       <c r="E50" s="12">
-        <v>21.016999999999999</v>
+        <v>54.65</v>
       </c>
       <c r="F50" s="12">
-        <v>19.95</v>
+        <v>53.4</v>
       </c>
       <c r="G50" s="12">
-        <f t="shared" si="11"/>
-        <v>-5.08</v>
+        <f t="shared" si="12"/>
+        <v>-2.29</v>
       </c>
       <c r="H50" s="13" t="s">
-        <v>893</v>
+        <v>843</v>
       </c>
       <c r="I50" s="13">
-        <v>24.6</v>
+        <v>60</v>
       </c>
       <c r="J50" s="37" t="s">
         <v>784</v>
       </c>
       <c r="K50" s="13" t="s">
-        <v>758</v>
+        <v>752</v>
       </c>
     </row>
     <row r="51" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A51" s="12" t="s">
-        <v>842</v>
+        <v>821</v>
       </c>
       <c r="B51" s="32" t="s">
-        <v>731</v>
+        <v>822</v>
       </c>
       <c r="C51" s="16" t="s">
-        <v>841</v>
-      </c>
-      <c r="D51" s="32"/>
+        <v>820</v>
+      </c>
+      <c r="D51" s="32" t="s">
+        <v>907</v>
+      </c>
       <c r="E51" s="12">
-        <v>54.65</v>
+        <v>34.33</v>
       </c>
       <c r="F51" s="12">
-        <v>53.4</v>
+        <v>33.9</v>
       </c>
       <c r="G51" s="12">
-        <f t="shared" si="11"/>
-        <v>-2.29</v>
+        <f t="shared" si="12"/>
+        <v>-1.25</v>
       </c>
       <c r="H51" s="13" t="s">
-        <v>843</v>
-      </c>
-      <c r="I51" s="13">
-        <v>60</v>
+        <v>819</v>
+      </c>
+      <c r="I51" s="13" t="s">
+        <v>897</v>
       </c>
       <c r="J51" s="37" t="s">
         <v>784</v>
       </c>
       <c r="K51" s="13" t="s">
-        <v>752</v>
+        <v>906</v>
       </c>
     </row>
     <row r="52" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A52" s="12" t="s">
-        <v>821</v>
+        <v>35</v>
       </c>
       <c r="B52" s="32" t="s">
-        <v>822</v>
-      </c>
-      <c r="C52" s="16" t="s">
-        <v>820</v>
+        <v>871</v>
+      </c>
+      <c r="C52" s="16">
+        <v>45819</v>
       </c>
       <c r="D52" s="32" t="s">
-        <v>907</v>
+        <v>903</v>
       </c>
       <c r="E52" s="12">
-        <v>34.33</v>
+        <v>68.954999999999998</v>
       </c>
       <c r="F52" s="12">
-        <v>33.9</v>
+        <v>65.5</v>
       </c>
       <c r="G52" s="12">
-        <f t="shared" si="11"/>
-        <v>-1.25</v>
+        <f t="shared" si="12"/>
+        <v>-5.01</v>
       </c>
       <c r="H52" s="13" t="s">
-        <v>819</v>
-      </c>
-      <c r="I52" s="13" t="s">
-        <v>897</v>
+        <v>872</v>
+      </c>
+      <c r="I52" s="13">
+        <v>78</v>
       </c>
       <c r="J52" s="37" t="s">
         <v>784</v>
       </c>
       <c r="K52" s="13" t="s">
-        <v>906</v>
+        <v>757</v>
       </c>
     </row>
     <row r="53" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A53" s="12" t="s">
-        <v>35</v>
+        <v>823</v>
       </c>
       <c r="B53" s="32" t="s">
-        <v>871</v>
-      </c>
-      <c r="C53" s="16">
-        <v>45819</v>
+        <v>731</v>
+      </c>
+      <c r="C53" s="16" t="s">
+        <v>852</v>
       </c>
       <c r="D53" s="32" t="s">
-        <v>903</v>
+        <v>889</v>
       </c>
       <c r="E53" s="12">
-        <v>68.954999999999998</v>
+        <v>17.965</v>
       </c>
       <c r="F53" s="12">
-        <v>65.5</v>
+        <v>17.05</v>
       </c>
       <c r="G53" s="12">
-        <f t="shared" si="11"/>
-        <v>-5.01</v>
+        <f t="shared" si="12"/>
+        <v>-5.09</v>
       </c>
       <c r="H53" s="13" t="s">
-        <v>872</v>
-      </c>
-      <c r="I53" s="13">
-        <v>78</v>
+        <v>853</v>
+      </c>
+      <c r="I53" s="13" t="s">
+        <v>886</v>
       </c>
       <c r="J53" s="37" t="s">
         <v>784</v>
       </c>
       <c r="K53" s="13" t="s">
-        <v>757</v>
+        <v>887</v>
       </c>
     </row>
     <row r="54" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A54" s="12" t="s">
-        <v>823</v>
+        <v>107</v>
       </c>
       <c r="B54" s="32" t="s">
-        <v>731</v>
-      </c>
-      <c r="C54" s="16" t="s">
-        <v>852</v>
+        <v>867</v>
+      </c>
+      <c r="C54" s="16">
+        <v>45788</v>
       </c>
       <c r="D54" s="32" t="s">
-        <v>889</v>
+        <v>878</v>
       </c>
       <c r="E54" s="12">
-        <v>17.965</v>
+        <v>17.114000000000001</v>
       </c>
       <c r="F54" s="12">
-        <v>17.05</v>
+        <v>16.25</v>
       </c>
       <c r="G54" s="12">
-        <f t="shared" si="11"/>
-        <v>-5.09</v>
+        <f t="shared" si="12"/>
+        <v>-5.05</v>
       </c>
       <c r="H54" s="13" t="s">
-        <v>853</v>
-      </c>
-      <c r="I54" s="13" t="s">
-        <v>886</v>
-      </c>
+        <v>868</v>
+      </c>
+      <c r="I54" s="13"/>
       <c r="J54" s="37" t="s">
         <v>784</v>
       </c>
       <c r="K54" s="13" t="s">
-        <v>887</v>
+        <v>874</v>
       </c>
     </row>
     <row r="55" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A55" s="12" t="s">
-        <v>107</v>
+        <v>13</v>
       </c>
       <c r="B55" s="32" t="s">
-        <v>867</v>
+        <v>686</v>
       </c>
       <c r="C55" s="16">
-        <v>45788</v>
+        <v>45727</v>
       </c>
       <c r="D55" s="32" t="s">
-        <v>878</v>
+        <v>870</v>
       </c>
       <c r="E55" s="12">
-        <v>17.114000000000001</v>
+        <v>40.131999999999998</v>
       </c>
       <c r="F55" s="12">
-        <v>16.25</v>
+        <v>39.049999999999997</v>
       </c>
       <c r="G55" s="12">
-        <f t="shared" si="11"/>
-        <v>-5.05</v>
+        <f t="shared" si="12"/>
+        <v>-2.7</v>
       </c>
       <c r="H55" s="13" t="s">
-        <v>868</v>
-      </c>
-      <c r="I55" s="13"/>
+        <v>860</v>
+      </c>
+      <c r="I55" s="13">
+        <v>45.4</v>
+      </c>
       <c r="J55" s="37" t="s">
         <v>784</v>
       </c>
       <c r="K55" s="13" t="s">
-        <v>874</v>
+        <v>796</v>
       </c>
     </row>
     <row r="56" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A56" s="12" t="s">
-        <v>13</v>
+        <v>863</v>
       </c>
       <c r="B56" s="32" t="s">
-        <v>686</v>
+        <v>776</v>
       </c>
       <c r="C56" s="16">
-        <v>45727</v>
+        <v>45758</v>
       </c>
       <c r="D56" s="32" t="s">
         <v>870</v>
       </c>
       <c r="E56" s="12">
-        <v>40.131999999999998</v>
+        <v>25.971</v>
       </c>
       <c r="F56" s="12">
-        <v>39.049999999999997</v>
+        <v>25.45</v>
       </c>
       <c r="G56" s="12">
-        <f t="shared" si="11"/>
-        <v>-2.7</v>
+        <f t="shared" si="12"/>
+        <v>-2.0099999999999998</v>
       </c>
       <c r="H56" s="13" t="s">
-        <v>860</v>
-      </c>
-      <c r="I56" s="13">
-        <v>45.4</v>
-      </c>
-      <c r="J56" s="37" t="s">
-        <v>784</v>
-      </c>
+        <v>760</v>
+      </c>
+      <c r="I56" s="13"/>
+      <c r="J56" s="37"/>
       <c r="K56" s="13" t="s">
-        <v>796</v>
+        <v>752</v>
       </c>
     </row>
     <row r="57" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A57" s="12" t="s">
-        <v>863</v>
+        <v>30</v>
       </c>
       <c r="B57" s="32" t="s">
-        <v>776</v>
-      </c>
-      <c r="C57" s="16">
-        <v>45758</v>
+        <v>510</v>
+      </c>
+      <c r="C57" s="16" t="s">
+        <v>836</v>
       </c>
       <c r="D57" s="32" t="s">
-        <v>870</v>
+        <v>862</v>
       </c>
       <c r="E57" s="12">
-        <v>25.971</v>
+        <v>35.078000000000003</v>
       </c>
       <c r="F57" s="12">
-        <v>25.45</v>
+        <v>33.299999999999997</v>
       </c>
       <c r="G57" s="12">
-        <f t="shared" si="11"/>
-        <v>-2.0099999999999998</v>
+        <f t="shared" si="12"/>
+        <v>-5.07</v>
       </c>
       <c r="H57" s="13" t="s">
         <v>760</v>
       </c>
-      <c r="I57" s="13"/>
-      <c r="J57" s="37"/>
+      <c r="I57" s="13">
+        <v>38</v>
+      </c>
+      <c r="J57" s="37" t="s">
+        <v>784</v>
+      </c>
       <c r="K57" s="13" t="s">
-        <v>752</v>
+        <v>859</v>
+      </c>
+      <c r="L57" s="12" t="s">
+        <v>865</v>
       </c>
     </row>
     <row r="58" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A58" s="12" t="s">
-        <v>30</v>
+        <v>655</v>
       </c>
       <c r="B58" s="32" t="s">
-        <v>510</v>
+        <v>587</v>
       </c>
       <c r="C58" s="16" t="s">
         <v>836</v>
@@ -20501,398 +20631,395 @@
         <v>862</v>
       </c>
       <c r="E58" s="12">
-        <v>35.078000000000003</v>
+        <v>93.674999999999997</v>
       </c>
       <c r="F58" s="12">
-        <v>33.299999999999997</v>
+        <v>89</v>
       </c>
       <c r="G58" s="12">
-        <f t="shared" si="11"/>
-        <v>-5.07</v>
-      </c>
-      <c r="H58" s="13" t="s">
-        <v>760</v>
-      </c>
+        <f t="shared" si="12"/>
+        <v>-4.99</v>
+      </c>
+      <c r="H58" s="13"/>
       <c r="I58" s="13">
-        <v>38</v>
+        <v>101</v>
       </c>
       <c r="J58" s="37" t="s">
         <v>784</v>
       </c>
       <c r="K58" s="13" t="s">
-        <v>859</v>
-      </c>
-      <c r="L58" s="12" t="s">
-        <v>865</v>
+        <v>858</v>
       </c>
     </row>
     <row r="59" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A59" s="12" t="s">
-        <v>655</v>
+        <v>37</v>
       </c>
       <c r="B59" s="32" t="s">
-        <v>587</v>
+        <v>846</v>
       </c>
       <c r="C59" s="16" t="s">
-        <v>836</v>
+        <v>845</v>
       </c>
       <c r="D59" s="32" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="E59" s="12">
-        <v>93.674999999999997</v>
+        <v>13.51</v>
       </c>
       <c r="F59" s="12">
-        <v>89</v>
+        <v>12.8</v>
       </c>
       <c r="G59" s="12">
-        <f t="shared" si="11"/>
-        <v>-4.99</v>
-      </c>
-      <c r="H59" s="13"/>
-      <c r="I59" s="13">
-        <v>101</v>
-      </c>
+        <f t="shared" si="12"/>
+        <v>-5.26</v>
+      </c>
+      <c r="H59" s="13" t="s">
+        <v>847</v>
+      </c>
+      <c r="I59" s="13"/>
       <c r="J59" s="37" t="s">
         <v>784</v>
       </c>
       <c r="K59" s="13" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="B60" s="32" t="s">
-        <v>846</v>
-      </c>
-      <c r="C60" s="16" t="s">
-        <v>845</v>
-      </c>
-      <c r="D60" s="32" t="s">
-        <v>857</v>
-      </c>
-      <c r="E60" s="12">
-        <v>13.51</v>
-      </c>
-      <c r="F60" s="12">
-        <v>12.8</v>
-      </c>
-      <c r="G60" s="12">
-        <f t="shared" si="11"/>
-        <v>-5.26</v>
-      </c>
-      <c r="H60" s="13" t="s">
-        <v>847</v>
-      </c>
-      <c r="I60" s="13"/>
-      <c r="J60" s="37" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="10" t="s">
+        <v>823</v>
+      </c>
+      <c r="B60" s="31" t="s">
+        <v>824</v>
+      </c>
+      <c r="C60" s="15" t="s">
+        <v>820</v>
+      </c>
+      <c r="D60" s="15" t="s">
+        <v>850</v>
+      </c>
+      <c r="E60" s="10">
+        <v>16.559999999999999</v>
+      </c>
+      <c r="F60" s="10">
+        <v>17.75</v>
+      </c>
+      <c r="G60" s="10">
+        <f t="shared" si="12"/>
+        <v>7.19</v>
+      </c>
+      <c r="H60" s="7" t="s">
+        <v>819</v>
+      </c>
+      <c r="I60" s="7">
+        <v>17.75</v>
+      </c>
+      <c r="J60" s="38" t="s">
         <v>784</v>
       </c>
-      <c r="K60" s="13" t="s">
-        <v>856</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="10" t="s">
-        <v>823</v>
-      </c>
-      <c r="B61" s="31" t="s">
-        <v>824</v>
-      </c>
-      <c r="C61" s="15" t="s">
-        <v>820</v>
-      </c>
-      <c r="D61" s="15" t="s">
-        <v>850</v>
-      </c>
-      <c r="E61" s="10">
-        <v>16.559999999999999</v>
-      </c>
-      <c r="F61" s="10">
-        <v>17.75</v>
-      </c>
-      <c r="G61" s="10">
-        <f t="shared" si="11"/>
-        <v>7.19</v>
-      </c>
-      <c r="H61" s="7" t="s">
+      <c r="K60" s="7" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="12" t="s">
+        <v>827</v>
+      </c>
+      <c r="B61" s="32" t="s">
+        <v>533</v>
+      </c>
+      <c r="C61" s="16" t="s">
+        <v>826</v>
+      </c>
+      <c r="D61" s="32" t="s">
+        <v>841</v>
+      </c>
+      <c r="E61" s="12">
+        <v>113.3</v>
+      </c>
+      <c r="F61" s="12">
+        <v>104</v>
+      </c>
+      <c r="G61" s="12">
+        <f t="shared" si="12"/>
+        <v>-8.2100000000000009</v>
+      </c>
+      <c r="H61" s="13" t="s">
         <v>819</v>
       </c>
-      <c r="I61" s="7">
-        <v>17.75</v>
-      </c>
-      <c r="J61" s="38" t="s">
-        <v>784</v>
-      </c>
-      <c r="K61" s="7" t="s">
-        <v>837</v>
+      <c r="I61" s="13"/>
+      <c r="J61" s="37" t="s">
+        <v>840</v>
+      </c>
+      <c r="K61" s="13" t="s">
+        <v>838</v>
       </c>
     </row>
     <row r="62" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A62" s="12" t="s">
-        <v>827</v>
+        <v>24</v>
       </c>
       <c r="B62" s="32" t="s">
-        <v>533</v>
+        <v>776</v>
       </c>
       <c r="C62" s="16" t="s">
-        <v>826</v>
+        <v>816</v>
       </c>
       <c r="D62" s="32" t="s">
-        <v>841</v>
+        <v>848</v>
       </c>
       <c r="E62" s="12">
-        <v>113.3</v>
+        <v>30.425000000000001</v>
       </c>
       <c r="F62" s="12">
-        <v>104</v>
+        <v>28.9</v>
       </c>
       <c r="G62" s="12">
-        <f t="shared" si="11"/>
-        <v>-8.2100000000000009</v>
+        <f t="shared" ref="G62" si="13">ROUND((F62 - E62) / E62 * 100, 2)</f>
+        <v>-5.01</v>
       </c>
       <c r="H62" s="13" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="I62" s="13"/>
       <c r="J62" s="37" t="s">
-        <v>840</v>
+        <v>784</v>
       </c>
       <c r="K62" s="13" t="s">
-        <v>838</v>
+        <v>833</v>
       </c>
     </row>
     <row r="63" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A63" s="12" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="B63" s="32" t="s">
-        <v>776</v>
+        <v>505</v>
       </c>
       <c r="C63" s="16" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="D63" s="32" t="s">
         <v>848</v>
       </c>
       <c r="E63" s="12">
-        <v>30.425000000000001</v>
+        <v>22.22</v>
       </c>
       <c r="F63" s="12">
-        <v>28.9</v>
+        <v>21.1</v>
       </c>
       <c r="G63" s="12">
-        <f t="shared" ref="G63" si="12">ROUND((F63 - E63) / E63 * 100, 2)</f>
-        <v>-5.01</v>
+        <f>ROUND((F63 - E63) / E63 * 100, 2)</f>
+        <v>-5.04</v>
       </c>
       <c r="H63" s="13" t="s">
-        <v>817</v>
-      </c>
-      <c r="I63" s="13"/>
+        <v>819</v>
+      </c>
+      <c r="I63" s="13">
+        <v>24.6</v>
+      </c>
       <c r="J63" s="37" t="s">
         <v>784</v>
       </c>
       <c r="K63" s="13" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
     </row>
     <row r="64" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="12" t="s">
-        <v>10</v>
-      </c>
+      <c r="A64" s="8"/>
       <c r="B64" s="32" t="s">
-        <v>505</v>
-      </c>
-      <c r="C64" s="16" t="s">
-        <v>820</v>
-      </c>
-      <c r="D64" s="32" t="s">
-        <v>848</v>
-      </c>
+        <v>792</v>
+      </c>
+      <c r="C64" s="16">
+        <v>45940</v>
+      </c>
+      <c r="D64" s="32"/>
       <c r="E64" s="12">
-        <v>22.22</v>
+        <v>15.863</v>
       </c>
       <c r="F64" s="12">
-        <v>21.1</v>
+        <v>15.05</v>
       </c>
       <c r="G64" s="12">
-        <f>ROUND((F64 - E64) / E64 * 100, 2)</f>
-        <v>-5.04</v>
+        <f t="shared" ref="G64" si="14">ROUND((F64 - E64) / E64 * 100, 2)</f>
+        <v>-5.13</v>
       </c>
       <c r="H64" s="13" t="s">
-        <v>819</v>
-      </c>
-      <c r="I64" s="13">
-        <v>24.6</v>
-      </c>
+        <v>793</v>
+      </c>
+      <c r="I64" s="13"/>
       <c r="J64" s="37" t="s">
         <v>784</v>
       </c>
       <c r="K64" s="13" t="s">
-        <v>834</v>
+        <v>812</v>
       </c>
     </row>
     <row r="65" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A65" s="8"/>
       <c r="B65" s="32" t="s">
-        <v>792</v>
+        <v>528</v>
       </c>
       <c r="C65" s="16">
-        <v>45940</v>
-      </c>
-      <c r="D65" s="32"/>
+        <v>45848</v>
+      </c>
+      <c r="D65" s="32" t="s">
+        <v>814</v>
+      </c>
       <c r="E65" s="12">
-        <v>15.863</v>
+        <v>12.484999999999999</v>
       </c>
       <c r="F65" s="12">
-        <v>15.05</v>
+        <v>11.8</v>
       </c>
       <c r="G65" s="12">
-        <f t="shared" ref="G65" si="13">ROUND((F65 - E65) / E65 * 100, 2)</f>
-        <v>-5.13</v>
+        <f>ROUND((F65 - E65) / E65 * 100, 2)</f>
+        <v>-5.49</v>
       </c>
       <c r="H65" s="13" t="s">
-        <v>793</v>
+        <v>760</v>
       </c>
       <c r="I65" s="13"/>
       <c r="J65" s="37" t="s">
-        <v>784</v>
+        <v>802</v>
       </c>
       <c r="K65" s="13" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="66" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="8"/>
+      <c r="A66" s="12" t="s">
+        <v>1</v>
+      </c>
       <c r="B66" s="32" t="s">
-        <v>528</v>
+        <v>777</v>
       </c>
       <c r="C66" s="16">
-        <v>45848</v>
+        <v>45818</v>
       </c>
       <c r="D66" s="32" t="s">
         <v>814</v>
       </c>
       <c r="E66" s="12">
-        <v>12.484999999999999</v>
+        <v>31.4</v>
       </c>
       <c r="F66" s="12">
-        <v>11.8</v>
+        <v>29.9</v>
       </c>
       <c r="G66" s="12">
-        <f>ROUND((F66 - E66) / E66 * 100, 2)</f>
-        <v>-5.49</v>
+        <f t="shared" ref="G66" si="15">ROUND((F66 - E66) / E66 * 100, 2)</f>
+        <v>-4.78</v>
       </c>
       <c r="H66" s="13" t="s">
-        <v>760</v>
-      </c>
-      <c r="I66" s="13"/>
+        <v>767</v>
+      </c>
+      <c r="I66" s="13">
+        <v>38.5</v>
+      </c>
       <c r="J66" s="37" t="s">
-        <v>802</v>
+        <v>784</v>
       </c>
       <c r="K66" s="13" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="67" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A67" s="12" t="s">
-        <v>1</v>
+        <v>780</v>
       </c>
       <c r="B67" s="32" t="s">
-        <v>777</v>
+        <v>488</v>
       </c>
       <c r="C67" s="16">
-        <v>45818</v>
+        <v>45698</v>
       </c>
       <c r="D67" s="32" t="s">
         <v>814</v>
       </c>
       <c r="E67" s="12">
-        <v>31.4</v>
+        <v>13.1</v>
       </c>
       <c r="F67" s="12">
-        <v>29.9</v>
+        <v>12.5</v>
       </c>
       <c r="G67" s="12">
-        <f t="shared" ref="G67" si="14">ROUND((F67 - E67) / E67 * 100, 2)</f>
-        <v>-4.78</v>
+        <f t="shared" ref="G67" si="16">ROUND((F67 - E67) / E67 * 100, 2)</f>
+        <v>-4.58</v>
       </c>
       <c r="H67" s="13" t="s">
         <v>767</v>
       </c>
       <c r="I67" s="13">
-        <v>38.5</v>
+        <v>14.9</v>
       </c>
       <c r="J67" s="37" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="K67" s="13" t="s">
-        <v>810</v>
+        <v>752</v>
       </c>
     </row>
     <row r="68" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A68" s="12" t="s">
-        <v>780</v>
+        <v>24</v>
       </c>
       <c r="B68" s="32" t="s">
         <v>488</v>
       </c>
-      <c r="C68" s="16">
-        <v>45698</v>
+      <c r="C68" s="16" t="s">
+        <v>744</v>
       </c>
       <c r="D68" s="32" t="s">
         <v>814</v>
       </c>
       <c r="E68" s="12">
-        <v>13.1</v>
+        <v>13.311</v>
       </c>
       <c r="F68" s="12">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="G68" s="12">
-        <f t="shared" ref="G68" si="15">ROUND((F68 - E68) / E68 * 100, 2)</f>
-        <v>-4.58</v>
+        <f t="shared" ref="G68" si="17">ROUND((F68 - E68) / E68 * 100, 2)</f>
+        <v>-2.34</v>
       </c>
       <c r="H68" s="13" t="s">
-        <v>767</v>
+        <v>747</v>
       </c>
       <c r="I68" s="13">
-        <v>14.9</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="J68" s="37" t="s">
-        <v>785</v>
+        <v>774</v>
       </c>
       <c r="K68" s="13" t="s">
-        <v>752</v>
+        <v>788</v>
       </c>
     </row>
     <row r="69" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A69" s="12" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="B69" s="32" t="s">
         <v>488</v>
       </c>
-      <c r="C69" s="16" t="s">
-        <v>744</v>
+      <c r="C69" s="16">
+        <v>45667</v>
       </c>
       <c r="D69" s="32" t="s">
         <v>814</v>
       </c>
       <c r="E69" s="12">
-        <v>13.311</v>
+        <v>14.1</v>
       </c>
       <c r="F69" s="12">
         <v>13</v>
       </c>
       <c r="G69" s="12">
-        <f t="shared" ref="G69" si="16">ROUND((F69 - E69) / E69 * 100, 2)</f>
-        <v>-2.34</v>
+        <f t="shared" ref="G69" si="18">ROUND((F69 - E69) / E69 * 100, 2)</f>
+        <v>-7.8</v>
       </c>
       <c r="H69" s="13" t="s">
-        <v>747</v>
+        <v>763</v>
       </c>
       <c r="I69" s="13">
         <v>16.399999999999999</v>
@@ -20906,38 +21033,38 @@
     </row>
     <row r="70" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A70" s="12" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B70" s="32" t="s">
-        <v>488</v>
+        <v>776</v>
       </c>
       <c r="C70" s="16">
-        <v>45667</v>
+        <v>45818</v>
       </c>
       <c r="D70" s="32" t="s">
         <v>814</v>
       </c>
       <c r="E70" s="12">
-        <v>14.1</v>
+        <v>27.422000000000001</v>
       </c>
       <c r="F70" s="12">
-        <v>13</v>
+        <v>26.05</v>
       </c>
       <c r="G70" s="12">
-        <f t="shared" ref="G70" si="17">ROUND((F70 - E70) / E70 * 100, 2)</f>
-        <v>-7.8</v>
+        <f t="shared" ref="G70" si="19">ROUND((F70 - E70) / E70 * 100, 2)</f>
+        <v>-5</v>
       </c>
       <c r="H70" s="13" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="I70" s="13">
-        <v>16.399999999999999</v>
+        <v>29.9</v>
       </c>
       <c r="J70" s="37" t="s">
-        <v>774</v>
+        <v>784</v>
       </c>
       <c r="K70" s="13" t="s">
-        <v>788</v>
+        <v>805</v>
       </c>
     </row>
     <row r="71" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
@@ -20945,205 +21072,203 @@
         <v>33</v>
       </c>
       <c r="B71" s="32" t="s">
-        <v>776</v>
-      </c>
-      <c r="C71" s="16">
-        <v>45818</v>
+        <v>718</v>
+      </c>
+      <c r="C71" s="16" t="s">
+        <v>759</v>
       </c>
       <c r="D71" s="32" t="s">
         <v>814</v>
       </c>
       <c r="E71" s="12">
-        <v>27.422000000000001</v>
+        <v>34</v>
       </c>
       <c r="F71" s="12">
-        <v>26.05</v>
+        <v>32.299999999999997</v>
       </c>
       <c r="G71" s="12">
-        <f t="shared" ref="G71" si="18">ROUND((F71 - E71) / E71 * 100, 2)</f>
+        <f t="shared" ref="G71" si="20">ROUND((F71 - E71) / E71 * 100, 2)</f>
         <v>-5</v>
       </c>
       <c r="H71" s="13" t="s">
-        <v>767</v>
+        <v>760</v>
       </c>
       <c r="I71" s="13">
-        <v>29.9</v>
-      </c>
-      <c r="J71" s="37" t="s">
-        <v>784</v>
+        <v>40.6</v>
+      </c>
+      <c r="J71" s="37">
+        <v>-5</v>
       </c>
       <c r="K71" s="13" t="s">
-        <v>805</v>
+        <v>553</v>
       </c>
     </row>
     <row r="72" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A72" s="12" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B72" s="32" t="s">
-        <v>718</v>
+        <v>754</v>
       </c>
       <c r="C72" s="16" t="s">
-        <v>759</v>
+        <v>753</v>
       </c>
       <c r="D72" s="32" t="s">
-        <v>814</v>
+        <v>766</v>
       </c>
       <c r="E72" s="12">
-        <v>34</v>
+        <v>15.061999999999999</v>
       </c>
       <c r="F72" s="12">
-        <v>32.299999999999997</v>
+        <v>14.15</v>
       </c>
       <c r="G72" s="12">
-        <f t="shared" ref="G72" si="19">ROUND((F72 - E72) / E72 * 100, 2)</f>
-        <v>-5</v>
+        <f>ROUND((F72 - E72) / E72 * 100, 2)</f>
+        <v>-6.05</v>
       </c>
       <c r="H72" s="13" t="s">
-        <v>760</v>
-      </c>
-      <c r="I72" s="13">
-        <v>40.6</v>
-      </c>
+        <v>755</v>
+      </c>
+      <c r="I72" s="13"/>
       <c r="J72" s="37">
-        <v>-5</v>
+        <v>14.15</v>
       </c>
       <c r="K72" s="13" t="s">
-        <v>553</v>
+        <v>765</v>
       </c>
     </row>
     <row r="73" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A73" s="12" t="s">
-        <v>12</v>
+        <v>396</v>
       </c>
       <c r="B73" s="32" t="s">
-        <v>754</v>
-      </c>
-      <c r="C73" s="16" t="s">
-        <v>753</v>
-      </c>
-      <c r="D73" s="32" t="s">
-        <v>766</v>
+        <v>488</v>
+      </c>
+      <c r="C73" s="16">
+        <v>46000</v>
+      </c>
+      <c r="D73" s="16" t="s">
+        <v>759</v>
       </c>
       <c r="E73" s="12">
-        <v>15.061999999999999</v>
+        <v>24.37</v>
       </c>
       <c r="F73" s="12">
-        <v>14.15</v>
+        <v>23.7</v>
       </c>
       <c r="G73" s="12">
-        <f>ROUND((F73 - E73) / E73 * 100, 2)</f>
-        <v>-6.05</v>
+        <f t="shared" ref="G73" si="21">ROUND((F73 - E73) / E73 * 100, 2)</f>
+        <v>-2.75</v>
       </c>
       <c r="H73" s="13" t="s">
-        <v>755</v>
+        <v>688</v>
       </c>
       <c r="I73" s="13"/>
       <c r="J73" s="37">
-        <v>14.15</v>
+        <v>-5</v>
       </c>
       <c r="K73" s="13" t="s">
-        <v>765</v>
+        <v>752</v>
+      </c>
+      <c r="L73" s="12" t="s">
+        <v>694</v>
       </c>
     </row>
     <row r="74" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A74" s="12" t="s">
-        <v>396</v>
+        <v>736</v>
       </c>
       <c r="B74" s="32" t="s">
-        <v>488</v>
-      </c>
-      <c r="C74" s="16">
-        <v>46000</v>
+        <v>528</v>
+      </c>
+      <c r="C74" s="16" t="s">
+        <v>700</v>
       </c>
       <c r="D74" s="16" t="s">
         <v>759</v>
       </c>
       <c r="E74" s="12">
-        <v>24.37</v>
+        <v>81.5</v>
       </c>
       <c r="F74" s="12">
-        <v>23.7</v>
+        <v>79</v>
       </c>
       <c r="G74" s="12">
-        <f t="shared" ref="G74" si="20">ROUND((F74 - E74) / E74 * 100, 2)</f>
-        <v>-2.75</v>
+        <f t="shared" ref="G74:G80" si="22">ROUND((F74 - E74) / E74 * 100, 2)</f>
+        <v>-3.07</v>
       </c>
       <c r="H74" s="13" t="s">
-        <v>688</v>
-      </c>
-      <c r="I74" s="13"/>
-      <c r="J74" s="37">
-        <v>-5</v>
+        <v>685</v>
+      </c>
+      <c r="I74" s="13">
+        <v>87.7</v>
+      </c>
+      <c r="J74" s="37" t="s">
+        <v>740</v>
       </c>
       <c r="K74" s="13" t="s">
-        <v>752</v>
-      </c>
-      <c r="L74" s="12" t="s">
-        <v>694</v>
+        <v>746</v>
       </c>
     </row>
     <row r="75" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A75" s="12" t="s">
-        <v>736</v>
+        <v>10</v>
       </c>
       <c r="B75" s="32" t="s">
-        <v>528</v>
+        <v>731</v>
       </c>
       <c r="C75" s="16" t="s">
-        <v>700</v>
+        <v>744</v>
       </c>
       <c r="D75" s="16" t="s">
         <v>759</v>
       </c>
       <c r="E75" s="12">
-        <v>81.5</v>
+        <v>60.15</v>
       </c>
       <c r="F75" s="12">
-        <v>79</v>
+        <v>57.1</v>
       </c>
       <c r="G75" s="12">
-        <f t="shared" ref="G75:G81" si="21">ROUND((F75 - E75) / E75 * 100, 2)</f>
-        <v>-3.07</v>
+        <f t="shared" si="22"/>
+        <v>-5.07</v>
       </c>
       <c r="H75" s="13" t="s">
-        <v>685</v>
-      </c>
-      <c r="I75" s="13">
-        <v>87.7</v>
-      </c>
-      <c r="J75" s="37" t="s">
-        <v>740</v>
+        <v>748</v>
+      </c>
+      <c r="I75" s="13"/>
+      <c r="J75" s="37">
+        <v>-5</v>
       </c>
       <c r="K75" s="13" t="s">
-        <v>746</v>
+        <v>752</v>
       </c>
     </row>
     <row r="76" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A76" s="12" t="s">
-        <v>10</v>
+        <v>704</v>
       </c>
       <c r="B76" s="32" t="s">
-        <v>731</v>
+        <v>737</v>
       </c>
       <c r="C76" s="16" t="s">
-        <v>744</v>
+        <v>738</v>
       </c>
       <c r="D76" s="16" t="s">
         <v>759</v>
       </c>
       <c r="E76" s="12">
-        <v>60.15</v>
+        <v>24.3</v>
       </c>
       <c r="F76" s="12">
-        <v>57.1</v>
+        <v>23.1</v>
       </c>
       <c r="G76" s="12">
-        <f t="shared" si="21"/>
-        <v>-5.07</v>
+        <f t="shared" si="22"/>
+        <v>-4.9400000000000004</v>
       </c>
       <c r="H76" s="13" t="s">
-        <v>748</v>
+        <v>734</v>
       </c>
       <c r="I76" s="13"/>
       <c r="J76" s="37">
@@ -21155,67 +21280,67 @@
     </row>
     <row r="77" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A77" s="12" t="s">
-        <v>704</v>
+        <v>743</v>
       </c>
       <c r="B77" s="32" t="s">
-        <v>737</v>
+        <v>587</v>
       </c>
       <c r="C77" s="16" t="s">
-        <v>738</v>
+        <v>716</v>
       </c>
       <c r="D77" s="16" t="s">
-        <v>759</v>
+        <v>753</v>
       </c>
       <c r="E77" s="12">
-        <v>24.3</v>
+        <v>105</v>
       </c>
       <c r="F77" s="12">
-        <v>23.1</v>
+        <v>98.6</v>
       </c>
       <c r="G77" s="12">
-        <f t="shared" si="21"/>
-        <v>-4.9400000000000004</v>
+        <f t="shared" si="22"/>
+        <v>-6.1</v>
       </c>
       <c r="H77" s="13" t="s">
-        <v>734</v>
+        <v>717</v>
       </c>
       <c r="I77" s="13"/>
       <c r="J77" s="37">
-        <v>-5</v>
+        <v>97.5</v>
       </c>
       <c r="K77" s="13" t="s">
-        <v>752</v>
+        <v>733</v>
       </c>
     </row>
     <row r="78" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A78" s="12" t="s">
-        <v>743</v>
+        <v>730</v>
       </c>
       <c r="B78" s="32" t="s">
-        <v>587</v>
+        <v>718</v>
       </c>
       <c r="C78" s="16" t="s">
         <v>716</v>
       </c>
       <c r="D78" s="16" t="s">
-        <v>753</v>
+        <v>738</v>
       </c>
       <c r="E78" s="12">
-        <v>105</v>
+        <v>34.35</v>
       </c>
       <c r="F78" s="12">
-        <v>98.6</v>
+        <v>32.700000000000003</v>
       </c>
       <c r="G78" s="12">
-        <f t="shared" si="21"/>
-        <v>-6.1</v>
+        <f t="shared" si="22"/>
+        <v>-4.8</v>
       </c>
       <c r="H78" s="13" t="s">
         <v>717</v>
       </c>
       <c r="I78" s="13"/>
       <c r="J78" s="37">
-        <v>97.5</v>
+        <v>32.15</v>
       </c>
       <c r="K78" s="13" t="s">
         <v>733</v>
@@ -21223,10 +21348,10 @@
     </row>
     <row r="79" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A79" s="12" t="s">
-        <v>730</v>
+        <v>406</v>
       </c>
       <c r="B79" s="32" t="s">
-        <v>718</v>
+        <v>731</v>
       </c>
       <c r="C79" s="16" t="s">
         <v>716</v>
@@ -21235,510 +21360,511 @@
         <v>738</v>
       </c>
       <c r="E79" s="12">
-        <v>34.35</v>
+        <v>61.4</v>
       </c>
       <c r="F79" s="12">
-        <v>32.700000000000003</v>
+        <v>59.4</v>
       </c>
       <c r="G79" s="12">
-        <f t="shared" si="21"/>
-        <v>-4.8</v>
+        <f t="shared" si="22"/>
+        <v>-3.26</v>
       </c>
       <c r="H79" s="13" t="s">
         <v>717</v>
       </c>
       <c r="I79" s="13"/>
       <c r="J79" s="37">
-        <v>32.15</v>
+        <v>58.7</v>
       </c>
       <c r="K79" s="13" t="s">
         <v>733</v>
       </c>
     </row>
-    <row r="80" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:12" s="12" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A80" s="12" t="s">
-        <v>406</v>
+        <v>586</v>
       </c>
       <c r="B80" s="32" t="s">
-        <v>731</v>
-      </c>
-      <c r="C80" s="16" t="s">
-        <v>716</v>
-      </c>
-      <c r="D80" s="16" t="s">
-        <v>738</v>
-      </c>
+        <v>686</v>
+      </c>
+      <c r="C80" s="16">
+        <v>45970</v>
+      </c>
+      <c r="D80" s="32"/>
       <c r="E80" s="12">
-        <v>61.4</v>
+        <v>43.784999999999997</v>
       </c>
       <c r="F80" s="12">
-        <v>59.4</v>
+        <v>41.6</v>
       </c>
       <c r="G80" s="12">
-        <f t="shared" si="21"/>
-        <v>-3.26</v>
+        <f t="shared" si="22"/>
+        <v>-4.99</v>
       </c>
       <c r="H80" s="13" t="s">
-        <v>717</v>
-      </c>
-      <c r="I80" s="13"/>
+        <v>693</v>
+      </c>
+      <c r="I80" s="13">
+        <v>48.2</v>
+      </c>
       <c r="J80" s="37">
-        <v>58.7</v>
+        <v>-5</v>
       </c>
       <c r="K80" s="13" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="81" spans="1:12" s="12" customFormat="1" ht="36" x14ac:dyDescent="0.3">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A81" s="12" t="s">
-        <v>586</v>
+        <v>612</v>
       </c>
       <c r="B81" s="32" t="s">
-        <v>686</v>
+        <v>489</v>
       </c>
       <c r="C81" s="16">
-        <v>45970</v>
+        <v>46000</v>
       </c>
       <c r="D81" s="32"/>
       <c r="E81" s="12">
-        <v>43.784999999999997</v>
+        <v>24.02</v>
       </c>
       <c r="F81" s="12">
-        <v>41.6</v>
+        <v>22.8</v>
       </c>
       <c r="G81" s="12">
-        <f t="shared" si="21"/>
-        <v>-4.99</v>
+        <f t="shared" ref="G81:G112" si="23">ROUND((F81 - E81) / E81 * 100, 2)</f>
+        <v>-5.08</v>
       </c>
       <c r="H81" s="13" t="s">
-        <v>693</v>
-      </c>
-      <c r="I81" s="13">
-        <v>48.2</v>
-      </c>
+        <v>698</v>
+      </c>
+      <c r="I81" s="13"/>
       <c r="J81" s="37">
         <v>-5</v>
       </c>
       <c r="K81" s="13" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="82" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A82" s="12" t="s">
-        <v>612</v>
+        <v>13</v>
       </c>
       <c r="B82" s="32" t="s">
         <v>489</v>
       </c>
       <c r="C82" s="16">
-        <v>46000</v>
+        <v>45970</v>
       </c>
       <c r="D82" s="32"/>
       <c r="E82" s="12">
-        <v>24.02</v>
+        <v>23.12</v>
       </c>
       <c r="F82" s="12">
-        <v>22.8</v>
+        <v>22.1</v>
       </c>
       <c r="G82" s="12">
-        <f t="shared" ref="G82:G113" si="22">ROUND((F82 - E82) / E82 * 100, 2)</f>
-        <v>-5.08</v>
+        <f t="shared" si="23"/>
+        <v>-4.41</v>
       </c>
       <c r="H82" s="13" t="s">
-        <v>698</v>
-      </c>
-      <c r="I82" s="13"/>
+        <v>688</v>
+      </c>
+      <c r="I82" s="13">
+        <v>25.8</v>
+      </c>
       <c r="J82" s="37">
         <v>-5</v>
       </c>
       <c r="K82" s="13" t="s">
-        <v>720</v>
+        <v>553</v>
       </c>
     </row>
     <row r="83" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A83" s="12" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="B83" s="32" t="s">
-        <v>489</v>
+        <v>505</v>
       </c>
       <c r="C83" s="16">
-        <v>45970</v>
+        <v>45939</v>
       </c>
       <c r="D83" s="32"/>
       <c r="E83" s="12">
-        <v>23.12</v>
+        <v>29.1</v>
       </c>
       <c r="F83" s="12">
-        <v>22.1</v>
+        <v>28.25</v>
       </c>
       <c r="G83" s="12">
-        <f t="shared" si="22"/>
-        <v>-4.41</v>
+        <f t="shared" si="23"/>
+        <v>-2.92</v>
       </c>
       <c r="H83" s="13" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="I83" s="13">
-        <v>25.8</v>
+        <v>31.4</v>
       </c>
       <c r="J83" s="37">
-        <v>-5</v>
+        <v>28.25</v>
       </c>
       <c r="K83" s="13" t="s">
-        <v>553</v>
+        <v>712</v>
       </c>
     </row>
     <row r="84" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A84" s="12" t="s">
-        <v>34</v>
+        <v>687</v>
       </c>
       <c r="B84" s="32" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="C84" s="16">
-        <v>45939</v>
+        <v>45970</v>
       </c>
       <c r="D84" s="32"/>
       <c r="E84" s="12">
-        <v>29.1</v>
+        <v>38.83</v>
       </c>
       <c r="F84" s="12">
-        <v>28.25</v>
+        <v>36.9</v>
       </c>
       <c r="G84" s="12">
-        <f t="shared" si="22"/>
-        <v>-2.92</v>
+        <f t="shared" si="23"/>
+        <v>-4.97</v>
       </c>
       <c r="H84" s="13" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="I84" s="13">
-        <v>31.4</v>
+        <v>42.3</v>
       </c>
       <c r="J84" s="37">
-        <v>28.25</v>
+        <v>-5</v>
       </c>
       <c r="K84" s="13" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="85" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" s="12" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A85" s="12" t="s">
-        <v>687</v>
+        <v>54</v>
       </c>
       <c r="B85" s="32" t="s">
-        <v>510</v>
+        <v>492</v>
       </c>
       <c r="C85" s="16">
-        <v>45970</v>
+        <v>45786</v>
       </c>
       <c r="D85" s="32"/>
       <c r="E85" s="12">
-        <v>38.83</v>
+        <v>28.05</v>
       </c>
       <c r="F85" s="12">
-        <v>36.9</v>
+        <v>25.75</v>
       </c>
       <c r="G85" s="12">
-        <f t="shared" si="22"/>
-        <v>-4.97</v>
+        <f t="shared" si="23"/>
+        <v>-8.1999999999999993</v>
       </c>
       <c r="H85" s="13" t="s">
-        <v>688</v>
-      </c>
-      <c r="I85" s="13">
-        <v>42.3</v>
-      </c>
-      <c r="J85" s="37">
-        <v>-5</v>
-      </c>
+        <v>665</v>
+      </c>
+      <c r="I85" s="13"/>
+      <c r="J85" s="37"/>
       <c r="K85" s="13" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="86" spans="1:12" s="12" customFormat="1" ht="36" x14ac:dyDescent="0.3">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A86" s="12" t="s">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="B86" s="32" t="s">
-        <v>492</v>
-      </c>
-      <c r="C86" s="16">
-        <v>45786</v>
+        <v>489</v>
+      </c>
+      <c r="C86" s="12" t="s">
+        <v>627</v>
       </c>
       <c r="D86" s="32"/>
       <c r="E86" s="12">
-        <v>28.05</v>
+        <v>24.92</v>
       </c>
       <c r="F86" s="12">
-        <v>25.75</v>
+        <v>23.7</v>
       </c>
       <c r="G86" s="12">
-        <f t="shared" si="22"/>
-        <v>-8.1999999999999993</v>
-      </c>
-      <c r="H86" s="13" t="s">
-        <v>665</v>
-      </c>
+        <f t="shared" si="23"/>
+        <v>-4.9000000000000004</v>
+      </c>
+      <c r="H86" s="13"/>
       <c r="I86" s="13"/>
-      <c r="J86" s="37"/>
+      <c r="J86" s="37">
+        <v>-5</v>
+      </c>
       <c r="K86" s="13" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="87" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A87" s="12" t="s">
-        <v>7</v>
+        <v>664</v>
       </c>
       <c r="B87" s="32" t="s">
-        <v>489</v>
+        <v>625</v>
       </c>
       <c r="C87" s="12" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="D87" s="32"/>
       <c r="E87" s="12">
-        <v>24.92</v>
+        <v>50.741</v>
       </c>
       <c r="F87" s="12">
-        <v>23.7</v>
+        <v>50.5</v>
       </c>
       <c r="G87" s="12">
-        <f t="shared" si="22"/>
-        <v>-4.9000000000000004</v>
+        <f t="shared" si="23"/>
+        <v>-0.47</v>
       </c>
       <c r="H87" s="13"/>
-      <c r="I87" s="13"/>
-      <c r="J87" s="37">
-        <v>-5</v>
+      <c r="I87" s="13">
+        <v>58</v>
+      </c>
+      <c r="J87" s="37" t="s">
+        <v>674</v>
       </c>
       <c r="K87" s="13" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="88" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A88" s="12" t="s">
-        <v>664</v>
-      </c>
-      <c r="B88" s="32" t="s">
-        <v>625</v>
-      </c>
-      <c r="C88" s="12" t="s">
-        <v>623</v>
-      </c>
-      <c r="D88" s="32"/>
-      <c r="E88" s="12">
-        <v>50.741</v>
-      </c>
-      <c r="F88" s="12">
-        <v>50.5</v>
-      </c>
-      <c r="G88" s="12">
-        <f t="shared" si="22"/>
-        <v>-0.47</v>
-      </c>
-      <c r="H88" s="13"/>
-      <c r="I88" s="13">
-        <v>58</v>
-      </c>
-      <c r="J88" s="37" t="s">
-        <v>674</v>
-      </c>
-      <c r="K88" s="13" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="89" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.3">
+        <v>629</v>
+      </c>
+      <c r="B88" s="31" t="s">
+        <v>620</v>
+      </c>
+      <c r="C88" s="10" t="s">
+        <v>619</v>
+      </c>
+      <c r="D88" s="31"/>
+      <c r="E88" s="10">
+        <v>26.86</v>
+      </c>
+      <c r="F88" s="10">
+        <v>32.200000000000003</v>
+      </c>
+      <c r="G88" s="10">
+        <f t="shared" si="23"/>
+        <v>19.88</v>
+      </c>
+      <c r="H88" s="7"/>
+      <c r="I88" s="7">
+        <v>38.5</v>
+      </c>
+      <c r="J88" s="38">
+        <v>32.200000000000003</v>
+      </c>
+      <c r="K88" s="7" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" s="10" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A89" s="12" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="B89" s="31" t="s">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="C89" s="10" t="s">
-        <v>619</v>
+        <v>627</v>
       </c>
       <c r="D89" s="31"/>
       <c r="E89" s="10">
-        <v>26.86</v>
+        <v>23.27</v>
       </c>
       <c r="F89" s="10">
-        <v>32.200000000000003</v>
+        <v>25</v>
       </c>
       <c r="G89" s="10">
-        <f t="shared" si="22"/>
-        <v>19.88</v>
+        <f t="shared" si="23"/>
+        <v>7.43</v>
       </c>
       <c r="H89" s="7"/>
-      <c r="I89" s="7">
-        <v>38.5</v>
-      </c>
+      <c r="I89" s="7"/>
       <c r="J89" s="38">
-        <v>32.200000000000003</v>
+        <v>25</v>
       </c>
       <c r="K89" s="7" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="90" spans="1:12" s="10" customFormat="1" ht="36" x14ac:dyDescent="0.3">
-      <c r="A90" s="12" t="s">
-        <v>624</v>
-      </c>
-      <c r="B90" s="31" t="s">
-        <v>628</v>
-      </c>
-      <c r="C90" s="10" t="s">
-        <v>627</v>
-      </c>
-      <c r="D90" s="31"/>
-      <c r="E90" s="10">
-        <v>23.27</v>
-      </c>
-      <c r="F90" s="10">
-        <v>25</v>
-      </c>
-      <c r="G90" s="10">
-        <f t="shared" si="22"/>
-        <v>7.43</v>
-      </c>
-      <c r="H90" s="7"/>
-      <c r="I90" s="7"/>
-      <c r="J90" s="38">
-        <v>25</v>
-      </c>
-      <c r="K90" s="7" t="s">
         <v>671</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B90" s="32" t="s">
+        <v>607</v>
+      </c>
+      <c r="C90" s="16" t="s">
+        <v>605</v>
+      </c>
+      <c r="D90" s="32"/>
+      <c r="E90" s="12">
+        <v>16.263000000000002</v>
+      </c>
+      <c r="F90" s="12">
+        <v>16.149999999999999</v>
+      </c>
+      <c r="G90" s="12">
+        <f t="shared" si="23"/>
+        <v>-0.69</v>
+      </c>
+      <c r="H90" s="13"/>
+      <c r="I90" s="13"/>
+      <c r="J90" s="37" t="s">
+        <v>661</v>
+      </c>
+      <c r="K90" s="13" t="s">
+        <v>635</v>
       </c>
     </row>
     <row r="91" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A91" s="10" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="B91" s="32" t="s">
-        <v>607</v>
-      </c>
-      <c r="C91" s="16" t="s">
-        <v>605</v>
+        <v>510</v>
+      </c>
+      <c r="C91" s="12" t="s">
+        <v>623</v>
       </c>
       <c r="D91" s="32"/>
       <c r="E91" s="12">
-        <v>16.263000000000002</v>
+        <v>39</v>
       </c>
       <c r="F91" s="12">
-        <v>16.149999999999999</v>
+        <v>39</v>
       </c>
       <c r="G91" s="12">
-        <f t="shared" si="22"/>
-        <v>-0.69</v>
+        <f t="shared" si="23"/>
+        <v>0</v>
       </c>
       <c r="H91" s="13"/>
-      <c r="I91" s="13"/>
+      <c r="I91" s="13">
+        <v>45</v>
+      </c>
       <c r="J91" s="37" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="K91" s="13" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="92" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="10" t="s">
-        <v>10</v>
+      <c r="A92" s="12" t="s">
+        <v>606</v>
       </c>
       <c r="B92" s="32" t="s">
-        <v>510</v>
+        <v>625</v>
       </c>
       <c r="C92" s="12" t="s">
-        <v>623</v>
+        <v>634</v>
       </c>
       <c r="D92" s="32"/>
       <c r="E92" s="12">
-        <v>39</v>
+        <v>40.9</v>
       </c>
       <c r="F92" s="12">
-        <v>39</v>
+        <v>38.9</v>
       </c>
       <c r="G92" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
+        <f t="shared" si="23"/>
+        <v>-4.8899999999999997</v>
       </c>
       <c r="H92" s="13"/>
-      <c r="I92" s="13">
-        <v>45</v>
-      </c>
-      <c r="J92" s="37" t="s">
-        <v>662</v>
+      <c r="I92" s="13"/>
+      <c r="J92" s="37">
+        <v>-5</v>
       </c>
       <c r="K92" s="13" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="93" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A93" s="12" t="s">
-        <v>606</v>
-      </c>
-      <c r="B93" s="32" t="s">
-        <v>625</v>
-      </c>
-      <c r="C93" s="12" t="s">
-        <v>634</v>
-      </c>
-      <c r="D93" s="32"/>
-      <c r="E93" s="12">
-        <v>40.9</v>
-      </c>
-      <c r="F93" s="12">
-        <v>38.9</v>
-      </c>
-      <c r="G93" s="12">
-        <f t="shared" si="22"/>
-        <v>-4.8899999999999997</v>
-      </c>
-      <c r="H93" s="13"/>
-      <c r="I93" s="13"/>
-      <c r="J93" s="37">
+        <v>396</v>
+      </c>
+      <c r="B93" s="31" t="s">
+        <v>528</v>
+      </c>
+      <c r="C93" s="10" t="s">
+        <v>619</v>
+      </c>
+      <c r="D93" s="31"/>
+      <c r="E93" s="10">
+        <v>62</v>
+      </c>
+      <c r="F93" s="10">
+        <v>62.5</v>
+      </c>
+      <c r="G93" s="10">
+        <f t="shared" si="23"/>
+        <v>0.81</v>
+      </c>
+      <c r="H93" s="7"/>
+      <c r="I93" s="7"/>
+      <c r="J93" s="38">
         <v>-5</v>
       </c>
-      <c r="K93" s="13" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="94" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="K93" s="7" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A94" s="12" t="s">
-        <v>396</v>
-      </c>
-      <c r="B94" s="31" t="s">
-        <v>528</v>
-      </c>
-      <c r="C94" s="10" t="s">
-        <v>619</v>
-      </c>
-      <c r="D94" s="31"/>
-      <c r="E94" s="10">
-        <v>62</v>
-      </c>
-      <c r="F94" s="10">
-        <v>62.5</v>
-      </c>
-      <c r="G94" s="10">
-        <f t="shared" si="22"/>
-        <v>0.81</v>
-      </c>
-      <c r="H94" s="7"/>
-      <c r="I94" s="7"/>
-      <c r="J94" s="38">
-        <v>-5</v>
-      </c>
-      <c r="K94" s="7" t="s">
-        <v>631</v>
+        <v>30</v>
+      </c>
+      <c r="B94" s="32" t="s">
+        <v>620</v>
+      </c>
+      <c r="C94" s="12" t="s">
+        <v>610</v>
+      </c>
+      <c r="D94" s="32"/>
+      <c r="E94" s="12">
+        <v>23.22</v>
+      </c>
+      <c r="F94" s="12">
+        <v>21.85</v>
+      </c>
+      <c r="G94" s="12">
+        <f t="shared" si="23"/>
+        <v>-5.9</v>
+      </c>
+      <c r="H94" s="13"/>
+      <c r="I94" s="13">
+        <v>30.5</v>
+      </c>
+      <c r="J94" s="37">
+        <v>22.4</v>
+      </c>
+      <c r="K94" s="13" t="s">
+        <v>615</v>
+      </c>
+      <c r="L94" s="12" t="s">
+        <v>618</v>
       </c>
     </row>
     <row r="95" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="12" t="s">
-        <v>30</v>
+      <c r="A95" s="10" t="s">
+        <v>612</v>
       </c>
       <c r="B95" s="32" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C95" s="12" t="s">
         <v>610</v>
@@ -21748,11 +21874,11 @@
         <v>23.22</v>
       </c>
       <c r="F95" s="12">
-        <v>21.85</v>
+        <v>22.4</v>
       </c>
       <c r="G95" s="12">
-        <f t="shared" si="22"/>
-        <v>-5.9</v>
+        <f t="shared" si="23"/>
+        <v>-3.53</v>
       </c>
       <c r="H95" s="13"/>
       <c r="I95" s="13">
@@ -21769,1942 +21895,1907 @@
       </c>
     </row>
     <row r="96" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="10" t="s">
-        <v>612</v>
+      <c r="A96" s="12" t="s">
+        <v>10</v>
       </c>
       <c r="B96" s="32" t="s">
-        <v>621</v>
-      </c>
-      <c r="C96" s="12" t="s">
-        <v>610</v>
+        <v>580</v>
+      </c>
+      <c r="C96" s="16">
+        <v>45755</v>
       </c>
       <c r="D96" s="32"/>
       <c r="E96" s="12">
-        <v>23.22</v>
+        <v>8.0359999999999996</v>
       </c>
       <c r="F96" s="12">
-        <v>22.4</v>
+        <v>7.6</v>
       </c>
       <c r="G96" s="12">
-        <f t="shared" si="22"/>
-        <v>-3.53</v>
+        <f t="shared" si="23"/>
+        <v>-5.43</v>
       </c>
       <c r="H96" s="13"/>
       <c r="I96" s="13">
-        <v>30.5</v>
+        <v>9.5</v>
       </c>
       <c r="J96" s="37">
-        <v>22.4</v>
+        <v>-5</v>
       </c>
       <c r="K96" s="13" t="s">
-        <v>615</v>
-      </c>
-      <c r="L96" s="12" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="97" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A97" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B97" s="32" t="s">
-        <v>580</v>
-      </c>
-      <c r="C97" s="16">
-        <v>45755</v>
-      </c>
-      <c r="D97" s="32"/>
-      <c r="E97" s="12">
-        <v>8.0359999999999996</v>
-      </c>
-      <c r="F97" s="12">
-        <v>7.6</v>
-      </c>
-      <c r="G97" s="12">
-        <f t="shared" si="22"/>
-        <v>-5.43</v>
-      </c>
-      <c r="H97" s="13"/>
-      <c r="I97" s="13">
-        <v>9.5</v>
-      </c>
-      <c r="J97" s="37">
-        <v>-5</v>
-      </c>
-      <c r="K97" s="13" t="s">
-        <v>611</v>
+      <c r="B97" s="31" t="s">
+        <v>529</v>
+      </c>
+      <c r="C97" s="10" t="s">
+        <v>519</v>
+      </c>
+      <c r="D97" s="31"/>
+      <c r="E97" s="10">
+        <v>11.573</v>
+      </c>
+      <c r="F97" s="10">
+        <v>15.2</v>
+      </c>
+      <c r="G97" s="10">
+        <f t="shared" si="23"/>
+        <v>31.34</v>
+      </c>
+      <c r="H97" s="7"/>
+      <c r="I97" s="7">
+        <v>15.2</v>
+      </c>
+      <c r="J97" s="38">
+        <v>12.3</v>
+      </c>
+      <c r="K97" s="7" t="s">
+        <v>609</v>
+      </c>
+      <c r="L97" s="10" t="s">
+        <v>562</v>
       </c>
     </row>
     <row r="98" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A98" s="12" t="s">
-        <v>10</v>
+        <v>550</v>
       </c>
       <c r="B98" s="31" t="s">
-        <v>529</v>
-      </c>
-      <c r="C98" s="10" t="s">
+        <v>520</v>
+      </c>
+      <c r="C98" s="15" t="s">
         <v>519</v>
       </c>
       <c r="D98" s="31"/>
       <c r="E98" s="10">
-        <v>11.573</v>
+        <v>11.464</v>
       </c>
       <c r="F98" s="10">
-        <v>15.2</v>
+        <v>14.75</v>
       </c>
       <c r="G98" s="10">
-        <f t="shared" si="22"/>
-        <v>31.34</v>
+        <f t="shared" si="23"/>
+        <v>28.66</v>
       </c>
       <c r="H98" s="7"/>
       <c r="I98" s="7">
-        <v>15.2</v>
-      </c>
-      <c r="J98" s="38">
-        <v>12.3</v>
+        <v>17.55</v>
+      </c>
+      <c r="J98" s="38" t="s">
+        <v>592</v>
       </c>
       <c r="K98" s="7" t="s">
-        <v>609</v>
-      </c>
-      <c r="L98" s="10" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="99" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="12" t="s">
-        <v>550</v>
-      </c>
-      <c r="B99" s="31" t="s">
-        <v>520</v>
-      </c>
-      <c r="C99" s="15" t="s">
-        <v>519</v>
-      </c>
-      <c r="D99" s="31"/>
-      <c r="E99" s="10">
-        <v>11.464</v>
-      </c>
-      <c r="F99" s="10">
-        <v>14.75</v>
-      </c>
-      <c r="G99" s="10">
-        <f t="shared" si="22"/>
-        <v>28.66</v>
-      </c>
-      <c r="H99" s="7"/>
-      <c r="I99" s="7">
-        <v>17.55</v>
-      </c>
-      <c r="J99" s="38" t="s">
-        <v>592</v>
-      </c>
-      <c r="K99" s="7" t="s">
         <v>590</v>
       </c>
     </row>
-    <row r="100" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B99" s="32" t="s">
+        <v>587</v>
+      </c>
+      <c r="C99" s="16">
+        <v>45999</v>
+      </c>
+      <c r="D99" s="32"/>
+      <c r="E99" s="12">
+        <v>37.18</v>
+      </c>
+      <c r="F99" s="12">
+        <v>35.299999999999997</v>
+      </c>
+      <c r="G99" s="12">
+        <f t="shared" si="23"/>
+        <v>-5.0599999999999996</v>
+      </c>
+      <c r="H99" s="13"/>
+      <c r="I99" s="13"/>
+      <c r="J99" s="37">
+        <v>-5</v>
+      </c>
+      <c r="K99" s="13" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A100" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="B100" s="32" t="s">
-        <v>587</v>
-      </c>
-      <c r="C100" s="16">
-        <v>45999</v>
-      </c>
-      <c r="D100" s="32"/>
-      <c r="E100" s="12">
-        <v>37.18</v>
-      </c>
-      <c r="F100" s="12">
-        <v>35.299999999999997</v>
-      </c>
-      <c r="G100" s="12">
-        <f t="shared" si="22"/>
-        <v>-5.0599999999999996</v>
-      </c>
-      <c r="H100" s="13"/>
-      <c r="I100" s="13"/>
-      <c r="J100" s="37">
-        <v>-5</v>
-      </c>
-      <c r="K100" s="13" t="s">
-        <v>594</v>
+        <v>33</v>
+      </c>
+      <c r="B100" s="31" t="s">
+        <v>493</v>
+      </c>
+      <c r="C100" s="15" t="s">
+        <v>458</v>
+      </c>
+      <c r="D100" s="31"/>
+      <c r="E100" s="10">
+        <v>18.5</v>
+      </c>
+      <c r="F100" s="10">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="G100" s="10">
+        <f t="shared" si="23"/>
+        <v>7.57</v>
+      </c>
+      <c r="H100" s="7"/>
+      <c r="I100" s="7">
+        <v>32</v>
+      </c>
+      <c r="J100" s="38" t="s">
+        <v>597</v>
+      </c>
+      <c r="K100" s="7" t="s">
+        <v>598</v>
       </c>
     </row>
     <row r="101" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="10" t="s">
-        <v>33</v>
+      <c r="A101" s="12" t="s">
+        <v>586</v>
       </c>
       <c r="B101" s="31" t="s">
-        <v>493</v>
-      </c>
-      <c r="C101" s="15" t="s">
-        <v>458</v>
+        <v>533</v>
+      </c>
+      <c r="C101" s="15">
+        <v>45785</v>
       </c>
       <c r="D101" s="31"/>
       <c r="E101" s="10">
-        <v>18.5</v>
+        <v>27.071999999999999</v>
       </c>
       <c r="F101" s="10">
-        <v>19.899999999999999</v>
+        <v>29</v>
       </c>
       <c r="G101" s="10">
-        <f t="shared" si="22"/>
-        <v>7.57</v>
+        <f t="shared" si="23"/>
+        <v>7.12</v>
       </c>
       <c r="H101" s="7"/>
       <c r="I101" s="7">
-        <v>32</v>
-      </c>
-      <c r="J101" s="38" t="s">
-        <v>597</v>
+        <v>29</v>
+      </c>
+      <c r="J101" s="38">
+        <v>-5</v>
       </c>
       <c r="K101" s="7" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="102" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="12" t="s">
-        <v>586</v>
-      </c>
-      <c r="B102" s="31" t="s">
-        <v>533</v>
-      </c>
-      <c r="C102" s="15">
-        <v>45785</v>
-      </c>
-      <c r="D102" s="31"/>
-      <c r="E102" s="10">
-        <v>27.071999999999999</v>
-      </c>
-      <c r="F102" s="10">
-        <v>29</v>
-      </c>
-      <c r="G102" s="10">
-        <f t="shared" si="22"/>
-        <v>7.12</v>
-      </c>
-      <c r="H102" s="7"/>
-      <c r="I102" s="7">
-        <v>29</v>
-      </c>
-      <c r="J102" s="38">
-        <v>-5</v>
-      </c>
-      <c r="K102" s="7" t="s">
         <v>576</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="10" t="s">
+        <v>460</v>
+      </c>
+      <c r="B102" s="32" t="s">
+        <v>510</v>
+      </c>
+      <c r="C102" s="12" t="s">
+        <v>549</v>
+      </c>
+      <c r="D102" s="32"/>
+      <c r="E102" s="12">
+        <v>44</v>
+      </c>
+      <c r="F102" s="12">
+        <v>40.5</v>
+      </c>
+      <c r="G102" s="12">
+        <f t="shared" si="23"/>
+        <v>-7.95</v>
+      </c>
+      <c r="H102" s="13"/>
+      <c r="I102" s="13"/>
+      <c r="J102" s="37">
+        <v>40.5</v>
+      </c>
+      <c r="K102" s="13" t="s">
+        <v>567</v>
       </c>
     </row>
     <row r="103" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A103" s="10" t="s">
-        <v>460</v>
+        <v>572</v>
       </c>
       <c r="B103" s="32" t="s">
-        <v>510</v>
+        <v>545</v>
       </c>
       <c r="C103" s="12" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="D103" s="32"/>
       <c r="E103" s="12">
-        <v>44</v>
+        <v>77.400000000000006</v>
       </c>
       <c r="F103" s="12">
-        <v>40.5</v>
+        <v>72.5</v>
       </c>
       <c r="G103" s="12">
-        <f t="shared" si="22"/>
-        <v>-7.95</v>
+        <f t="shared" si="23"/>
+        <v>-6.33</v>
       </c>
       <c r="H103" s="13"/>
       <c r="I103" s="13"/>
       <c r="J103" s="37">
-        <v>40.5</v>
+        <v>72.5</v>
       </c>
       <c r="K103" s="13" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="104" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="10" t="s">
-        <v>572</v>
-      </c>
-      <c r="B104" s="32" t="s">
-        <v>545</v>
-      </c>
-      <c r="C104" s="12" t="s">
-        <v>544</v>
-      </c>
-      <c r="D104" s="32"/>
-      <c r="E104" s="12">
-        <v>77.400000000000006</v>
-      </c>
-      <c r="F104" s="12">
-        <v>72.5</v>
-      </c>
-      <c r="G104" s="12">
-        <f t="shared" si="22"/>
-        <v>-6.33</v>
-      </c>
-      <c r="H104" s="13"/>
-      <c r="I104" s="13"/>
-      <c r="J104" s="37">
-        <v>72.5</v>
-      </c>
-      <c r="K104" s="13" t="s">
         <v>556</v>
       </c>
     </row>
-    <row r="105" spans="1:12" s="10" customFormat="1" ht="36" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:12" s="10" customFormat="1" ht="36" x14ac:dyDescent="0.3">
+      <c r="A104" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B104" s="31" t="s">
+        <v>492</v>
+      </c>
+      <c r="C104" s="15" t="s">
+        <v>453</v>
+      </c>
+      <c r="D104" s="31"/>
+      <c r="E104" s="10">
+        <v>102.35</v>
+      </c>
+      <c r="F104" s="10">
+        <v>105.8</v>
+      </c>
+      <c r="G104" s="10">
+        <f t="shared" si="23"/>
+        <v>3.37</v>
+      </c>
+      <c r="H104" s="7"/>
+      <c r="I104" s="7"/>
+      <c r="J104" s="38">
+        <v>104</v>
+      </c>
+      <c r="K104" s="7" t="s">
+        <v>552</v>
+      </c>
+      <c r="L104" s="7" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A105" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="B105" s="31" t="s">
-        <v>492</v>
-      </c>
-      <c r="C105" s="15" t="s">
-        <v>453</v>
-      </c>
-      <c r="D105" s="31"/>
-      <c r="E105" s="10">
-        <v>102.35</v>
-      </c>
-      <c r="F105" s="10">
-        <v>105.8</v>
-      </c>
-      <c r="G105" s="10">
-        <f t="shared" si="22"/>
-        <v>3.37</v>
-      </c>
-      <c r="H105" s="7"/>
-      <c r="I105" s="7"/>
-      <c r="J105" s="38">
-        <v>104</v>
-      </c>
-      <c r="K105" s="7" t="s">
-        <v>552</v>
-      </c>
-      <c r="L105" s="7" t="s">
-        <v>555</v>
+        <v>464</v>
+      </c>
+      <c r="B105" s="32" t="s">
+        <v>533</v>
+      </c>
+      <c r="C105" s="12" t="s">
+        <v>532</v>
+      </c>
+      <c r="D105" s="32"/>
+      <c r="E105" s="12">
+        <v>80</v>
+      </c>
+      <c r="F105" s="12">
+        <v>71</v>
+      </c>
+      <c r="G105" s="12">
+        <f t="shared" si="23"/>
+        <v>-11.25</v>
+      </c>
+      <c r="H105" s="13"/>
+      <c r="I105" s="13"/>
+      <c r="J105" s="37">
+        <v>71</v>
+      </c>
+      <c r="K105" s="13" t="s">
+        <v>554</v>
+      </c>
+      <c r="L105" s="12" t="s">
+        <v>559</v>
       </c>
     </row>
     <row r="106" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="12" t="s">
-        <v>464</v>
+      <c r="A106" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="B106" s="32" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="C106" s="12" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="D106" s="32"/>
       <c r="E106" s="12">
-        <v>80</v>
+        <v>39.731999999999999</v>
       </c>
       <c r="F106" s="12">
-        <v>71</v>
+        <v>37.700000000000003</v>
       </c>
       <c r="G106" s="12">
-        <f t="shared" si="22"/>
-        <v>-11.25</v>
+        <f t="shared" si="23"/>
+        <v>-5.1100000000000003</v>
       </c>
       <c r="H106" s="13"/>
       <c r="I106" s="13"/>
       <c r="J106" s="37">
-        <v>71</v>
+        <v>-5</v>
       </c>
       <c r="K106" s="13" t="s">
-        <v>554</v>
-      </c>
-      <c r="L106" s="12" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="107" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="10" t="s">
-        <v>19</v>
+        <v>553</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12" s="12" customFormat="1" ht="36" x14ac:dyDescent="0.3">
+      <c r="A107" s="12" t="s">
+        <v>531</v>
       </c>
       <c r="B107" s="32" t="s">
-        <v>528</v>
+        <v>492</v>
       </c>
       <c r="C107" s="12" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="D107" s="32"/>
       <c r="E107" s="12">
-        <v>39.731999999999999</v>
+        <v>128.1</v>
       </c>
       <c r="F107" s="12">
-        <v>37.700000000000003</v>
+        <v>119</v>
       </c>
       <c r="G107" s="12">
-        <f t="shared" si="22"/>
-        <v>-5.1100000000000003</v>
+        <f t="shared" si="23"/>
+        <v>-7.1</v>
       </c>
       <c r="H107" s="13"/>
       <c r="I107" s="13"/>
       <c r="J107" s="37">
-        <v>-5</v>
+        <v>119</v>
       </c>
       <c r="K107" s="13" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="108" spans="1:12" s="12" customFormat="1" ht="36" x14ac:dyDescent="0.3">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A108" s="12" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="B108" s="32" t="s">
-        <v>492</v>
-      </c>
-      <c r="C108" s="12" t="s">
-        <v>519</v>
+        <v>505</v>
+      </c>
+      <c r="C108" s="16">
+        <v>45937</v>
       </c>
       <c r="D108" s="32"/>
       <c r="E108" s="12">
-        <v>128.1</v>
+        <v>20.77</v>
       </c>
       <c r="F108" s="12">
-        <v>119</v>
+        <v>20.55</v>
       </c>
       <c r="G108" s="12">
-        <f t="shared" si="22"/>
-        <v>-7.1</v>
-      </c>
-      <c r="H108" s="13"/>
-      <c r="I108" s="13"/>
+        <f t="shared" si="23"/>
+        <v>-1.06</v>
+      </c>
+      <c r="H108" s="13" t="s">
+        <v>518</v>
+      </c>
+      <c r="I108" s="13">
+        <v>22.25</v>
+      </c>
       <c r="J108" s="37">
-        <v>119</v>
+        <v>-5</v>
       </c>
       <c r="K108" s="13" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="109" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
+        <v>482</v>
+      </c>
+      <c r="L108" s="12" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12" s="10" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A109" s="12" t="s">
-        <v>527</v>
-      </c>
-      <c r="B109" s="32" t="s">
-        <v>505</v>
-      </c>
-      <c r="C109" s="16">
-        <v>45937</v>
-      </c>
-      <c r="D109" s="32"/>
-      <c r="E109" s="12">
-        <v>20.77</v>
-      </c>
-      <c r="F109" s="12">
-        <v>20.55</v>
-      </c>
-      <c r="G109" s="12">
-        <f t="shared" si="22"/>
-        <v>-1.06</v>
-      </c>
-      <c r="H109" s="13" t="s">
-        <v>518</v>
-      </c>
-      <c r="I109" s="13">
-        <v>22.25</v>
-      </c>
-      <c r="J109" s="37">
-        <v>-5</v>
-      </c>
-      <c r="K109" s="13" t="s">
-        <v>482</v>
-      </c>
-      <c r="L109" s="12" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="110" spans="1:12" s="10" customFormat="1" ht="54" x14ac:dyDescent="0.3">
+        <v>406</v>
+      </c>
+      <c r="B109" s="31">
+        <v>4200</v>
+      </c>
+      <c r="C109" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="D109" s="31"/>
+      <c r="E109" s="10">
+        <v>15.4</v>
+      </c>
+      <c r="F109" s="10">
+        <v>20</v>
+      </c>
+      <c r="G109" s="10">
+        <f t="shared" si="23"/>
+        <v>29.87</v>
+      </c>
+      <c r="H109" s="7" t="s">
+        <v>516</v>
+      </c>
+      <c r="I109" s="7">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="J109" s="38" t="s">
+        <v>522</v>
+      </c>
+      <c r="K109" s="7" t="s">
+        <v>524</v>
+      </c>
+      <c r="L109" s="7" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A110" s="12" t="s">
-        <v>406</v>
-      </c>
-      <c r="B110" s="31">
-        <v>4200</v>
-      </c>
-      <c r="C110" s="15" t="s">
-        <v>115</v>
+        <v>34</v>
+      </c>
+      <c r="B110" s="31" t="s">
+        <v>489</v>
+      </c>
+      <c r="C110" s="15">
+        <v>45967</v>
       </c>
       <c r="D110" s="31"/>
       <c r="E110" s="10">
-        <v>15.4</v>
+        <v>15.871</v>
       </c>
       <c r="F110" s="10">
-        <v>20</v>
+        <v>18.8</v>
       </c>
       <c r="G110" s="10">
-        <f t="shared" si="22"/>
-        <v>29.87</v>
-      </c>
-      <c r="H110" s="7" t="s">
-        <v>516</v>
-      </c>
+        <f t="shared" si="23"/>
+        <v>18.46</v>
+      </c>
+      <c r="H110" s="7"/>
       <c r="I110" s="7">
-        <v>19.899999999999999</v>
-      </c>
-      <c r="J110" s="38" t="s">
-        <v>522</v>
+        <v>18.8</v>
+      </c>
+      <c r="J110" s="38">
+        <v>16.649999999999999</v>
       </c>
       <c r="K110" s="7" t="s">
-        <v>524</v>
-      </c>
-      <c r="L110" s="7" t="s">
-        <v>457</v>
+        <v>480</v>
       </c>
     </row>
     <row r="111" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="12" t="s">
-        <v>34</v>
+      <c r="A111" s="10" t="s">
+        <v>10</v>
       </c>
       <c r="B111" s="31" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C111" s="15">
         <v>45967</v>
       </c>
       <c r="D111" s="31"/>
       <c r="E111" s="10">
-        <v>15.871</v>
+        <v>14.074999999999999</v>
       </c>
       <c r="F111" s="10">
-        <v>18.8</v>
+        <v>15</v>
       </c>
       <c r="G111" s="10">
-        <f t="shared" si="22"/>
-        <v>18.46</v>
+        <f t="shared" si="23"/>
+        <v>6.57</v>
       </c>
       <c r="H111" s="7"/>
       <c r="I111" s="7">
-        <v>18.8</v>
-      </c>
-      <c r="J111" s="38">
-        <v>16.649999999999999</v>
+        <v>17.5</v>
+      </c>
+      <c r="J111" s="38" t="s">
+        <v>513</v>
       </c>
       <c r="K111" s="7" t="s">
-        <v>480</v>
+        <v>507</v>
       </c>
     </row>
     <row r="112" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A112" s="10" t="s">
-        <v>10</v>
+        <v>420</v>
       </c>
       <c r="B112" s="31" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="C112" s="15">
-        <v>45967</v>
+        <v>45997</v>
       </c>
       <c r="D112" s="31"/>
       <c r="E112" s="10">
-        <v>14.074999999999999</v>
+        <v>18.215</v>
       </c>
       <c r="F112" s="10">
-        <v>15</v>
+        <v>20.3</v>
       </c>
       <c r="G112" s="10">
-        <f t="shared" si="22"/>
-        <v>6.57</v>
+        <f t="shared" si="23"/>
+        <v>11.45</v>
       </c>
       <c r="H112" s="7"/>
       <c r="I112" s="7">
-        <v>17.5</v>
+        <v>20.3</v>
       </c>
       <c r="J112" s="38" t="s">
-        <v>513</v>
+        <v>494</v>
       </c>
       <c r="K112" s="7" t="s">
-        <v>507</v>
+        <v>496</v>
       </c>
     </row>
     <row r="113" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A113" s="10" t="s">
-        <v>420</v>
+        <v>1</v>
       </c>
       <c r="B113" s="31" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C113" s="15">
-        <v>45997</v>
+        <v>45936</v>
       </c>
       <c r="D113" s="31"/>
       <c r="E113" s="10">
-        <v>18.215</v>
+        <v>10.909000000000001</v>
       </c>
       <c r="F113" s="10">
-        <v>20.3</v>
+        <v>12.75</v>
       </c>
       <c r="G113" s="10">
-        <f t="shared" si="22"/>
-        <v>11.45</v>
+        <f t="shared" ref="G113:G144" si="24">ROUND((F113 - E113) / E113 * 100, 2)</f>
+        <v>16.88</v>
       </c>
       <c r="H113" s="7"/>
       <c r="I113" s="7">
-        <v>20.3</v>
-      </c>
-      <c r="J113" s="38" t="s">
-        <v>494</v>
+        <v>12.75</v>
+      </c>
+      <c r="J113" s="38">
+        <v>11.6</v>
       </c>
       <c r="K113" s="7" t="s">
-        <v>496</v>
+        <v>481</v>
       </c>
     </row>
     <row r="114" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A114" s="10" t="s">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="B114" s="31" t="s">
-        <v>490</v>
-      </c>
-      <c r="C114" s="15">
-        <v>45936</v>
+        <v>492</v>
+      </c>
+      <c r="C114" s="15" t="s">
+        <v>465</v>
       </c>
       <c r="D114" s="31"/>
       <c r="E114" s="10">
-        <v>10.909000000000001</v>
+        <v>35.979999999999997</v>
       </c>
       <c r="F114" s="10">
-        <v>12.75</v>
+        <v>38.299999999999997</v>
       </c>
       <c r="G114" s="10">
-        <f t="shared" ref="G114:G145" si="23">ROUND((F114 - E114) / E114 * 100, 2)</f>
-        <v>16.88</v>
-      </c>
-      <c r="H114" s="7"/>
+        <f t="shared" si="24"/>
+        <v>6.45</v>
+      </c>
+      <c r="H114" s="7" t="s">
+        <v>498</v>
+      </c>
       <c r="I114" s="7">
-        <v>12.75</v>
-      </c>
-      <c r="J114" s="38">
-        <v>11.6</v>
+        <v>38.299999999999997</v>
+      </c>
+      <c r="J114" s="38" t="s">
+        <v>478</v>
       </c>
       <c r="K114" s="7" t="s">
-        <v>481</v>
+        <v>497</v>
       </c>
     </row>
     <row r="115" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A115" s="10" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="B115" s="31" t="s">
-        <v>492</v>
-      </c>
-      <c r="C115" s="15" t="s">
-        <v>465</v>
+        <v>510</v>
+      </c>
+      <c r="C115" s="15">
+        <v>45936</v>
       </c>
       <c r="D115" s="31"/>
       <c r="E115" s="10">
-        <v>35.979999999999997</v>
+        <v>22.350999999999999</v>
       </c>
       <c r="F115" s="10">
-        <v>38.299999999999997</v>
+        <v>23.4</v>
       </c>
       <c r="G115" s="10">
-        <f t="shared" si="23"/>
-        <v>6.45</v>
-      </c>
-      <c r="H115" s="7" t="s">
-        <v>498</v>
-      </c>
+        <f t="shared" si="24"/>
+        <v>4.6900000000000004</v>
+      </c>
+      <c r="H115" s="7"/>
       <c r="I115" s="7">
-        <v>38.299999999999997</v>
-      </c>
-      <c r="J115" s="38" t="s">
-        <v>478</v>
-      </c>
+        <v>23.4</v>
+      </c>
+      <c r="J115" s="38"/>
       <c r="K115" s="7" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="116" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.3">
+        <v>441</v>
+      </c>
+      <c r="L115" s="10" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A116" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="B116" s="31" t="s">
-        <v>510</v>
-      </c>
-      <c r="C116" s="15">
-        <v>45936</v>
-      </c>
-      <c r="D116" s="31"/>
-      <c r="E116" s="10">
-        <v>22.350999999999999</v>
-      </c>
-      <c r="F116" s="10">
-        <v>23.4</v>
-      </c>
-      <c r="G116" s="10">
-        <f t="shared" si="23"/>
-        <v>4.6900000000000004</v>
-      </c>
-      <c r="H116" s="7"/>
-      <c r="I116" s="7">
-        <v>23.4</v>
-      </c>
-      <c r="J116" s="38"/>
-      <c r="K116" s="7" t="s">
-        <v>441</v>
-      </c>
-      <c r="L116" s="10" t="s">
-        <v>473</v>
+        <v>463</v>
+      </c>
+      <c r="B116" s="32"/>
+      <c r="C116" s="16" t="s">
+        <v>429</v>
+      </c>
+      <c r="D116" s="32"/>
+      <c r="E116" s="12">
+        <v>20.48</v>
+      </c>
+      <c r="F116" s="12">
+        <v>19.95</v>
+      </c>
+      <c r="G116" s="12">
+        <f t="shared" si="24"/>
+        <v>-2.59</v>
+      </c>
+      <c r="H116" s="13"/>
+      <c r="I116" s="13">
+        <v>22.75</v>
+      </c>
+      <c r="J116" s="37">
+        <v>-5</v>
+      </c>
+      <c r="K116" s="13" t="s">
+        <v>461</v>
+      </c>
+      <c r="L116" s="12" t="s">
+        <v>466</v>
       </c>
     </row>
     <row r="117" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A117" s="10" t="s">
-        <v>463</v>
+        <v>422</v>
       </c>
       <c r="B117" s="32"/>
-      <c r="C117" s="16" t="s">
-        <v>429</v>
+      <c r="C117" s="16">
+        <v>45967</v>
       </c>
       <c r="D117" s="32"/>
       <c r="E117" s="12">
-        <v>20.48</v>
+        <v>14.361000000000001</v>
       </c>
       <c r="F117" s="12">
-        <v>19.95</v>
+        <v>14.25</v>
       </c>
       <c r="G117" s="12">
-        <f t="shared" si="23"/>
-        <v>-2.59</v>
+        <f t="shared" si="24"/>
+        <v>-0.77</v>
       </c>
       <c r="H117" s="13"/>
       <c r="I117" s="13">
-        <v>22.75</v>
-      </c>
-      <c r="J117" s="37">
-        <v>-5</v>
+        <v>17</v>
+      </c>
+      <c r="J117" s="37" t="s">
+        <v>456</v>
       </c>
       <c r="K117" s="13" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="L117" s="12" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="118" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="B118" s="32"/>
-      <c r="C118" s="16">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A118" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B118" s="31"/>
+      <c r="C118" s="15">
         <v>45967</v>
       </c>
-      <c r="D118" s="32"/>
-      <c r="E118" s="12">
-        <v>14.361000000000001</v>
-      </c>
-      <c r="F118" s="12">
-        <v>14.25</v>
-      </c>
-      <c r="G118" s="12">
-        <f t="shared" si="23"/>
-        <v>-0.77</v>
-      </c>
-      <c r="H118" s="13"/>
-      <c r="I118" s="13">
-        <v>17</v>
-      </c>
-      <c r="J118" s="37" t="s">
-        <v>456</v>
-      </c>
-      <c r="K118" s="13" t="s">
-        <v>455</v>
-      </c>
-      <c r="L118" s="12" t="s">
-        <v>459</v>
+      <c r="D118" s="31"/>
+      <c r="E118" s="10">
+        <v>34.1</v>
+      </c>
+      <c r="F118" s="10">
+        <v>37.1</v>
+      </c>
+      <c r="G118" s="10">
+        <f t="shared" si="24"/>
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="H118" s="7"/>
+      <c r="I118" s="7">
+        <v>37.1</v>
+      </c>
+      <c r="J118" s="38" t="s">
+        <v>443</v>
+      </c>
+      <c r="K118" s="7" t="s">
+        <v>450</v>
       </c>
     </row>
     <row r="119" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A119" s="12" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B119" s="31"/>
       <c r="C119" s="15">
-        <v>45967</v>
+        <v>45722</v>
       </c>
       <c r="D119" s="31"/>
       <c r="E119" s="10">
-        <v>34.1</v>
+        <v>34.4</v>
       </c>
       <c r="F119" s="10">
-        <v>37.1</v>
+        <v>39.15</v>
       </c>
       <c r="G119" s="10">
-        <f t="shared" si="23"/>
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="H119" s="7"/>
+        <f t="shared" si="24"/>
+        <v>13.81</v>
+      </c>
+      <c r="H119" s="7" t="s">
+        <v>399</v>
+      </c>
       <c r="I119" s="7">
-        <v>37.1</v>
+        <v>38.799999999999997</v>
       </c>
       <c r="J119" s="38" t="s">
-        <v>443</v>
+        <v>415</v>
       </c>
       <c r="K119" s="7" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="120" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="B120" s="31"/>
-      <c r="C120" s="15">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="120" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A120" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B120" s="32"/>
+      <c r="C120" s="16">
         <v>45722</v>
       </c>
-      <c r="D120" s="31"/>
-      <c r="E120" s="10">
-        <v>34.4</v>
-      </c>
-      <c r="F120" s="10">
-        <v>39.15</v>
-      </c>
-      <c r="G120" s="10">
-        <f t="shared" si="23"/>
-        <v>13.81</v>
-      </c>
-      <c r="H120" s="7" t="s">
-        <v>399</v>
-      </c>
-      <c r="I120" s="7">
-        <v>38.799999999999997</v>
-      </c>
-      <c r="J120" s="38" t="s">
-        <v>415</v>
-      </c>
-      <c r="K120" s="7" t="s">
-        <v>419</v>
+      <c r="D120" s="32"/>
+      <c r="E120" s="12">
+        <v>55.844999999999999</v>
+      </c>
+      <c r="F120" s="12">
+        <v>55.1</v>
+      </c>
+      <c r="G120" s="12">
+        <f t="shared" si="24"/>
+        <v>-1.33</v>
+      </c>
+      <c r="H120" s="13"/>
+      <c r="I120" s="13">
+        <v>60.6</v>
+      </c>
+      <c r="J120" s="37" t="s">
+        <v>416</v>
+      </c>
+      <c r="K120" s="13" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="121" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A121" s="10" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B121" s="32"/>
-      <c r="C121" s="16">
-        <v>45722</v>
+      <c r="C121" s="16" t="s">
+        <v>117</v>
       </c>
       <c r="D121" s="32"/>
       <c r="E121" s="12">
-        <v>55.844999999999999</v>
+        <v>14.114000000000001</v>
       </c>
       <c r="F121" s="12">
-        <v>55.1</v>
+        <v>14</v>
       </c>
       <c r="G121" s="12">
-        <f t="shared" si="23"/>
-        <v>-1.33</v>
-      </c>
-      <c r="H121" s="13"/>
+        <f t="shared" si="24"/>
+        <v>-0.81</v>
+      </c>
+      <c r="H121" s="13" t="s">
+        <v>118</v>
+      </c>
       <c r="I121" s="13">
-        <v>60.6</v>
+        <v>16.2</v>
       </c>
       <c r="J121" s="37" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="K121" s="13" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="122" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B122" s="32"/>
-      <c r="C122" s="16" t="s">
-        <v>117</v>
-      </c>
-      <c r="D122" s="32"/>
-      <c r="E122" s="12">
-        <v>14.114000000000001</v>
-      </c>
-      <c r="F122" s="12">
-        <v>14</v>
-      </c>
-      <c r="G122" s="12">
-        <f t="shared" si="23"/>
-        <v>-0.81</v>
-      </c>
-      <c r="H122" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="I122" s="13">
-        <v>16.2</v>
-      </c>
-      <c r="J122" s="37" t="s">
-        <v>417</v>
-      </c>
-      <c r="K122" s="13" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="123" spans="1:12" s="10" customFormat="1" ht="36" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:12" s="10" customFormat="1" ht="36" x14ac:dyDescent="0.3">
+      <c r="A122" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B122" s="31"/>
+      <c r="C122" s="15">
+        <v>45965</v>
+      </c>
+      <c r="D122" s="31"/>
+      <c r="E122" s="10">
+        <v>23.4</v>
+      </c>
+      <c r="F122" s="10">
+        <v>35.15</v>
+      </c>
+      <c r="G122" s="10">
+        <f t="shared" si="24"/>
+        <v>50.21</v>
+      </c>
+      <c r="H122" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="I122" s="7">
+        <v>38.200000000000003</v>
+      </c>
+      <c r="J122" s="38">
+        <v>35.15</v>
+      </c>
+      <c r="K122" s="7" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="123" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A123" s="12" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="B123" s="31"/>
-      <c r="C123" s="15">
-        <v>45965</v>
+      <c r="C123" s="15" t="s">
+        <v>100</v>
       </c>
       <c r="D123" s="31"/>
       <c r="E123" s="10">
-        <v>23.4</v>
+        <v>22</v>
       </c>
       <c r="F123" s="10">
-        <v>35.15</v>
+        <v>25.4</v>
       </c>
       <c r="G123" s="10">
-        <f t="shared" si="23"/>
-        <v>50.21</v>
+        <f t="shared" si="24"/>
+        <v>15.45</v>
       </c>
       <c r="H123" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="I123" s="7">
-        <v>38.200000000000003</v>
+        <v>124</v>
+      </c>
+      <c r="I123" s="7" t="s">
+        <v>395</v>
       </c>
       <c r="J123" s="38">
-        <v>35.15</v>
+        <v>25.4</v>
       </c>
       <c r="K123" s="7" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="124" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="B124" s="31"/>
-      <c r="C124" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="D124" s="31"/>
-      <c r="E124" s="10">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="124" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A124" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="F124" s="10">
-        <v>25.4</v>
-      </c>
-      <c r="G124" s="10">
-        <f t="shared" si="23"/>
-        <v>15.45</v>
-      </c>
-      <c r="H124" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="I124" s="7" t="s">
-        <v>395</v>
-      </c>
-      <c r="J124" s="38">
-        <v>25.4</v>
-      </c>
-      <c r="K124" s="7" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="125" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B124" s="32"/>
+      <c r="C124" s="16">
+        <v>45722</v>
+      </c>
+      <c r="D124" s="32"/>
+      <c r="E124" s="12">
+        <v>28.623000000000001</v>
+      </c>
+      <c r="F124" s="12">
+        <v>27.2</v>
+      </c>
+      <c r="G124" s="12">
+        <f t="shared" si="24"/>
+        <v>-4.97</v>
+      </c>
+      <c r="H124" s="13" t="s">
+        <v>400</v>
+      </c>
+      <c r="I124" s="13">
+        <v>31.1</v>
+      </c>
+      <c r="J124" s="37">
+        <v>-5</v>
+      </c>
+      <c r="K124" s="13" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="125" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A125" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="B125" s="32"/>
-      <c r="C125" s="16">
-        <v>45722</v>
-      </c>
-      <c r="D125" s="32"/>
-      <c r="E125" s="12">
-        <v>28.623000000000001</v>
-      </c>
-      <c r="F125" s="12">
-        <v>27.2</v>
-      </c>
-      <c r="G125" s="12">
-        <f t="shared" si="23"/>
-        <v>-4.97</v>
-      </c>
-      <c r="H125" s="13" t="s">
-        <v>400</v>
-      </c>
-      <c r="I125" s="13">
-        <v>31.1</v>
-      </c>
-      <c r="J125" s="37">
-        <v>-5</v>
-      </c>
-      <c r="K125" s="13" t="s">
-        <v>409</v>
+        <v>7</v>
+      </c>
+      <c r="B125" s="31"/>
+      <c r="C125" s="15">
+        <v>45874</v>
+      </c>
+      <c r="D125" s="31"/>
+      <c r="E125" s="10">
+        <v>12.45</v>
+      </c>
+      <c r="F125" s="10">
+        <v>13.6</v>
+      </c>
+      <c r="G125" s="10">
+        <f t="shared" si="24"/>
+        <v>9.24</v>
+      </c>
+      <c r="H125" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="I125" s="7">
+        <v>13.65</v>
+      </c>
+      <c r="J125" s="38">
+        <v>5</v>
+      </c>
+      <c r="K125" s="7" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="126" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="10" t="s">
-        <v>7</v>
+      <c r="A126" s="12" t="s">
+        <v>396</v>
       </c>
       <c r="B126" s="31"/>
-      <c r="C126" s="15">
-        <v>45874</v>
+      <c r="C126" s="15" t="s">
+        <v>103</v>
       </c>
       <c r="D126" s="31"/>
       <c r="E126" s="10">
-        <v>12.45</v>
+        <v>21.4</v>
       </c>
       <c r="F126" s="10">
-        <v>13.6</v>
+        <v>21.55</v>
       </c>
       <c r="G126" s="10">
-        <f t="shared" si="23"/>
-        <v>9.24</v>
+        <f t="shared" si="24"/>
+        <v>0.7</v>
       </c>
       <c r="H126" s="7" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="I126" s="7">
-        <v>13.65</v>
+        <v>23</v>
       </c>
       <c r="J126" s="38">
         <v>5</v>
       </c>
       <c r="K126" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="127" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="12" t="s">
-        <v>396</v>
-      </c>
-      <c r="B127" s="31"/>
-      <c r="C127" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="D127" s="31"/>
-      <c r="E127" s="10">
-        <v>21.4</v>
-      </c>
-      <c r="F127" s="10">
-        <v>21.55</v>
-      </c>
-      <c r="G127" s="10">
-        <f t="shared" si="23"/>
-        <v>0.7</v>
-      </c>
-      <c r="H127" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="I127" s="7">
-        <v>23</v>
-      </c>
-      <c r="J127" s="38">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="127" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A127" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="B127" s="32"/>
+      <c r="C127" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="D127" s="32"/>
+      <c r="E127" s="12">
+        <v>13.411</v>
+      </c>
+      <c r="F127" s="12">
+        <v>13.1</v>
+      </c>
+      <c r="G127" s="12">
+        <f t="shared" si="24"/>
+        <v>-2.3199999999999998</v>
+      </c>
+      <c r="H127" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="I127" s="13"/>
+      <c r="J127" s="37"/>
+      <c r="K127" s="13" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="128" spans="1:12" s="10" customFormat="1" ht="36" x14ac:dyDescent="0.3">
+      <c r="A128" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="B128" s="31"/>
+      <c r="C128" s="15">
+        <v>45965</v>
+      </c>
+      <c r="D128" s="31"/>
+      <c r="E128" s="10">
+        <v>4.16</v>
+      </c>
+      <c r="F128" s="10">
+        <v>4.4800000000000004</v>
+      </c>
+      <c r="G128" s="10">
+        <f t="shared" si="24"/>
+        <v>7.69</v>
+      </c>
+      <c r="H128" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="I128" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="J128" s="38">
         <v>5</v>
       </c>
-      <c r="K127" s="7" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="128" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A128" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="B128" s="32"/>
-      <c r="C128" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="D128" s="32"/>
-      <c r="E128" s="12">
-        <v>13.411</v>
-      </c>
-      <c r="F128" s="12">
-        <v>13.1</v>
-      </c>
-      <c r="G128" s="12">
-        <f t="shared" si="23"/>
-        <v>-2.3199999999999998</v>
-      </c>
-      <c r="H128" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="I128" s="13"/>
-      <c r="J128" s="37"/>
-      <c r="K128" s="13" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="129" spans="1:11" s="10" customFormat="1" ht="36" x14ac:dyDescent="0.3">
-      <c r="A129" s="10" t="s">
-        <v>102</v>
+      <c r="K128" s="7" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A129" s="12" t="s">
+        <v>29</v>
       </c>
       <c r="B129" s="31"/>
       <c r="C129" s="15">
-        <v>45965</v>
+        <v>45905</v>
       </c>
       <c r="D129" s="31"/>
       <c r="E129" s="10">
-        <v>4.16</v>
+        <v>34.94</v>
       </c>
       <c r="F129" s="10">
-        <v>4.4800000000000004</v>
+        <v>38.200000000000003</v>
       </c>
       <c r="G129" s="10">
-        <f t="shared" si="23"/>
-        <v>7.69</v>
+        <f t="shared" si="24"/>
+        <v>9.33</v>
       </c>
       <c r="H129" s="7" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="I129" s="7">
-        <v>4.5</v>
+        <v>38.200000000000003</v>
       </c>
       <c r="J129" s="38">
         <v>5</v>
       </c>
       <c r="K129" s="7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="130" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="12" t="s">
-        <v>29</v>
+      <c r="A130" s="10" t="s">
+        <v>41</v>
       </c>
       <c r="B130" s="31"/>
       <c r="C130" s="15">
-        <v>45905</v>
+        <v>45782</v>
       </c>
       <c r="D130" s="31"/>
       <c r="E130" s="10">
-        <v>34.94</v>
+        <v>21.67</v>
       </c>
       <c r="F130" s="10">
-        <v>38.200000000000003</v>
+        <v>22.45</v>
       </c>
       <c r="G130" s="10">
-        <f t="shared" si="23"/>
-        <v>9.33</v>
-      </c>
-      <c r="H130" s="7" t="s">
-        <v>111</v>
-      </c>
+        <f t="shared" si="24"/>
+        <v>3.6</v>
+      </c>
+      <c r="H130" s="7"/>
       <c r="I130" s="7">
-        <v>38.200000000000003</v>
+        <v>22.7</v>
       </c>
       <c r="J130" s="38">
         <v>5</v>
       </c>
       <c r="K130" s="7" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
     </row>
     <row r="131" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A131" s="10" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="B131" s="31"/>
       <c r="C131" s="15">
-        <v>45782</v>
+        <v>45813</v>
       </c>
       <c r="D131" s="31"/>
       <c r="E131" s="10">
-        <v>21.67</v>
+        <v>27.45</v>
       </c>
       <c r="F131" s="10">
-        <v>22.45</v>
+        <v>29.4</v>
       </c>
       <c r="G131" s="10">
-        <f t="shared" si="23"/>
-        <v>3.6</v>
-      </c>
-      <c r="H131" s="7"/>
-      <c r="I131" s="7">
-        <v>22.7</v>
-      </c>
+        <f t="shared" si="24"/>
+        <v>7.1</v>
+      </c>
+      <c r="H131" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="I131" s="7"/>
       <c r="J131" s="38">
         <v>5</v>
       </c>
       <c r="K131" s="7" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="132" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11" s="10" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A132" s="10" t="s">
-        <v>30</v>
+        <v>104</v>
       </c>
       <c r="B132" s="31"/>
-      <c r="C132" s="15">
-        <v>45813</v>
+      <c r="C132" s="15" t="s">
+        <v>100</v>
       </c>
       <c r="D132" s="31"/>
       <c r="E132" s="10">
-        <v>27.45</v>
+        <v>11.3</v>
       </c>
       <c r="F132" s="10">
-        <v>29.4</v>
+        <v>12.6</v>
       </c>
       <c r="G132" s="10">
-        <f t="shared" si="23"/>
-        <v>7.1</v>
+        <f t="shared" si="24"/>
+        <v>11.5</v>
       </c>
       <c r="H132" s="7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I132" s="7"/>
-      <c r="J132" s="38">
+      <c r="J132" s="38"/>
+      <c r="K132" s="7" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="133" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A133" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="B133" s="32"/>
+      <c r="C133" s="16">
+        <v>45905</v>
+      </c>
+      <c r="D133" s="32"/>
+      <c r="E133" s="12">
+        <v>92.4</v>
+      </c>
+      <c r="F133" s="12">
+        <v>88.9</v>
+      </c>
+      <c r="G133" s="12">
+        <f t="shared" si="24"/>
+        <v>-3.79</v>
+      </c>
+      <c r="H133" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="I133" s="13"/>
+      <c r="J133" s="37">
         <v>5</v>
       </c>
-      <c r="K132" s="7" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="133" spans="1:11" s="10" customFormat="1" ht="36" x14ac:dyDescent="0.3">
-      <c r="A133" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="B133" s="31"/>
-      <c r="C133" s="15" t="s">
+      <c r="K133" s="13" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="134" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A134" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B134" s="31"/>
+      <c r="C134" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="D133" s="31"/>
-      <c r="E133" s="10">
-        <v>11.3</v>
-      </c>
-      <c r="F133" s="10">
-        <v>12.6</v>
-      </c>
-      <c r="G133" s="10">
-        <f t="shared" si="23"/>
-        <v>11.5</v>
-      </c>
-      <c r="H133" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="I133" s="7"/>
-      <c r="J133" s="38"/>
-      <c r="K133" s="7" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="134" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="B134" s="32"/>
-      <c r="C134" s="16">
-        <v>45905</v>
-      </c>
-      <c r="D134" s="32"/>
-      <c r="E134" s="12">
-        <v>92.4</v>
-      </c>
-      <c r="F134" s="12">
-        <v>88.9</v>
-      </c>
-      <c r="G134" s="12">
-        <f t="shared" si="23"/>
-        <v>-3.79</v>
-      </c>
-      <c r="H134" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="I134" s="13"/>
-      <c r="J134" s="37">
+      <c r="D134" s="31"/>
+      <c r="E134" s="10">
+        <v>31.832000000000001</v>
+      </c>
+      <c r="F134" s="10">
+        <v>34</v>
+      </c>
+      <c r="G134" s="10">
+        <f t="shared" si="24"/>
+        <v>6.81</v>
+      </c>
+      <c r="H134" s="7"/>
+      <c r="I134" s="7">
+        <v>34</v>
+      </c>
+      <c r="J134" s="38">
         <v>5</v>
       </c>
-      <c r="K134" s="13" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="135" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A135" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="B135" s="31"/>
-      <c r="C135" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="D135" s="31"/>
-      <c r="E135" s="10">
-        <v>31.832000000000001</v>
-      </c>
-      <c r="F135" s="10">
-        <v>34</v>
-      </c>
-      <c r="G135" s="10">
-        <f t="shared" si="23"/>
-        <v>6.81</v>
-      </c>
-      <c r="H135" s="7"/>
-      <c r="I135" s="7">
-        <v>34</v>
-      </c>
-      <c r="J135" s="38">
+      <c r="K134" s="7"/>
+    </row>
+    <row r="135" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A135" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B135" s="32"/>
+      <c r="C135" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="D135" s="32"/>
+      <c r="E135" s="12">
+        <v>12.05</v>
+      </c>
+      <c r="F135" s="12">
+        <v>11.75</v>
+      </c>
+      <c r="G135" s="12">
+        <f t="shared" si="24"/>
+        <v>-2.4900000000000002</v>
+      </c>
+      <c r="H135" s="13"/>
+      <c r="I135" s="13">
+        <v>12.95</v>
+      </c>
+      <c r="J135" s="37">
         <v>5</v>
       </c>
-      <c r="K135" s="7"/>
+      <c r="K135" s="13" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="136" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A136" s="12" t="s">
-        <v>11</v>
+      <c r="A136" s="10" t="s">
+        <v>28</v>
       </c>
       <c r="B136" s="32"/>
       <c r="C136" s="16" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D136" s="32"/>
       <c r="E136" s="12">
-        <v>12.05</v>
+        <v>62</v>
       </c>
       <c r="F136" s="12">
-        <v>11.75</v>
+        <v>58.6</v>
       </c>
       <c r="G136" s="12">
-        <f t="shared" si="23"/>
-        <v>-2.4900000000000002</v>
-      </c>
-      <c r="H136" s="13"/>
-      <c r="I136" s="13">
-        <v>12.95</v>
-      </c>
-      <c r="J136" s="37">
-        <v>5</v>
-      </c>
+        <f t="shared" si="24"/>
+        <v>-5.48</v>
+      </c>
+      <c r="H136" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="I136" s="13"/>
+      <c r="J136" s="37"/>
       <c r="K136" s="13" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="137" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A137" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B137" s="32"/>
-      <c r="C137" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="D137" s="32"/>
-      <c r="E137" s="12">
-        <v>62</v>
-      </c>
-      <c r="F137" s="12">
-        <v>58.6</v>
-      </c>
-      <c r="G137" s="12">
-        <f t="shared" si="23"/>
-        <v>-5.48</v>
-      </c>
-      <c r="H137" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="I137" s="13"/>
-      <c r="J137" s="37"/>
-      <c r="K137" s="13" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="138" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A137" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="B137" s="31"/>
+      <c r="C137" s="15">
+        <v>45965</v>
+      </c>
+      <c r="D137" s="31"/>
+      <c r="E137" s="10">
+        <v>83.9</v>
+      </c>
+      <c r="F137" s="10">
+        <v>91.2</v>
+      </c>
+      <c r="G137" s="10">
+        <f t="shared" si="24"/>
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="H137" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="I137" s="7"/>
+      <c r="J137" s="38"/>
+      <c r="K137" s="7" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="138" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A138" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="B138" s="31"/>
-      <c r="C138" s="15">
+        <v>15</v>
+      </c>
+      <c r="B138" s="32"/>
+      <c r="C138" s="16">
         <v>45965</v>
       </c>
-      <c r="D138" s="31"/>
-      <c r="E138" s="10">
-        <v>83.9</v>
-      </c>
-      <c r="F138" s="10">
-        <v>91.2</v>
-      </c>
-      <c r="G138" s="10">
-        <f t="shared" si="23"/>
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="H138" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="I138" s="7"/>
-      <c r="J138" s="38"/>
-      <c r="K138" s="7" t="s">
-        <v>90</v>
+      <c r="D138" s="32"/>
+      <c r="E138" s="12">
+        <v>15.365</v>
+      </c>
+      <c r="F138" s="12">
+        <v>14.8</v>
+      </c>
+      <c r="G138" s="12">
+        <f t="shared" si="24"/>
+        <v>-3.68</v>
+      </c>
+      <c r="H138" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="I138" s="13"/>
+      <c r="J138" s="37"/>
+      <c r="K138" s="13" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="139" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A139" s="12" t="s">
-        <v>15</v>
+      <c r="A139" s="10" t="s">
+        <v>11</v>
       </c>
       <c r="B139" s="32"/>
-      <c r="C139" s="16">
-        <v>45965</v>
+      <c r="C139" s="16" t="s">
+        <v>87</v>
       </c>
       <c r="D139" s="32"/>
       <c r="E139" s="12">
-        <v>15.365</v>
+        <v>31.8</v>
       </c>
       <c r="F139" s="12">
-        <v>14.8</v>
+        <v>30.3</v>
       </c>
       <c r="G139" s="12">
-        <f t="shared" si="23"/>
-        <v>-3.68</v>
+        <f t="shared" si="24"/>
+        <v>-4.72</v>
       </c>
       <c r="H139" s="13" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="I139" s="13"/>
       <c r="J139" s="37"/>
       <c r="K139" s="13" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="140" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A140" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B140" s="32"/>
-      <c r="C140" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="D140" s="32"/>
-      <c r="E140" s="12">
-        <v>31.8</v>
-      </c>
-      <c r="F140" s="12">
-        <v>30.3</v>
-      </c>
-      <c r="G140" s="12">
-        <f t="shared" si="23"/>
-        <v>-4.72</v>
-      </c>
-      <c r="H140" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="I140" s="13"/>
-      <c r="J140" s="37"/>
-      <c r="K140" s="13" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="141" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A140" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B140" s="31"/>
+      <c r="C140" s="15">
+        <v>45965</v>
+      </c>
+      <c r="D140" s="31"/>
+      <c r="E140" s="10">
+        <v>11.7</v>
+      </c>
+      <c r="F140" s="10">
+        <v>13</v>
+      </c>
+      <c r="G140" s="10">
+        <f t="shared" si="24"/>
+        <v>11.11</v>
+      </c>
+      <c r="H140" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="I140" s="7"/>
+      <c r="J140" s="38"/>
+      <c r="K140" s="7" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="141" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A141" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B141" s="31"/>
-      <c r="C141" s="15">
+        <v>14</v>
+      </c>
+      <c r="B141" s="32"/>
+      <c r="C141" s="16">
         <v>45965</v>
       </c>
-      <c r="D141" s="31"/>
-      <c r="E141" s="10">
-        <v>11.7</v>
-      </c>
-      <c r="F141" s="10">
-        <v>13</v>
-      </c>
-      <c r="G141" s="10">
-        <f t="shared" si="23"/>
-        <v>11.11</v>
-      </c>
-      <c r="H141" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="I141" s="7"/>
-      <c r="J141" s="38"/>
-      <c r="K141" s="7" t="s">
-        <v>89</v>
-      </c>
+      <c r="D141" s="32"/>
+      <c r="E141" s="12">
+        <v>2.6669999999999998</v>
+      </c>
+      <c r="F141" s="12">
+        <v>2.5099999999999998</v>
+      </c>
+      <c r="G141" s="12">
+        <f t="shared" si="24"/>
+        <v>-5.89</v>
+      </c>
+      <c r="H141" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="I141" s="13"/>
+      <c r="J141" s="37"/>
+      <c r="K141" s="13"/>
     </row>
     <row r="142" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A142" s="12" t="s">
-        <v>14</v>
+      <c r="A142" s="10" t="s">
+        <v>66</v>
       </c>
       <c r="B142" s="32"/>
       <c r="C142" s="16">
-        <v>45965</v>
+        <v>45661</v>
       </c>
       <c r="D142" s="32"/>
       <c r="E142" s="12">
-        <v>2.6669999999999998</v>
+        <v>4.55</v>
       </c>
       <c r="F142" s="12">
-        <v>2.5099999999999998</v>
+        <v>4.53</v>
       </c>
       <c r="G142" s="12">
-        <f t="shared" si="23"/>
-        <v>-5.89</v>
+        <f t="shared" si="24"/>
+        <v>-0.44</v>
       </c>
       <c r="H142" s="13" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="I142" s="13"/>
       <c r="J142" s="37"/>
-      <c r="K142" s="13"/>
+      <c r="K142" s="13" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="143" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A143" s="10" t="s">
-        <v>66</v>
+      <c r="A143" s="12" t="s">
+        <v>31</v>
       </c>
       <c r="B143" s="32"/>
-      <c r="C143" s="16">
-        <v>45661</v>
-      </c>
       <c r="D143" s="32"/>
       <c r="E143" s="12">
-        <v>4.55</v>
+        <v>24.45</v>
       </c>
       <c r="F143" s="12">
-        <v>4.53</v>
+        <v>23.9</v>
       </c>
       <c r="G143" s="12">
-        <f t="shared" si="23"/>
-        <v>-0.44</v>
+        <f t="shared" si="24"/>
+        <v>-2.25</v>
       </c>
       <c r="H143" s="13" t="s">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="I143" s="13"/>
       <c r="J143" s="37"/>
       <c r="K143" s="13" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="144" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.3">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="144" spans="1:11" s="12" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A144" s="12" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="B144" s="32"/>
+      <c r="C144" s="16">
+        <v>45692</v>
+      </c>
       <c r="D144" s="32"/>
       <c r="E144" s="12">
-        <v>24.45</v>
+        <v>13</v>
       </c>
       <c r="F144" s="12">
-        <v>23.9</v>
+        <v>12.95</v>
       </c>
       <c r="G144" s="12">
-        <f t="shared" si="23"/>
-        <v>-2.25</v>
+        <f t="shared" si="24"/>
+        <v>-0.38</v>
       </c>
       <c r="H144" s="13" t="s">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="I144" s="13"/>
       <c r="J144" s="37"/>
       <c r="K144" s="13" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="145" spans="1:11" s="12" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A145" s="12" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B145" s="32"/>
-      <c r="C145" s="16">
-        <v>45692</v>
-      </c>
       <c r="D145" s="32"/>
       <c r="E145" s="12">
-        <v>13</v>
+        <v>11.7</v>
       </c>
       <c r="F145" s="12">
-        <v>12.95</v>
-      </c>
-      <c r="G145" s="12">
-        <f t="shared" si="23"/>
-        <v>-0.38</v>
+        <v>11.6</v>
+      </c>
+      <c r="G145" s="13">
+        <f t="shared" ref="G145:G158" si="25">ROUND((F145 - E145) / E145 * 100, 2)</f>
+        <v>-0.85</v>
       </c>
       <c r="H145" s="13" t="s">
-        <v>79</v>
+        <v>49</v>
       </c>
       <c r="I145" s="13"/>
       <c r="J145" s="37"/>
       <c r="K145" s="13" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="146" spans="1:11" s="12" customFormat="1" ht="36" x14ac:dyDescent="0.3">
-      <c r="A146" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="B146" s="32"/>
-      <c r="D146" s="32"/>
-      <c r="E146" s="12">
-        <v>11.7</v>
-      </c>
-      <c r="F146" s="12">
-        <v>11.6</v>
-      </c>
-      <c r="G146" s="13">
-        <f t="shared" ref="G146:G159" si="24">ROUND((F146 - E146) / E146 * 100, 2)</f>
-        <v>-0.85</v>
-      </c>
-      <c r="H146" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="I146" s="13"/>
-      <c r="J146" s="37"/>
-      <c r="K146" s="13" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="147" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A147" s="12"/>
-      <c r="B147" s="31"/>
-      <c r="C147" s="10" t="s">
+    <row r="146" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A146" s="12"/>
+      <c r="B146" s="31"/>
+      <c r="C146" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="D147" s="31"/>
-      <c r="E147" s="10">
+      <c r="D146" s="31"/>
+      <c r="E146" s="10">
         <v>51.2</v>
       </c>
-      <c r="F147" s="10">
+      <c r="F146" s="10">
         <v>51.5</v>
       </c>
-      <c r="G147" s="10">
-        <f t="shared" si="24"/>
+      <c r="G146" s="10">
+        <f t="shared" si="25"/>
         <v>0.59</v>
       </c>
-      <c r="H147" s="7" t="s">
+      <c r="H146" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="I147" s="7"/>
-      <c r="J147" s="38"/>
-      <c r="K147" s="7" t="s">
+      <c r="I146" s="7"/>
+      <c r="J146" s="38"/>
+      <c r="K146" s="7" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="148" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A148" s="12" t="s">
+    <row r="147" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A147" s="12" t="s">
         <v>9</v>
+      </c>
+      <c r="B147" s="32"/>
+      <c r="D147" s="32"/>
+      <c r="E147" s="12">
+        <v>12.6</v>
+      </c>
+      <c r="F147" s="12">
+        <v>12.5</v>
+      </c>
+      <c r="G147" s="12">
+        <f t="shared" si="25"/>
+        <v>-0.79</v>
+      </c>
+      <c r="H147" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="I147" s="13"/>
+      <c r="J147" s="37"/>
+      <c r="K147" s="13" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="148" spans="1:11" s="12" customFormat="1" ht="36" x14ac:dyDescent="0.3">
+      <c r="A148" s="10" t="s">
+        <v>65</v>
       </c>
       <c r="B148" s="32"/>
       <c r="D148" s="32"/>
       <c r="E148" s="12">
-        <v>12.6</v>
+        <v>69.3</v>
       </c>
       <c r="F148" s="12">
-        <v>12.5</v>
-      </c>
-      <c r="G148" s="12">
-        <f t="shared" si="24"/>
-        <v>-0.79</v>
-      </c>
-      <c r="H148" s="13" t="s">
-        <v>68</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="G148" s="13">
+        <f t="shared" si="25"/>
+        <v>-4.76</v>
+      </c>
+      <c r="H148" s="13"/>
       <c r="I148" s="13"/>
       <c r="J148" s="37"/>
       <c r="K148" s="13" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="149" spans="1:11" s="12" customFormat="1" ht="36" x14ac:dyDescent="0.3">
-      <c r="A149" s="10" t="s">
-        <v>65</v>
+      <c r="A149" s="12" t="s">
+        <v>66</v>
       </c>
       <c r="B149" s="32"/>
+      <c r="C149" s="12" t="s">
+        <v>70</v>
+      </c>
       <c r="D149" s="32"/>
       <c r="E149" s="12">
-        <v>69.3</v>
+        <v>16.05</v>
       </c>
       <c r="F149" s="12">
-        <v>66</v>
-      </c>
-      <c r="G149" s="13">
-        <f t="shared" si="24"/>
-        <v>-4.76</v>
-      </c>
-      <c r="H149" s="13"/>
+        <v>15.25</v>
+      </c>
+      <c r="G149" s="12">
+        <f t="shared" si="25"/>
+        <v>-4.9800000000000004</v>
+      </c>
+      <c r="H149" s="13" t="s">
+        <v>71</v>
+      </c>
       <c r="I149" s="13"/>
       <c r="J149" s="37"/>
       <c r="K149" s="13" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="150" spans="1:11" s="12" customFormat="1" ht="36" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A150" s="12" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="B150" s="32"/>
       <c r="C150" s="12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D150" s="32"/>
       <c r="E150" s="12">
-        <v>16.05</v>
+        <v>78.7</v>
       </c>
       <c r="F150" s="12">
-        <v>15.25</v>
+        <v>77.8</v>
       </c>
       <c r="G150" s="12">
-        <f t="shared" si="24"/>
-        <v>-4.9800000000000004</v>
+        <f t="shared" si="25"/>
+        <v>-1.1399999999999999</v>
       </c>
       <c r="H150" s="13" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="I150" s="13"/>
       <c r="J150" s="37"/>
       <c r="K150" s="13" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="151" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="151" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A151" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="B151" s="32"/>
-      <c r="C151" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="D151" s="32"/>
-      <c r="E151" s="12">
-        <v>78.7</v>
-      </c>
-      <c r="F151" s="12">
-        <v>77.8</v>
-      </c>
-      <c r="G151" s="12">
-        <f t="shared" si="24"/>
-        <v>-1.1399999999999999</v>
-      </c>
-      <c r="H151" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="I151" s="13"/>
-      <c r="J151" s="37"/>
-      <c r="K151" s="13" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="152" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+      <c r="B151" s="31"/>
+      <c r="C151" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="D151" s="31"/>
+      <c r="E151" s="10">
+        <v>23.85</v>
+      </c>
+      <c r="F151" s="10">
+        <v>23.95</v>
+      </c>
+      <c r="G151" s="10">
+        <f t="shared" si="25"/>
+        <v>0.42</v>
+      </c>
+      <c r="H151" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="I151" s="7"/>
+      <c r="J151" s="38"/>
+      <c r="K151" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="152" spans="1:11" s="12" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A152" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="B152" s="31"/>
-      <c r="C152" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B152" s="32"/>
+      <c r="D152" s="32"/>
+      <c r="E152" s="12">
+        <v>20.76</v>
+      </c>
+      <c r="F152" s="12">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="G152" s="12">
+        <f t="shared" si="25"/>
+        <v>-4.1399999999999997</v>
+      </c>
+      <c r="H152" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="I152" s="13"/>
+      <c r="J152" s="37"/>
+      <c r="K152" s="13" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="153" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A153" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B153" s="31"/>
+      <c r="D153" s="31"/>
+      <c r="E153" s="10">
+        <v>17.75</v>
+      </c>
+      <c r="F153" s="10">
+        <v>20</v>
+      </c>
+      <c r="G153" s="10">
+        <f t="shared" si="25"/>
+        <v>12.68</v>
+      </c>
+      <c r="H153" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="I153" s="7"/>
+      <c r="J153" s="38"/>
+      <c r="K153" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="154" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A154" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B154" s="32"/>
+      <c r="D154" s="32"/>
+      <c r="E154" s="12">
+        <v>99</v>
+      </c>
+      <c r="F154" s="12">
+        <v>96.2</v>
+      </c>
+      <c r="G154" s="13">
+        <f t="shared" si="25"/>
+        <v>-2.83</v>
+      </c>
+      <c r="H154" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="I154" s="13"/>
+      <c r="J154" s="37"/>
+      <c r="K154" s="13" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="155" spans="1:11" s="12" customFormat="1" ht="36" x14ac:dyDescent="0.3">
+      <c r="A155" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B155" s="32"/>
+      <c r="C155" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="D152" s="31"/>
-      <c r="E152" s="10">
-        <v>23.85</v>
-      </c>
-      <c r="F152" s="10">
-        <v>23.95</v>
-      </c>
-      <c r="G152" s="10">
-        <f t="shared" si="24"/>
-        <v>0.42</v>
-      </c>
-      <c r="H152" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="I152" s="7"/>
-      <c r="J152" s="38"/>
-      <c r="K152" s="7" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="153" spans="1:11" s="12" customFormat="1" ht="36" x14ac:dyDescent="0.3">
-      <c r="A153" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="B153" s="32"/>
-      <c r="D153" s="32"/>
-      <c r="E153" s="12">
-        <v>20.76</v>
-      </c>
-      <c r="F153" s="12">
-        <v>19.899999999999999</v>
-      </c>
-      <c r="G153" s="12">
-        <f t="shared" si="24"/>
-        <v>-4.1399999999999997</v>
-      </c>
-      <c r="H153" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="I153" s="13"/>
-      <c r="J153" s="37"/>
-      <c r="K153" s="13" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="154" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A154" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B154" s="31"/>
-      <c r="D154" s="31"/>
-      <c r="E154" s="10">
-        <v>17.75</v>
-      </c>
-      <c r="F154" s="10">
-        <v>20</v>
-      </c>
-      <c r="G154" s="10">
-        <f t="shared" si="24"/>
-        <v>12.68</v>
-      </c>
-      <c r="H154" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="I154" s="7"/>
-      <c r="J154" s="38"/>
-      <c r="K154" s="7" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="155" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A155" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B155" s="32"/>
       <c r="D155" s="32"/>
       <c r="E155" s="12">
-        <v>99</v>
+        <v>29.5</v>
       </c>
       <c r="F155" s="12">
-        <v>96.2</v>
+        <v>29.4</v>
       </c>
       <c r="G155" s="13">
-        <f t="shared" si="24"/>
-        <v>-2.83</v>
+        <f t="shared" si="25"/>
+        <v>-0.34</v>
       </c>
       <c r="H155" s="13" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="I155" s="13"/>
       <c r="J155" s="37"/>
       <c r="K155" s="13" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="156" spans="1:11" s="12" customFormat="1" ht="36" x14ac:dyDescent="0.3">
-      <c r="A156" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="B156" s="32"/>
-      <c r="C156" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="D156" s="32"/>
-      <c r="E156" s="12">
-        <v>29.5</v>
-      </c>
-      <c r="F156" s="12">
-        <v>29.4</v>
-      </c>
-      <c r="G156" s="13">
-        <f t="shared" si="24"/>
-        <v>-0.34</v>
-      </c>
-      <c r="H156" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="I156" s="13"/>
-      <c r="J156" s="37"/>
-      <c r="K156" s="13" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="157" spans="1:11" s="10" customFormat="1" ht="54" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:11" s="10" customFormat="1" ht="54" x14ac:dyDescent="0.3">
+      <c r="A156" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B156" s="31"/>
+      <c r="D156" s="31"/>
+      <c r="E156" s="10">
+        <v>10.5</v>
+      </c>
+      <c r="F156" s="10">
+        <v>12.45</v>
+      </c>
+      <c r="G156" s="10">
+        <f t="shared" si="25"/>
+        <v>18.57</v>
+      </c>
+      <c r="H156" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I156" s="7"/>
+      <c r="J156" s="38"/>
+      <c r="K156" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="157" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A157" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="B157" s="31"/>
-      <c r="D157" s="31"/>
-      <c r="E157" s="10">
-        <v>10.5</v>
-      </c>
-      <c r="F157" s="10">
-        <v>12.45</v>
-      </c>
-      <c r="G157" s="10">
-        <f t="shared" si="24"/>
-        <v>18.57</v>
-      </c>
-      <c r="H157" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="I157" s="7"/>
-      <c r="J157" s="38"/>
-      <c r="K157" s="7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="158" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A158" s="12" t="s">
         <v>54</v>
+      </c>
+      <c r="B157" s="32"/>
+      <c r="D157" s="32"/>
+      <c r="E157" s="12">
+        <v>18.7</v>
+      </c>
+      <c r="F157" s="12">
+        <v>18.3</v>
+      </c>
+      <c r="G157" s="13">
+        <f t="shared" si="25"/>
+        <v>-2.14</v>
+      </c>
+      <c r="H157" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="I157" s="13"/>
+      <c r="J157" s="37"/>
+      <c r="K157" s="13" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="158" spans="1:11" s="12" customFormat="1" ht="36" x14ac:dyDescent="0.3">
+      <c r="A158" s="10" t="s">
+        <v>25</v>
       </c>
       <c r="B158" s="32"/>
       <c r="D158" s="32"/>
       <c r="E158" s="12">
-        <v>18.7</v>
+        <v>51.9</v>
       </c>
       <c r="F158" s="12">
-        <v>18.3</v>
+        <v>51.6</v>
       </c>
       <c r="G158" s="13">
-        <f t="shared" si="24"/>
-        <v>-2.14</v>
+        <f t="shared" si="25"/>
+        <v>-0.57999999999999996</v>
       </c>
       <c r="H158" s="13" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I158" s="13"/>
       <c r="J158" s="37"/>
       <c r="K158" s="13" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="159" spans="1:11" s="12" customFormat="1" ht="36" x14ac:dyDescent="0.3">
-      <c r="A159" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="B159" s="32"/>
-      <c r="D159" s="32"/>
-      <c r="E159" s="12">
-        <v>51.9</v>
-      </c>
-      <c r="F159" s="12">
-        <v>51.6</v>
-      </c>
-      <c r="G159" s="13">
-        <f t="shared" si="24"/>
-        <v>-0.57999999999999996</v>
-      </c>
-      <c r="H159" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="I159" s="13"/>
-      <c r="J159" s="37"/>
-      <c r="K159" s="13" t="s">
         <v>47</v>
+      </c>
+    </row>
+    <row r="159" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A159" s="12" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="160" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A160" s="12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="161" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A161" s="12" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="168" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B168" s="33"/>
-      <c r="C168" s="11"/>
-      <c r="D168" s="33"/>
-      <c r="E168" s="11"/>
-      <c r="F168" s="11"/>
-      <c r="G168" s="11"/>
-      <c r="H168" s="14"/>
-      <c r="I168" s="14"/>
-      <c r="J168" s="39"/>
-      <c r="K168" s="14"/>
-      <c r="L168" s="11"/>
-      <c r="M168" s="11"/>
-      <c r="N168" s="11"/>
-      <c r="O168" s="11"/>
-    </row>
-    <row r="170" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A170" s="11"/>
+    <row r="167" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B167" s="33"/>
+      <c r="C167" s="11"/>
+      <c r="D167" s="33"/>
+      <c r="E167" s="11"/>
+      <c r="F167" s="11"/>
+      <c r="G167" s="11"/>
+      <c r="H167" s="14"/>
+      <c r="I167" s="14"/>
+      <c r="J167" s="39"/>
+      <c r="K167" s="14"/>
+      <c r="L167" s="11"/>
+      <c r="M167" s="11"/>
+      <c r="N167" s="11"/>
+      <c r="O167" s="11"/>
+    </row>
+    <row r="169" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A169" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -24019,12 +24110,12 @@
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B62" s="20" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B63" s="20" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.3">
@@ -24034,7 +24125,7 @@
     </row>
     <row r="65" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B65" s="20" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="66" spans="2:2" x14ac:dyDescent="0.3">

--- a/stock_trading_journal.xlsx
+++ b/stock_trading_journal.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ChienVH\Code\Document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CFD3348-F228-47EE-87A8-81807280512B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C5FB780-51A2-4E20-8094-0600F528D73E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1492" uniqueCount="1148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1494" uniqueCount="1150">
   <si>
     <t>Ngày giao dịch</t>
   </si>
@@ -3481,6 +3481,12 @@
   </si>
   <si>
     <t>207.208</t>
+  </si>
+  <si>
+    <t>19/3/2026</t>
+  </si>
+  <si>
+    <t>201.260</t>
   </si>
 </sst>
 </file>
@@ -4262,7 +4268,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F80FBEA-61B1-4D5E-A59E-30CA607BFEAD}">
-  <dimension ref="A1:E207"/>
+  <dimension ref="A1:E208"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16.44140625" style="27" bestFit="1" customWidth="1"/>
@@ -6034,7 +6040,7 @@
         <v>920</v>
       </c>
       <c r="C138" s="27">
-        <f t="shared" ref="C138:C207" si="18">B138-B137</f>
+        <f t="shared" ref="C138:C208" si="18">B138-B137</f>
         <v>-4.5640000000000214</v>
       </c>
       <c r="D138" s="27" t="s">
@@ -6944,6 +6950,18 @@
       <c r="C207" s="27">
         <f t="shared" si="18"/>
         <v>-2.6630000000000109</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A208" s="27" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B208" s="27" t="s">
+        <v>1149</v>
+      </c>
+      <c r="C208" s="27">
+        <f t="shared" si="18"/>
+        <v>-5.9480000000000075</v>
       </c>
     </row>
   </sheetData>
@@ -19245,11 +19263,11 @@
         <v>42.2</v>
       </c>
       <c r="F2" s="10">
-        <v>43.7</v>
+        <v>43.5</v>
       </c>
       <c r="G2" s="10">
         <f t="shared" ref="G2" si="0">ROUND((F2 - E2) / E2 * 100, 2)</f>
-        <v>3.55</v>
+        <v>3.08</v>
       </c>
       <c r="H2" s="7" t="s">
         <v>993</v>
@@ -19282,11 +19300,11 @@
         <v>63.86</v>
       </c>
       <c r="F3" s="12">
-        <v>60.5</v>
+        <v>59.8</v>
       </c>
       <c r="G3" s="12">
         <f t="shared" ref="G3" si="1">ROUND((F3 - E3) / E3 * 100, 2)</f>
-        <v>-5.26</v>
+        <v>-6.36</v>
       </c>
       <c r="H3" s="13" t="s">
         <v>1003</v>
@@ -19315,11 +19333,11 @@
         <v>27.21</v>
       </c>
       <c r="F4" s="12">
-        <v>21.45</v>
+        <v>20.55</v>
       </c>
       <c r="G4" s="12">
         <f t="shared" ref="G4" si="2">ROUND((F4 - E4) / E4 * 100, 2)</f>
-        <v>-21.17</v>
+        <v>-24.48</v>
       </c>
       <c r="H4" s="13" t="s">
         <v>1025</v>
@@ -19348,11 +19366,11 @@
         <v>20.67</v>
       </c>
       <c r="F5" s="12">
-        <v>16.149999999999999</v>
+        <v>15.6</v>
       </c>
       <c r="G5" s="12">
         <f>ROUND((F5 - E5) / E5 * 100, 2)</f>
-        <v>-21.87</v>
+        <v>-24.53</v>
       </c>
       <c r="H5" s="13" t="s">
         <v>1016</v>
@@ -19381,11 +19399,11 @@
         <v>12.707000000000001</v>
       </c>
       <c r="F6" s="12">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="G6" s="12">
         <f>ROUND((F6 - E6) / E6 * 100, 2)</f>
-        <v>-14.22</v>
+        <v>-15.01</v>
       </c>
       <c r="H6" s="13" t="s">
         <v>835</v>

--- a/stock_trading_journal.xlsx
+++ b/stock_trading_journal.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ChienVH\Code\Document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30DBDBD5-868A-4446-A323-00931B8ECC98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB7A2A59-74EB-4A42-8E54-D7A677511C86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tài Khoản" sheetId="5" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1504" uniqueCount="1161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1522" uniqueCount="1173">
   <si>
     <t>Ngày giao dịch</t>
   </si>
@@ -3232,9 +3232,6 @@
     <t>30/1/2026</t>
   </si>
   <si>
-    <t>HHS</t>
-  </si>
-  <si>
     <t>237.789</t>
   </si>
   <si>
@@ -3442,12 +3439,6 @@
     <t>13/3/2026</t>
   </si>
   <si>
-    <t>NLG</t>
-  </si>
-  <si>
-    <t>VIB</t>
-  </si>
-  <si>
     <t>203.397</t>
   </si>
   <si>
@@ -3502,25 +3493,70 @@
     <t>184.647</t>
   </si>
   <si>
-    <t>vẫn trong kênh song song hướng lên</t>
-  </si>
-  <si>
-    <t>chờ lên gần ma20 bán</t>
-  </si>
-  <si>
-    <t>yếu thủng đáy</t>
-  </si>
-  <si>
     <t>25/3/2026</t>
   </si>
   <si>
     <t>189.882</t>
   </si>
   <si>
-    <t>5400</t>
-  </si>
-  <si>
-    <t>tăng trần nhưng vol vẫn yếu lắm lên ma20 thì bán</t>
+    <t>26/3/2026</t>
+  </si>
+  <si>
+    <t>192.015</t>
+  </si>
+  <si>
+    <t>27/3/2026</t>
+  </si>
+  <si>
+    <t>198.723</t>
+  </si>
+  <si>
+    <t>6.19</t>
+  </si>
+  <si>
+    <t>chạm đáy cây song song hồi phục nhưng yếu</t>
+  </si>
+  <si>
+    <t>30/3/2026</t>
+  </si>
+  <si>
+    <t>vượt ma20, 2 cây tích luỹ xanh, macd cắt lên trên, ma10 cắt ma20</t>
+  </si>
+  <si>
+    <t>196.169</t>
+  </si>
+  <si>
+    <t>31/3/2026</t>
+  </si>
+  <si>
+    <t>SHS</t>
+  </si>
+  <si>
+    <t>TCB</t>
+  </si>
+  <si>
+    <t>CTS</t>
+  </si>
+  <si>
+    <t>199.881</t>
+  </si>
+  <si>
+    <t>tiếp tục tích luỹ trên ma20</t>
+  </si>
+  <si>
+    <t>1/4/2026</t>
+  </si>
+  <si>
+    <t>206.999</t>
+  </si>
+  <si>
+    <t>giá lên chạm ma200 giảm</t>
+  </si>
+  <si>
+    <t>giá vượt lên ma20, macd cắt lên trên đường tín hiệu</t>
+  </si>
+  <si>
+    <t>dừng rơi tạo nền mới</t>
   </si>
 </sst>
 </file>
@@ -4140,7 +4176,7 @@
     <row r="4" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="22"/>
       <c r="B4" s="28" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="C4" s="22"/>
       <c r="D4" s="22"/>
@@ -4272,7 +4308,7 @@
     <row r="17" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="22"/>
       <c r="B17" s="28" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="C17" s="41"/>
       <c r="D17" s="41"/>
@@ -4302,7 +4338,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F80FBEA-61B1-4D5E-A59E-30CA607BFEAD}">
-  <dimension ref="A1:E212"/>
+  <dimension ref="A1:E217"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.42578125" style="27" bestFit="1" customWidth="1"/>
@@ -6074,7 +6110,7 @@
         <v>920</v>
       </c>
       <c r="C138" s="27">
-        <f t="shared" ref="C138:C212" si="18">B138-B137</f>
+        <f t="shared" ref="C138:C217" si="18">B138-B137</f>
         <v>-4.5640000000000214</v>
       </c>
       <c r="D138" s="27" t="s">
@@ -6623,22 +6659,22 @@
         <v>1063</v>
       </c>
       <c r="B180" s="27" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="C180" s="27">
         <f t="shared" si="18"/>
         <v>5.1079999999999757</v>
       </c>
       <c r="D180" s="27" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="181" spans="1:5" s="35" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A181" s="29" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B181" s="29" t="s">
         <v>1068</v>
-      </c>
-      <c r="B181" s="29" t="s">
-        <v>1069</v>
       </c>
       <c r="C181" s="29">
         <f t="shared" si="18"/>
@@ -6649,10 +6685,10 @@
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A182" s="27" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B182" s="27" t="s">
         <v>1070</v>
-      </c>
-      <c r="B182" s="27" t="s">
-        <v>1071</v>
       </c>
       <c r="C182" s="27">
         <f t="shared" si="18"/>
@@ -6661,10 +6697,10 @@
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A183" s="27" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B183" s="27" t="s">
         <v>1072</v>
-      </c>
-      <c r="B183" s="27" t="s">
-        <v>1073</v>
       </c>
       <c r="C183" s="27">
         <f t="shared" si="18"/>
@@ -6673,25 +6709,25 @@
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A184" s="27" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B184" s="27" t="s">
         <v>1076</v>
-      </c>
-      <c r="B184" s="27" t="s">
-        <v>1077</v>
       </c>
       <c r="C184" s="27">
         <f t="shared" si="18"/>
         <v>-14.457000000000022</v>
       </c>
       <c r="D184" s="27" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="185" spans="1:5" s="35" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A185" s="29" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B185" s="29" t="s">
         <v>1081</v>
-      </c>
-      <c r="B185" s="29" t="s">
-        <v>1082</v>
       </c>
       <c r="C185" s="29">
         <f t="shared" si="18"/>
@@ -6702,10 +6738,10 @@
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A186" s="27" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B186" s="27" t="s">
         <v>1083</v>
-      </c>
-      <c r="B186" s="27" t="s">
-        <v>1084</v>
       </c>
       <c r="C186" s="27">
         <f t="shared" si="18"/>
@@ -6714,10 +6750,10 @@
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A187" s="27" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B187" s="27" t="s">
         <v>1085</v>
-      </c>
-      <c r="B187" s="27" t="s">
-        <v>1086</v>
       </c>
       <c r="C187" s="27">
         <f t="shared" si="18"/>
@@ -6726,10 +6762,10 @@
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A188" s="27" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B188" s="27" t="s">
         <v>1087</v>
-      </c>
-      <c r="B188" s="27" t="s">
-        <v>1088</v>
       </c>
       <c r="C188" s="27">
         <f t="shared" si="18"/>
@@ -6738,25 +6774,25 @@
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A189" s="27" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="B189" s="27" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="C189" s="27">
         <f t="shared" si="18"/>
         <v>2.0679999999999836</v>
       </c>
       <c r="D189" s="27" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="190" spans="1:5" s="35" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A190" s="29" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B190" s="29" t="s">
         <v>1093</v>
-      </c>
-      <c r="B190" s="29" t="s">
-        <v>1094</v>
       </c>
       <c r="C190" s="29">
         <f t="shared" si="18"/>
@@ -6767,10 +6803,10 @@
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A191" s="27" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B191" s="27" t="s">
         <v>1095</v>
-      </c>
-      <c r="B191" s="27" t="s">
-        <v>1096</v>
       </c>
       <c r="C191" s="27">
         <f t="shared" si="18"/>
@@ -6779,24 +6815,24 @@
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A192" s="27" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="B192" s="27" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="C192" s="27" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="E192" s="27" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A193" s="27" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="B193" s="27" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="C193" s="27">
         <f t="shared" si="18"/>
@@ -6805,25 +6841,25 @@
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A194" s="27" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B194" s="27" t="s">
         <v>1110</v>
-      </c>
-      <c r="B194" s="27" t="s">
-        <v>1111</v>
       </c>
       <c r="C194" s="27">
         <f t="shared" si="18"/>
         <v>-3.0240000000000009</v>
       </c>
       <c r="D194" s="27" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="195" spans="1:5" s="35" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A195" s="29" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B195" s="29" t="s">
         <v>1113</v>
-      </c>
-      <c r="B195" s="29" t="s">
-        <v>1114</v>
       </c>
       <c r="C195" s="29">
         <f t="shared" si="18"/>
@@ -6834,10 +6870,10 @@
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A196" s="27" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B196" s="27" t="s">
         <v>1115</v>
-      </c>
-      <c r="B196" s="27" t="s">
-        <v>1116</v>
       </c>
       <c r="C196" s="27">
         <f t="shared" si="18"/>
@@ -6846,10 +6882,10 @@
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A197" s="27" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B197" s="27" t="s">
         <v>1117</v>
-      </c>
-      <c r="B197" s="27" t="s">
-        <v>1118</v>
       </c>
       <c r="C197" s="27">
         <f t="shared" si="18"/>
@@ -6858,10 +6894,10 @@
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A198" s="27" t="s">
+        <v>1118</v>
+      </c>
+      <c r="B198" s="27" t="s">
         <v>1119</v>
-      </c>
-      <c r="B198" s="27" t="s">
-        <v>1120</v>
       </c>
       <c r="C198" s="27">
         <f t="shared" si="18"/>
@@ -6870,25 +6906,25 @@
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A199" s="27" t="s">
+        <v>1120</v>
+      </c>
+      <c r="B199" s="27" t="s">
         <v>1121</v>
-      </c>
-      <c r="B199" s="27" t="s">
-        <v>1122</v>
       </c>
       <c r="C199" s="27">
         <f t="shared" si="18"/>
         <v>-12.381</v>
       </c>
       <c r="D199" s="27" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="200" spans="1:5" s="35" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A200" s="29" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="B200" s="29" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="C200" s="29">
         <f t="shared" si="18"/>
@@ -6899,10 +6935,10 @@
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A201" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B201" s="27" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="C201" s="27">
         <f t="shared" si="18"/>
@@ -6911,10 +6947,10 @@
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A202" s="27" t="s">
+        <v>1128</v>
+      </c>
+      <c r="B202" s="27" t="s">
         <v>1129</v>
-      </c>
-      <c r="B202" s="27" t="s">
-        <v>1130</v>
       </c>
       <c r="C202" s="27">
         <f t="shared" si="18"/>
@@ -6923,10 +6959,10 @@
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A203" s="27" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B203" s="27" t="s">
         <v>1131</v>
-      </c>
-      <c r="B203" s="27" t="s">
-        <v>1132</v>
       </c>
       <c r="C203" s="27">
         <f t="shared" si="18"/>
@@ -6935,25 +6971,25 @@
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A204" s="27" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B204" s="27" t="s">
         <v>1133</v>
-      </c>
-      <c r="B204" s="27" t="s">
-        <v>1136</v>
       </c>
       <c r="C204" s="27">
         <f t="shared" si="18"/>
         <v>-5.0049999999999955</v>
       </c>
       <c r="D204" s="27" t="s">
-        <v>1137</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="205" spans="1:5" s="35" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A205" s="29" t="s">
-        <v>1138</v>
+        <v>1135</v>
       </c>
       <c r="B205" s="29" t="s">
-        <v>1139</v>
+        <v>1136</v>
       </c>
       <c r="C205" s="29">
         <f t="shared" si="18"/>
@@ -6964,10 +7000,10 @@
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A206" s="27" t="s">
-        <v>1140</v>
+        <v>1137</v>
       </c>
       <c r="B206" s="27" t="s">
-        <v>1141</v>
+        <v>1138</v>
       </c>
       <c r="C206" s="27">
         <f t="shared" si="18"/>
@@ -6976,10 +7012,10 @@
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A207" s="27" t="s">
-        <v>1143</v>
+        <v>1140</v>
       </c>
       <c r="B207" s="27" t="s">
-        <v>1144</v>
+        <v>1141</v>
       </c>
       <c r="C207" s="27">
         <f t="shared" si="18"/>
@@ -6988,10 +7024,10 @@
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A208" s="27" t="s">
-        <v>1145</v>
+        <v>1142</v>
       </c>
       <c r="B208" s="27" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
       <c r="C208" s="27">
         <f t="shared" si="18"/>
@@ -7000,25 +7036,25 @@
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A209" s="27" t="s">
-        <v>1147</v>
+        <v>1144</v>
       </c>
       <c r="B209" s="27" t="s">
-        <v>1148</v>
+        <v>1145</v>
       </c>
       <c r="C209" s="27">
         <f t="shared" si="18"/>
         <v>-8.7270000000000039</v>
       </c>
       <c r="D209" s="27" t="s">
-        <v>1149</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="210" spans="1:5" s="35" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A210" s="29" t="s">
-        <v>1150</v>
+        <v>1147</v>
       </c>
       <c r="B210" s="29" t="s">
-        <v>1151</v>
+        <v>1148</v>
       </c>
       <c r="C210" s="29">
         <f t="shared" si="18"/>
@@ -7029,10 +7065,10 @@
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A211" s="27" t="s">
-        <v>1152</v>
+        <v>1149</v>
       </c>
       <c r="B211" s="27" t="s">
-        <v>1153</v>
+        <v>1150</v>
       </c>
       <c r="C211" s="27">
         <f t="shared" si="18"/>
@@ -7041,14 +7077,79 @@
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A212" s="27" t="s">
-        <v>1157</v>
+        <v>1151</v>
       </c>
       <c r="B212" s="27" t="s">
-        <v>1158</v>
+        <v>1152</v>
       </c>
       <c r="C212" s="27">
         <f t="shared" si="18"/>
         <v>5.2350000000000136</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A213" s="27" t="s">
+        <v>1153</v>
+      </c>
+      <c r="B213" s="27" t="s">
+        <v>1154</v>
+      </c>
+      <c r="C213" s="27">
+        <f t="shared" si="18"/>
+        <v>2.1329999999999814</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A214" s="27" t="s">
+        <v>1155</v>
+      </c>
+      <c r="B214" s="27" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C214" s="27">
+        <f t="shared" si="18"/>
+        <v>6.7080000000000268</v>
+      </c>
+      <c r="D214" s="27" t="s">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5" s="35" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A215" s="29" t="s">
+        <v>1159</v>
+      </c>
+      <c r="B215" s="29" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C215" s="29">
+        <f t="shared" si="18"/>
+        <v>-2.554000000000002</v>
+      </c>
+      <c r="D215" s="29"/>
+      <c r="E215" s="29"/>
+    </row>
+    <row r="216" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A216" s="27" t="s">
+        <v>1162</v>
+      </c>
+      <c r="B216" s="27" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C216" s="27">
+        <f t="shared" si="18"/>
+        <v>3.7119999999999891</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A217" s="27" t="s">
+        <v>1168</v>
+      </c>
+      <c r="B217" s="27" t="s">
+        <v>1169</v>
+      </c>
+      <c r="C217" s="27">
+        <f t="shared" si="18"/>
+        <v>7.117999999999995</v>
       </c>
     </row>
   </sheetData>
@@ -19274,7 +19375,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F70DC592-D4E4-4D13-ADCA-E681C1A017AC}">
-  <dimension ref="A1:O168"/>
+  <dimension ref="A1:O167"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="8" customWidth="1"/>
@@ -19350,11 +19451,11 @@
         <v>63.86</v>
       </c>
       <c r="F2" s="12">
-        <v>58.4</v>
+        <v>59</v>
       </c>
       <c r="G2" s="12">
         <f t="shared" ref="G2" si="0">ROUND((F2 - E2) / E2 * 100, 2)</f>
-        <v>-8.5500000000000007</v>
+        <v>-7.61</v>
       </c>
       <c r="H2" s="13" t="s">
         <v>1003</v>
@@ -19362,42 +19463,42 @@
       <c r="I2" s="13"/>
       <c r="J2" s="37"/>
       <c r="K2" s="13" t="s">
-        <v>1154</v>
+        <v>1158</v>
       </c>
       <c r="L2" s="13" t="s">
-        <v>1080</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" s="12" customFormat="1" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" s="10" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="32" t="s">
-        <v>1159</v>
-      </c>
-      <c r="C3" s="16" t="s">
+      <c r="B3" s="31" t="s">
+        <v>490</v>
+      </c>
+      <c r="C3" s="15" t="s">
         <v>1024</v>
       </c>
-      <c r="D3" s="32"/>
-      <c r="E3" s="12">
+      <c r="D3" s="31"/>
+      <c r="E3" s="10">
         <v>23.13</v>
       </c>
-      <c r="F3" s="12">
-        <v>21.1</v>
-      </c>
-      <c r="G3" s="12">
+      <c r="F3" s="10">
+        <v>23.5</v>
+      </c>
+      <c r="G3" s="10">
         <f t="shared" ref="G3" si="1">ROUND((F3 - E3) / E3 * 100, 2)</f>
-        <v>-8.7799999999999994</v>
-      </c>
-      <c r="H3" s="13" t="s">
+        <v>1.6</v>
+      </c>
+      <c r="H3" s="7" t="s">
         <v>1025</v>
       </c>
-      <c r="I3" s="13"/>
-      <c r="J3" s="37"/>
-      <c r="K3" s="13" t="s">
-        <v>1160</v>
-      </c>
-      <c r="L3" s="13" t="s">
+      <c r="I3" s="7"/>
+      <c r="J3" s="38"/>
+      <c r="K3" s="7" t="s">
+        <v>1170</v>
+      </c>
+      <c r="L3" s="7" t="s">
         <v>1050</v>
       </c>
     </row>
@@ -19416,11 +19517,11 @@
         <v>20.67</v>
       </c>
       <c r="F4" s="12">
-        <v>15.5</v>
+        <v>16.25</v>
       </c>
       <c r="G4" s="12">
         <f>ROUND((F4 - E4) / E4 * 100, 2)</f>
-        <v>-25.01</v>
+        <v>-21.38</v>
       </c>
       <c r="H4" s="13" t="s">
         <v>1016</v>
@@ -19428,7 +19529,7 @@
       <c r="I4" s="13"/>
       <c r="J4" s="37"/>
       <c r="K4" s="13" t="s">
-        <v>1155</v>
+        <v>1171</v>
       </c>
       <c r="L4" s="12" t="s">
         <v>1051</v>
@@ -19439,21 +19540,21 @@
         <v>736</v>
       </c>
       <c r="B5" s="32" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="D5" s="32"/>
       <c r="E5" s="12">
         <v>12.707000000000001</v>
       </c>
       <c r="F5" s="12">
-        <v>10.1</v>
+        <v>10.15</v>
       </c>
       <c r="G5" s="12">
         <f>ROUND((F5 - E5) / E5 * 100, 2)</f>
-        <v>-20.52</v>
+        <v>-20.12</v>
       </c>
       <c r="H5" s="13" t="s">
         <v>835</v>
@@ -19461,326 +19562,398 @@
       <c r="I5" s="13"/>
       <c r="J5" s="37"/>
       <c r="K5" s="13" t="s">
-        <v>1156</v>
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" s="10" customFormat="1" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="31" t="s">
+        <v>510</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>1159</v>
+      </c>
+      <c r="D6" s="31"/>
+      <c r="E6" s="10">
+        <v>35.78</v>
+      </c>
+      <c r="F6" s="10">
+        <v>37.049999999999997</v>
+      </c>
+      <c r="G6" s="10">
+        <f>ROUND((F6 - E6) / E6 * 100, 2)</f>
+        <v>3.55</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>1160</v>
+      </c>
+      <c r="I6" s="7"/>
+      <c r="J6" s="38"/>
+      <c r="K6" s="7" t="s">
+        <v>1167</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>953</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>66</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>23</v>
+        <v>1163</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>1061</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>1064</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>1061</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>1134</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>1135</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" s="12" customFormat="1" ht="37.5" x14ac:dyDescent="0.25">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" s="8" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" s="8" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" s="12" customFormat="1" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A21" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B21" s="32" t="s">
+        <v>822</v>
+      </c>
+      <c r="C21" s="16">
+        <v>45778</v>
+      </c>
+      <c r="D21" s="32" t="s">
+        <v>1147</v>
+      </c>
+      <c r="E21" s="12">
+        <v>42.2</v>
+      </c>
+      <c r="F21" s="12">
+        <v>39.65</v>
+      </c>
+      <c r="G21" s="12">
+        <f t="shared" ref="G21" si="2">ROUND((F21 - E21) / E21 * 100, 2)</f>
+        <v>-6.04</v>
+      </c>
+      <c r="H21" s="13" t="s">
+        <v>993</v>
+      </c>
+      <c r="I21" s="13">
+        <v>57</v>
+      </c>
+      <c r="J21" s="37" t="s">
+        <v>784</v>
+      </c>
+      <c r="K21" s="13" t="s">
+        <v>1139</v>
+      </c>
+      <c r="L21" s="12" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
-        <v>13</v>
+        <v>1032</v>
       </c>
       <c r="B22" s="32" t="s">
         <v>822</v>
       </c>
-      <c r="C22" s="16">
-        <v>45778</v>
-      </c>
-      <c r="D22" s="32" t="s">
-        <v>1150</v>
-      </c>
+      <c r="C22" s="12" t="s">
+        <v>1088</v>
+      </c>
+      <c r="D22" s="32"/>
       <c r="E22" s="12">
-        <v>42.2</v>
+        <v>24.52</v>
       </c>
       <c r="F22" s="12">
-        <v>39.65</v>
+        <v>23</v>
       </c>
       <c r="G22" s="12">
-        <f t="shared" ref="G22" si="2">ROUND((F22 - E22) / E22 * 100, 2)</f>
-        <v>-6.04</v>
+        <f t="shared" ref="G22:G27" si="3">ROUND((F22 - E22) / E22 * 100, 2)</f>
+        <v>-6.2</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>993</v>
+        <v>1089</v>
       </c>
       <c r="I22" s="13">
-        <v>57</v>
+        <v>32.5</v>
       </c>
       <c r="J22" s="37" t="s">
         <v>784</v>
       </c>
       <c r="K22" s="13" t="s">
-        <v>1142</v>
-      </c>
-      <c r="L22" s="12" t="s">
-        <v>1043</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="23" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
-        <v>1032</v>
+        <v>1062</v>
       </c>
       <c r="B23" s="32" t="s">
-        <v>822</v>
-      </c>
-      <c r="C23" s="12" t="s">
-        <v>1089</v>
+        <v>1073</v>
+      </c>
+      <c r="C23" s="16">
+        <v>46175</v>
       </c>
       <c r="D23" s="32"/>
       <c r="E23" s="12">
-        <v>24.52</v>
+        <v>89.6</v>
       </c>
       <c r="F23" s="12">
-        <v>23</v>
+        <v>85.1</v>
       </c>
       <c r="G23" s="12">
-        <f t="shared" ref="G23:G28" si="3">ROUND((F23 - E23) / E23 * 100, 2)</f>
-        <v>-6.2</v>
+        <f t="shared" si="3"/>
+        <v>-5.0199999999999996</v>
       </c>
       <c r="H23" s="13" t="s">
-        <v>1090</v>
-      </c>
-      <c r="I23" s="13">
-        <v>32.5</v>
-      </c>
+        <v>1074</v>
+      </c>
+      <c r="I23" s="13"/>
       <c r="J23" s="37" t="s">
         <v>784</v>
       </c>
       <c r="K23" s="13" t="s">
-        <v>1128</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="12" t="s">
-        <v>1062</v>
-      </c>
-      <c r="B24" s="32" t="s">
-        <v>1074</v>
-      </c>
-      <c r="C24" s="16">
-        <v>46175</v>
-      </c>
-      <c r="D24" s="32"/>
-      <c r="E24" s="12">
-        <v>89.6</v>
-      </c>
-      <c r="F24" s="12">
-        <v>85.1</v>
-      </c>
-      <c r="G24" s="12">
-        <f t="shared" si="3"/>
-        <v>-5.0199999999999996</v>
-      </c>
-      <c r="H24" s="13" t="s">
-        <v>1075</v>
-      </c>
-      <c r="I24" s="13"/>
-      <c r="J24" s="37" t="s">
-        <v>784</v>
-      </c>
-      <c r="K24" s="13" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="25" spans="1:12" s="10" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="10" t="s">
+    <row r="24" spans="1:12" s="10" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="10" t="s">
         <v>953</v>
       </c>
-      <c r="B25" s="31" t="s">
+      <c r="B24" s="31" t="s">
         <v>731</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="C24" s="15" t="s">
         <v>1054</v>
       </c>
-      <c r="D25" s="31" t="s">
-        <v>1113</v>
-      </c>
-      <c r="E25" s="10">
+      <c r="D24" s="31" t="s">
+        <v>1112</v>
+      </c>
+      <c r="E24" s="10">
         <v>30.475000000000001</v>
       </c>
-      <c r="F25" s="10">
+      <c r="F24" s="10">
         <v>35</v>
       </c>
-      <c r="G25" s="10">
+      <c r="G24" s="10">
         <f t="shared" si="3"/>
         <v>14.85</v>
       </c>
-      <c r="H25" s="7" t="s">
+      <c r="H24" s="7" t="s">
         <v>1055</v>
       </c>
-      <c r="I25" s="7">
+      <c r="I24" s="7">
         <v>35</v>
       </c>
-      <c r="J25" s="38" t="s">
+      <c r="J24" s="38" t="s">
         <v>784</v>
       </c>
-      <c r="K25" s="7" t="s">
-        <v>1097</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" s="12" customFormat="1" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A26" s="12" t="s">
+      <c r="K24" s="7" t="s">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" s="12" customFormat="1" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A25" s="12" t="s">
         <v>1058</v>
       </c>
-      <c r="B26" s="32" t="s">
+      <c r="B25" s="32" t="s">
         <v>824</v>
       </c>
-      <c r="C26" s="16" t="s">
+      <c r="C25" s="16" t="s">
         <v>1063</v>
       </c>
-      <c r="D26" s="32" t="s">
-        <v>1081</v>
-      </c>
-      <c r="E26" s="12">
+      <c r="D25" s="32" t="s">
+        <v>1080</v>
+      </c>
+      <c r="E25" s="12">
         <v>17.715</v>
       </c>
-      <c r="F26" s="12">
+      <c r="F25" s="12">
         <v>16.850000000000001</v>
       </c>
-      <c r="G26" s="12">
+      <c r="G25" s="12">
         <f t="shared" si="3"/>
         <v>-4.88</v>
       </c>
-      <c r="H26" s="13" t="s">
-        <v>1067</v>
-      </c>
-      <c r="I26" s="13"/>
-      <c r="J26" s="37" t="s">
+      <c r="H25" s="13" t="s">
+        <v>1066</v>
+      </c>
+      <c r="I25" s="13"/>
+      <c r="J25" s="37" t="s">
         <v>784</v>
       </c>
-      <c r="K26" s="13" t="s">
-        <v>1079</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" s="42" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="42" t="s">
+      <c r="K25" s="13" t="s">
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" s="42" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="42" t="s">
         <v>515</v>
       </c>
-      <c r="B27" s="43" t="s">
+      <c r="B26" s="43" t="s">
         <v>822</v>
       </c>
-      <c r="C27" s="44" t="s">
+      <c r="C26" s="44" t="s">
         <v>829</v>
       </c>
-      <c r="D27" s="43" t="s">
+      <c r="D26" s="43" t="s">
         <v>1059</v>
       </c>
-      <c r="E27" s="42">
+      <c r="E26" s="42">
         <v>37.700000000000003</v>
       </c>
-      <c r="F27" s="42">
+      <c r="F26" s="42">
         <v>40.299999999999997</v>
       </c>
-      <c r="G27" s="42">
+      <c r="G26" s="42">
         <f t="shared" si="3"/>
         <v>6.9</v>
       </c>
-      <c r="H27" s="45" t="s">
+      <c r="H26" s="45" t="s">
         <v>819</v>
       </c>
-      <c r="I27" s="45">
+      <c r="I26" s="45">
         <v>49.9</v>
       </c>
-      <c r="J27" s="46" t="s">
+      <c r="J26" s="46" t="s">
         <v>784</v>
       </c>
-      <c r="K27" s="45" t="s">
+      <c r="K26" s="45" t="s">
         <v>1057</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B27" s="32" t="s">
+        <v>493</v>
+      </c>
+      <c r="C27" s="16">
+        <v>45992</v>
+      </c>
+      <c r="D27" s="32" t="s">
+        <v>1048</v>
+      </c>
+      <c r="E27" s="12">
+        <v>32.5</v>
+      </c>
+      <c r="F27" s="12">
+        <v>30.85</v>
+      </c>
+      <c r="G27" s="12">
+        <f t="shared" si="3"/>
+        <v>-5.08</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>1016</v>
+      </c>
+      <c r="I27" s="13">
+        <v>37.5</v>
+      </c>
+      <c r="J27" s="37" t="s">
+        <v>784</v>
+      </c>
+      <c r="K27" s="13" t="s">
+        <v>752</v>
       </c>
     </row>
     <row r="28" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B28" s="32" t="s">
-        <v>493</v>
-      </c>
-      <c r="C28" s="16">
-        <v>45992</v>
+        <v>830</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>1019</v>
       </c>
       <c r="D28" s="32" t="s">
-        <v>1048</v>
+        <v>1031</v>
       </c>
       <c r="E28" s="12">
-        <v>32.5</v>
+        <v>43.35</v>
       </c>
       <c r="F28" s="12">
-        <v>30.85</v>
+        <v>41.15</v>
       </c>
       <c r="G28" s="12">
-        <f t="shared" si="3"/>
-        <v>-5.08</v>
+        <f t="shared" ref="G28" si="4">ROUND((F28 - E28) / E28 * 100, 2)</f>
+        <v>-5.07</v>
       </c>
       <c r="H28" s="13" t="s">
-        <v>1016</v>
-      </c>
-      <c r="I28" s="13">
-        <v>37.5</v>
-      </c>
+        <v>1020</v>
+      </c>
+      <c r="I28" s="13"/>
       <c r="J28" s="37" t="s">
         <v>784</v>
       </c>
       <c r="K28" s="13" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="B29" s="32" t="s">
-        <v>830</v>
-      </c>
-      <c r="C29" s="16" t="s">
-        <v>1019</v>
-      </c>
-      <c r="D29" s="32" t="s">
-        <v>1031</v>
-      </c>
-      <c r="E29" s="12">
-        <v>43.35</v>
-      </c>
-      <c r="F29" s="12">
-        <v>41.15</v>
-      </c>
-      <c r="G29" s="12">
-        <f t="shared" ref="G29" si="4">ROUND((F29 - E29) / E29 * 100, 2)</f>
-        <v>-5.07</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>1020</v>
-      </c>
-      <c r="I29" s="13"/>
-      <c r="J29" s="37" t="s">
-        <v>784</v>
-      </c>
-      <c r="K29" s="13" t="s">
         <v>1029</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" s="10" customFormat="1" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A29" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" s="31" t="s">
+        <v>528</v>
+      </c>
+      <c r="C29" s="15">
+        <v>45809</v>
+      </c>
+      <c r="D29" s="31" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E29" s="10">
+        <v>66.653000000000006</v>
+      </c>
+      <c r="F29" s="10">
+        <v>67</v>
+      </c>
+      <c r="G29" s="10">
+        <f>ROUND((F29 - E29) / E29 * 100, 2)</f>
+        <v>0.52</v>
+      </c>
+      <c r="H29" s="7" t="s">
+        <v>1000</v>
+      </c>
+      <c r="I29" s="7"/>
+      <c r="J29" s="38"/>
+      <c r="K29" s="7" t="s">
+        <v>1015</v>
       </c>
     </row>
     <row r="30" spans="1:12" s="10" customFormat="1" ht="37.5" x14ac:dyDescent="0.25">
@@ -19800,11 +19973,11 @@
         <v>66.653000000000006</v>
       </c>
       <c r="F30" s="10">
-        <v>67</v>
+        <v>67.599999999999994</v>
       </c>
       <c r="G30" s="10">
-        <f>ROUND((F30 - E30) / E30 * 100, 2)</f>
-        <v>0.52</v>
+        <f t="shared" ref="G30" si="5">ROUND((F30 - E30) / E30 * 100, 2)</f>
+        <v>1.42</v>
       </c>
       <c r="H30" s="7" t="s">
         <v>1000</v>
@@ -19815,269 +19988,271 @@
         <v>1015</v>
       </c>
     </row>
-    <row r="31" spans="1:12" s="10" customFormat="1" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
-        <v>35</v>
+        <v>768</v>
       </c>
       <c r="B31" s="31" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="C31" s="15">
-        <v>45809</v>
+        <v>46003</v>
       </c>
       <c r="D31" s="31" t="s">
-        <v>1018</v>
+        <v>1014</v>
       </c>
       <c r="E31" s="10">
-        <v>66.653000000000006</v>
+        <v>92.1</v>
       </c>
       <c r="F31" s="10">
-        <v>67.599999999999994</v>
+        <v>92.6</v>
       </c>
       <c r="G31" s="10">
-        <f t="shared" ref="G31" si="5">ROUND((F31 - E31) / E31 * 100, 2)</f>
-        <v>1.42</v>
+        <f t="shared" ref="G31" si="6">ROUND((F31 - E31) / E31 * 100, 2)</f>
+        <v>0.54</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>1000</v>
-      </c>
-      <c r="I31" s="7"/>
+        <v>951</v>
+      </c>
+      <c r="I31" s="7">
+        <v>108</v>
+      </c>
       <c r="J31" s="38"/>
       <c r="K31" s="7" t="s">
-        <v>1015</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="10" t="s">
-        <v>768</v>
-      </c>
-      <c r="B32" s="31" t="s">
-        <v>533</v>
-      </c>
-      <c r="C32" s="15">
-        <v>46003</v>
-      </c>
-      <c r="D32" s="31" t="s">
-        <v>1014</v>
-      </c>
-      <c r="E32" s="10">
-        <v>92.1</v>
-      </c>
-      <c r="F32" s="10">
-        <v>92.6</v>
-      </c>
-      <c r="G32" s="10">
-        <f t="shared" ref="G32" si="6">ROUND((F32 - E32) / E32 * 100, 2)</f>
-        <v>0.54</v>
-      </c>
-      <c r="H32" s="7" t="s">
-        <v>951</v>
-      </c>
-      <c r="I32" s="7">
-        <v>108</v>
-      </c>
-      <c r="J32" s="38"/>
-      <c r="K32" s="7" t="s">
         <v>1012</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B32" s="32" t="s">
+        <v>587</v>
+      </c>
+      <c r="C32" s="16">
+        <v>45669</v>
+      </c>
+      <c r="D32" s="32"/>
+      <c r="E32" s="12">
+        <v>48.85</v>
+      </c>
+      <c r="F32" s="12">
+        <v>48.5</v>
+      </c>
+      <c r="G32" s="12">
+        <f t="shared" ref="G32" si="7">ROUND((F32 - E32) / E32 * 100, 2)</f>
+        <v>-0.72</v>
+      </c>
+      <c r="H32" s="13" t="s">
+        <v>923</v>
+      </c>
+      <c r="I32" s="13">
+        <v>59.5</v>
+      </c>
+      <c r="J32" s="37" t="s">
+        <v>784</v>
+      </c>
+      <c r="K32" s="13" t="s">
+        <v>1006</v>
       </c>
     </row>
     <row r="33" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="s">
-        <v>20</v>
+        <v>780</v>
       </c>
       <c r="B33" s="32" t="s">
-        <v>587</v>
+        <v>894</v>
       </c>
       <c r="C33" s="16">
-        <v>45669</v>
-      </c>
-      <c r="D33" s="32"/>
+        <v>45942</v>
+      </c>
+      <c r="D33" s="32" t="s">
+        <v>999</v>
+      </c>
       <c r="E33" s="12">
-        <v>48.85</v>
+        <v>11</v>
       </c>
       <c r="F33" s="12">
-        <v>48.5</v>
+        <v>9.9499999999999993</v>
       </c>
       <c r="G33" s="12">
-        <f t="shared" ref="G33" si="7">ROUND((F33 - E33) / E33 * 100, 2)</f>
-        <v>-0.72</v>
+        <f>ROUND((F33 - E33) / E33 * 100, 2)</f>
+        <v>-9.5500000000000007</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>923</v>
-      </c>
-      <c r="I33" s="13">
-        <v>59.5</v>
-      </c>
+        <v>947</v>
+      </c>
+      <c r="I33" s="13"/>
       <c r="J33" s="37" t="s">
-        <v>784</v>
+        <v>997</v>
       </c>
       <c r="K33" s="13" t="s">
-        <v>1006</v>
+        <v>996</v>
       </c>
     </row>
     <row r="34" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="12" t="s">
-        <v>780</v>
+        <v>30</v>
       </c>
       <c r="B34" s="32" t="s">
-        <v>894</v>
-      </c>
-      <c r="C34" s="16">
-        <v>45942</v>
+        <v>994</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>973</v>
       </c>
       <c r="D34" s="32" t="s">
         <v>999</v>
       </c>
       <c r="E34" s="12">
-        <v>11</v>
+        <v>34.270000000000003</v>
       </c>
       <c r="F34" s="12">
-        <v>9.9499999999999993</v>
+        <v>31.3</v>
       </c>
       <c r="G34" s="12">
         <f>ROUND((F34 - E34) / E34 * 100, 2)</f>
-        <v>-9.5500000000000007</v>
+        <v>-8.67</v>
       </c>
       <c r="H34" s="13" t="s">
-        <v>947</v>
+        <v>974</v>
       </c>
       <c r="I34" s="13"/>
       <c r="J34" s="37" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="K34" s="13" t="s">
-        <v>996</v>
+        <v>752</v>
       </c>
     </row>
     <row r="35" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="12" t="s">
-        <v>30</v>
+        <v>953</v>
       </c>
       <c r="B35" s="32" t="s">
-        <v>994</v>
-      </c>
-      <c r="C35" s="12" t="s">
-        <v>973</v>
+        <v>954</v>
+      </c>
+      <c r="C35" s="16">
+        <v>46003</v>
       </c>
       <c r="D35" s="32" t="s">
-        <v>999</v>
+        <v>985</v>
       </c>
       <c r="E35" s="12">
-        <v>34.270000000000003</v>
+        <v>28.75</v>
       </c>
       <c r="F35" s="12">
-        <v>31.3</v>
+        <v>27.35</v>
       </c>
       <c r="G35" s="12">
         <f>ROUND((F35 - E35) / E35 * 100, 2)</f>
-        <v>-8.67</v>
+        <v>-4.87</v>
       </c>
       <c r="H35" s="13" t="s">
-        <v>974</v>
-      </c>
-      <c r="I35" s="13"/>
+        <v>955</v>
+      </c>
+      <c r="I35" s="13">
+        <v>32.200000000000003</v>
+      </c>
       <c r="J35" s="37" t="s">
-        <v>998</v>
+        <v>784</v>
       </c>
       <c r="K35" s="13" t="s">
-        <v>752</v>
+        <v>757</v>
       </c>
     </row>
     <row r="36" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="12" t="s">
-        <v>953</v>
+        <v>34</v>
       </c>
       <c r="B36" s="32" t="s">
-        <v>954</v>
-      </c>
-      <c r="C36" s="16">
-        <v>46003</v>
+        <v>718</v>
+      </c>
+      <c r="C36" s="12" t="s">
+        <v>966</v>
       </c>
       <c r="D36" s="32" t="s">
-        <v>985</v>
+        <v>980</v>
       </c>
       <c r="E36" s="12">
-        <v>28.75</v>
+        <v>27.872</v>
       </c>
       <c r="F36" s="12">
-        <v>27.35</v>
+        <v>26.5</v>
       </c>
       <c r="G36" s="12">
         <f>ROUND((F36 - E36) / E36 * 100, 2)</f>
-        <v>-4.87</v>
+        <v>-4.92</v>
       </c>
       <c r="H36" s="13" t="s">
-        <v>955</v>
-      </c>
-      <c r="I36" s="13">
-        <v>32.200000000000003</v>
-      </c>
+        <v>967</v>
+      </c>
+      <c r="I36" s="13"/>
       <c r="J36" s="37" t="s">
         <v>784</v>
       </c>
       <c r="K36" s="13" t="s">
-        <v>757</v>
+        <v>970</v>
       </c>
     </row>
     <row r="37" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="B37" s="32" t="s">
-        <v>718</v>
-      </c>
-      <c r="C37" s="12" t="s">
-        <v>966</v>
+        <v>529</v>
+      </c>
+      <c r="C37" s="16">
+        <v>45881</v>
       </c>
       <c r="D37" s="32" t="s">
-        <v>980</v>
+        <v>958</v>
       </c>
       <c r="E37" s="12">
-        <v>27.872</v>
+        <v>4.8040000000000003</v>
       </c>
       <c r="F37" s="12">
-        <v>26.5</v>
+        <v>4.5599999999999996</v>
       </c>
       <c r="G37" s="12">
         <f>ROUND((F37 - E37) / E37 * 100, 2)</f>
-        <v>-4.92</v>
+        <v>-5.08</v>
       </c>
       <c r="H37" s="13" t="s">
-        <v>967</v>
+        <v>938</v>
       </c>
       <c r="I37" s="13"/>
       <c r="J37" s="37" t="s">
         <v>784</v>
       </c>
       <c r="K37" s="13" t="s">
-        <v>970</v>
+        <v>752</v>
       </c>
     </row>
     <row r="38" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="12" t="s">
-        <v>41</v>
+        <v>736</v>
       </c>
       <c r="B38" s="32" t="s">
-        <v>529</v>
-      </c>
-      <c r="C38" s="16">
-        <v>45881</v>
+        <v>754</v>
+      </c>
+      <c r="C38" s="12" t="s">
+        <v>907</v>
       </c>
       <c r="D38" s="32" t="s">
         <v>958</v>
       </c>
       <c r="E38" s="12">
-        <v>4.8040000000000003</v>
+        <v>12.41</v>
       </c>
       <c r="F38" s="12">
-        <v>4.5599999999999996</v>
+        <v>11.8</v>
       </c>
       <c r="G38" s="12">
-        <f>ROUND((F38 - E38) / E38 * 100, 2)</f>
-        <v>-5.08</v>
+        <f t="shared" ref="G38" si="8">ROUND((F38 - E38) / E38 * 100, 2)</f>
+        <v>-4.92</v>
       </c>
       <c r="H38" s="13" t="s">
-        <v>938</v>
+        <v>893</v>
       </c>
       <c r="I38" s="13"/>
       <c r="J38" s="37" t="s">
@@ -20089,608 +20264,613 @@
     </row>
     <row r="39" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="12" t="s">
-        <v>736</v>
+        <v>396</v>
       </c>
       <c r="B39" s="32" t="s">
-        <v>754</v>
-      </c>
-      <c r="C39" s="12" t="s">
-        <v>907</v>
+        <v>930</v>
+      </c>
+      <c r="C39" s="16">
+        <v>45759</v>
       </c>
       <c r="D39" s="32" t="s">
-        <v>958</v>
+        <v>952</v>
       </c>
       <c r="E39" s="12">
-        <v>12.41</v>
+        <v>29.524000000000001</v>
       </c>
       <c r="F39" s="12">
-        <v>11.8</v>
+        <v>26.4</v>
       </c>
       <c r="G39" s="12">
-        <f t="shared" ref="G39" si="8">ROUND((F39 - E39) / E39 * 100, 2)</f>
-        <v>-4.92</v>
+        <f>ROUND((F39 - E39) / E39 * 100, 2)</f>
+        <v>-10.58</v>
       </c>
       <c r="H39" s="13" t="s">
-        <v>893</v>
+        <v>931</v>
       </c>
       <c r="I39" s="13"/>
-      <c r="J39" s="37" t="s">
-        <v>784</v>
-      </c>
+      <c r="J39" s="37"/>
       <c r="K39" s="13" t="s">
-        <v>752</v>
+        <v>944</v>
       </c>
     </row>
     <row r="40" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="12" t="s">
-        <v>396</v>
+        <v>11</v>
       </c>
       <c r="B40" s="32" t="s">
-        <v>930</v>
-      </c>
-      <c r="C40" s="16">
-        <v>45759</v>
+        <v>587</v>
+      </c>
+      <c r="C40" s="16" t="s">
+        <v>836</v>
       </c>
       <c r="D40" s="32" t="s">
         <v>952</v>
       </c>
       <c r="E40" s="12">
-        <v>29.524000000000001</v>
+        <v>93.1</v>
       </c>
       <c r="F40" s="12">
-        <v>26.4</v>
+        <v>93</v>
       </c>
       <c r="G40" s="12">
         <f>ROUND((F40 - E40) / E40 * 100, 2)</f>
-        <v>-10.58</v>
+        <v>-0.11</v>
       </c>
       <c r="H40" s="13" t="s">
-        <v>931</v>
-      </c>
-      <c r="I40" s="13"/>
-      <c r="J40" s="37"/>
+        <v>760</v>
+      </c>
+      <c r="I40" s="13">
+        <v>107</v>
+      </c>
+      <c r="J40" s="37" t="s">
+        <v>945</v>
+      </c>
       <c r="K40" s="13" t="s">
-        <v>944</v>
+        <v>949</v>
       </c>
     </row>
     <row r="41" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="12" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B41" s="32" t="s">
-        <v>587</v>
-      </c>
-      <c r="C41" s="16" t="s">
-        <v>836</v>
+        <v>908</v>
+      </c>
+      <c r="C41" s="12" t="s">
+        <v>907</v>
       </c>
       <c r="D41" s="32" t="s">
         <v>952</v>
       </c>
       <c r="E41" s="12">
-        <v>93.1</v>
+        <v>28.93</v>
       </c>
       <c r="F41" s="12">
-        <v>93</v>
+        <v>27.5</v>
       </c>
       <c r="G41" s="12">
-        <f>ROUND((F41 - E41) / E41 * 100, 2)</f>
-        <v>-0.11</v>
+        <f t="shared" ref="G41" si="9">ROUND((F41 - E41) / E41 * 100, 2)</f>
+        <v>-4.9400000000000004</v>
       </c>
       <c r="H41" s="13" t="s">
-        <v>760</v>
+        <v>893</v>
       </c>
       <c r="I41" s="13">
-        <v>107</v>
+        <v>33.799999999999997</v>
       </c>
       <c r="J41" s="37" t="s">
-        <v>945</v>
+        <v>784</v>
       </c>
       <c r="K41" s="13" t="s">
-        <v>949</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="B42" s="32" t="s">
-        <v>908</v>
-      </c>
-      <c r="C42" s="12" t="s">
-        <v>907</v>
+        <v>811</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="10" t="s">
+        <v>780</v>
+      </c>
+      <c r="B42" s="31" t="s">
+        <v>894</v>
+      </c>
+      <c r="C42" s="10" t="s">
+        <v>892</v>
       </c>
       <c r="D42" s="32" t="s">
-        <v>952</v>
-      </c>
-      <c r="E42" s="12">
-        <v>28.93</v>
-      </c>
-      <c r="F42" s="12">
-        <v>27.5</v>
-      </c>
-      <c r="G42" s="12">
-        <f t="shared" ref="G42" si="9">ROUND((F42 - E42) / E42 * 100, 2)</f>
-        <v>-4.9400000000000004</v>
-      </c>
-      <c r="H42" s="13" t="s">
+        <v>942</v>
+      </c>
+      <c r="E42" s="10">
+        <v>10.507999999999999</v>
+      </c>
+      <c r="F42" s="10">
+        <v>11.25</v>
+      </c>
+      <c r="G42" s="10">
+        <f t="shared" ref="G42" si="10">ROUND((F42 - E42) / E42 * 100, 2)</f>
+        <v>7.06</v>
+      </c>
+      <c r="H42" s="7" t="s">
         <v>893</v>
       </c>
-      <c r="I42" s="13">
-        <v>33.799999999999997</v>
-      </c>
-      <c r="J42" s="37" t="s">
+      <c r="I42" s="7">
+        <v>11.6</v>
+      </c>
+      <c r="J42" s="38" t="s">
         <v>784</v>
       </c>
-      <c r="K42" s="13" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="10" t="s">
-        <v>780</v>
-      </c>
-      <c r="B43" s="31" t="s">
-        <v>894</v>
-      </c>
-      <c r="C43" s="10" t="s">
-        <v>892</v>
+      <c r="K42" s="7" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B43" s="32" t="s">
+        <v>493</v>
+      </c>
+      <c r="C43" s="12" t="s">
+        <v>912</v>
       </c>
       <c r="D43" s="32" t="s">
         <v>942</v>
       </c>
-      <c r="E43" s="10">
-        <v>10.507999999999999</v>
-      </c>
-      <c r="F43" s="10">
-        <v>11.25</v>
-      </c>
-      <c r="G43" s="10">
-        <f t="shared" ref="G43" si="10">ROUND((F43 - E43) / E43 * 100, 2)</f>
-        <v>7.06</v>
-      </c>
-      <c r="H43" s="7" t="s">
-        <v>893</v>
-      </c>
-      <c r="I43" s="7">
-        <v>11.6</v>
-      </c>
-      <c r="J43" s="38" t="s">
+      <c r="E43" s="12">
+        <v>43.435000000000002</v>
+      </c>
+      <c r="F43" s="12">
+        <v>41.25</v>
+      </c>
+      <c r="G43" s="12">
+        <f>ROUND((F43 - E43) / E43 * 100, 2)</f>
+        <v>-5.03</v>
+      </c>
+      <c r="H43" s="13" t="s">
+        <v>915</v>
+      </c>
+      <c r="I43" s="13">
+        <v>48.5</v>
+      </c>
+      <c r="J43" s="37" t="s">
         <v>784</v>
       </c>
-      <c r="K43" s="7" t="s">
-        <v>940</v>
+      <c r="K43" s="13" t="s">
+        <v>941</v>
       </c>
     </row>
     <row r="44" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="12" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B44" s="32" t="s">
-        <v>493</v>
+        <v>625</v>
       </c>
       <c r="C44" s="12" t="s">
         <v>912</v>
       </c>
       <c r="D44" s="32" t="s">
-        <v>942</v>
+        <v>937</v>
       </c>
       <c r="E44" s="12">
-        <v>43.435000000000002</v>
+        <v>45.936999999999998</v>
       </c>
       <c r="F44" s="12">
-        <v>41.25</v>
+        <v>43.65</v>
       </c>
       <c r="G44" s="12">
         <f>ROUND((F44 - E44) / E44 * 100, 2)</f>
-        <v>-5.03</v>
+        <v>-4.9800000000000004</v>
       </c>
       <c r="H44" s="13" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="I44" s="13">
-        <v>48.5</v>
+        <v>52.5</v>
       </c>
       <c r="J44" s="37" t="s">
         <v>784</v>
       </c>
       <c r="K44" s="13" t="s">
-        <v>941</v>
+        <v>936</v>
       </c>
     </row>
     <row r="45" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="12" t="s">
-        <v>22</v>
+        <v>735</v>
       </c>
       <c r="B45" s="32" t="s">
-        <v>625</v>
-      </c>
-      <c r="C45" s="12" t="s">
-        <v>912</v>
+        <v>822</v>
+      </c>
+      <c r="C45" s="16">
+        <v>45819</v>
       </c>
       <c r="D45" s="32" t="s">
-        <v>937</v>
+        <v>922</v>
       </c>
       <c r="E45" s="12">
-        <v>45.936999999999998</v>
+        <v>31.475000000000001</v>
       </c>
       <c r="F45" s="12">
-        <v>43.65</v>
+        <v>30.8</v>
       </c>
       <c r="G45" s="12">
-        <f>ROUND((F45 - E45) / E45 * 100, 2)</f>
-        <v>-4.9800000000000004</v>
+        <f t="shared" ref="G45" si="11">ROUND((F45 - E45) / E45 * 100, 2)</f>
+        <v>-2.14</v>
       </c>
       <c r="H45" s="13" t="s">
-        <v>914</v>
+        <v>835</v>
       </c>
       <c r="I45" s="13">
-        <v>52.5</v>
+        <v>35.35</v>
       </c>
       <c r="J45" s="37" t="s">
         <v>784</v>
       </c>
       <c r="K45" s="13" t="s">
-        <v>936</v>
+        <v>918</v>
       </c>
     </row>
     <row r="46" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="12" t="s">
-        <v>735</v>
+        <v>107</v>
       </c>
       <c r="B46" s="32" t="s">
-        <v>822</v>
+        <v>879</v>
       </c>
       <c r="C46" s="16">
-        <v>45819</v>
-      </c>
-      <c r="D46" s="32" t="s">
-        <v>922</v>
+        <v>45941</v>
+      </c>
+      <c r="D46" s="16" t="s">
+        <v>911</v>
       </c>
       <c r="E46" s="12">
-        <v>31.475000000000001</v>
+        <v>16.914999999999999</v>
       </c>
       <c r="F46" s="12">
-        <v>30.8</v>
+        <v>16.05</v>
       </c>
       <c r="G46" s="12">
-        <f t="shared" ref="G46" si="11">ROUND((F46 - E46) / E46 * 100, 2)</f>
-        <v>-2.14</v>
+        <f t="shared" ref="G46:G59" si="12">ROUND((F46 - E46) / E46 * 100, 2)</f>
+        <v>-5.1100000000000003</v>
       </c>
       <c r="H46" s="13" t="s">
-        <v>835</v>
+        <v>843</v>
       </c>
       <c r="I46" s="13">
-        <v>35.35</v>
+        <v>19.5</v>
       </c>
       <c r="J46" s="37" t="s">
         <v>784</v>
       </c>
       <c r="K46" s="13" t="s">
-        <v>918</v>
+        <v>909</v>
       </c>
     </row>
     <row r="47" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="12" t="s">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="B47" s="32" t="s">
-        <v>879</v>
-      </c>
-      <c r="C47" s="16">
-        <v>45941</v>
+        <v>489</v>
+      </c>
+      <c r="C47" s="12" t="s">
+        <v>892</v>
       </c>
       <c r="D47" s="16" t="s">
         <v>911</v>
       </c>
       <c r="E47" s="12">
-        <v>16.914999999999999</v>
+        <v>21.016999999999999</v>
       </c>
       <c r="F47" s="12">
-        <v>16.05</v>
+        <v>19.95</v>
       </c>
       <c r="G47" s="12">
-        <f t="shared" ref="G47:G60" si="12">ROUND((F47 - E47) / E47 * 100, 2)</f>
-        <v>-5.1100000000000003</v>
+        <f t="shared" si="12"/>
+        <v>-5.08</v>
       </c>
       <c r="H47" s="13" t="s">
-        <v>843</v>
+        <v>893</v>
       </c>
       <c r="I47" s="13">
-        <v>19.5</v>
+        <v>24.6</v>
       </c>
       <c r="J47" s="37" t="s">
         <v>784</v>
       </c>
       <c r="K47" s="13" t="s">
-        <v>909</v>
+        <v>758</v>
       </c>
     </row>
     <row r="48" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="12" t="s">
-        <v>10</v>
+        <v>842</v>
       </c>
       <c r="B48" s="32" t="s">
-        <v>489</v>
-      </c>
-      <c r="C48" s="12" t="s">
-        <v>892</v>
-      </c>
-      <c r="D48" s="16" t="s">
-        <v>911</v>
-      </c>
+        <v>731</v>
+      </c>
+      <c r="C48" s="16" t="s">
+        <v>841</v>
+      </c>
+      <c r="D48" s="32"/>
       <c r="E48" s="12">
-        <v>21.016999999999999</v>
+        <v>54.65</v>
       </c>
       <c r="F48" s="12">
-        <v>19.95</v>
+        <v>53.4</v>
       </c>
       <c r="G48" s="12">
         <f t="shared" si="12"/>
-        <v>-5.08</v>
+        <v>-2.29</v>
       </c>
       <c r="H48" s="13" t="s">
-        <v>893</v>
+        <v>843</v>
       </c>
       <c r="I48" s="13">
-        <v>24.6</v>
+        <v>60</v>
       </c>
       <c r="J48" s="37" t="s">
         <v>784</v>
       </c>
       <c r="K48" s="13" t="s">
-        <v>758</v>
+        <v>752</v>
       </c>
     </row>
     <row r="49" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="12" t="s">
-        <v>842</v>
+        <v>821</v>
       </c>
       <c r="B49" s="32" t="s">
-        <v>731</v>
+        <v>822</v>
       </c>
       <c r="C49" s="16" t="s">
-        <v>841</v>
-      </c>
-      <c r="D49" s="32"/>
+        <v>820</v>
+      </c>
+      <c r="D49" s="32" t="s">
+        <v>907</v>
+      </c>
       <c r="E49" s="12">
-        <v>54.65</v>
+        <v>34.33</v>
       </c>
       <c r="F49" s="12">
-        <v>53.4</v>
+        <v>33.9</v>
       </c>
       <c r="G49" s="12">
         <f t="shared" si="12"/>
-        <v>-2.29</v>
+        <v>-1.25</v>
       </c>
       <c r="H49" s="13" t="s">
-        <v>843</v>
-      </c>
-      <c r="I49" s="13">
-        <v>60</v>
+        <v>819</v>
+      </c>
+      <c r="I49" s="13" t="s">
+        <v>897</v>
       </c>
       <c r="J49" s="37" t="s">
         <v>784</v>
       </c>
       <c r="K49" s="13" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" s="12" customFormat="1" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A50" s="12" t="s">
-        <v>821</v>
+        <v>35</v>
       </c>
       <c r="B50" s="32" t="s">
-        <v>822</v>
-      </c>
-      <c r="C50" s="16" t="s">
-        <v>820</v>
+        <v>871</v>
+      </c>
+      <c r="C50" s="16">
+        <v>45819</v>
       </c>
       <c r="D50" s="32" t="s">
-        <v>907</v>
+        <v>903</v>
       </c>
       <c r="E50" s="12">
-        <v>34.33</v>
+        <v>68.954999999999998</v>
       </c>
       <c r="F50" s="12">
-        <v>33.9</v>
+        <v>65.5</v>
       </c>
       <c r="G50" s="12">
         <f t="shared" si="12"/>
-        <v>-1.25</v>
+        <v>-5.01</v>
       </c>
       <c r="H50" s="13" t="s">
-        <v>819</v>
-      </c>
-      <c r="I50" s="13" t="s">
-        <v>897</v>
+        <v>872</v>
+      </c>
+      <c r="I50" s="13">
+        <v>78</v>
       </c>
       <c r="J50" s="37" t="s">
         <v>784</v>
       </c>
       <c r="K50" s="13" t="s">
-        <v>906</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" s="12" customFormat="1" ht="37.5" x14ac:dyDescent="0.25">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="12" t="s">
-        <v>35</v>
+        <v>823</v>
       </c>
       <c r="B51" s="32" t="s">
-        <v>871</v>
-      </c>
-      <c r="C51" s="16">
-        <v>45819</v>
+        <v>731</v>
+      </c>
+      <c r="C51" s="16" t="s">
+        <v>852</v>
       </c>
       <c r="D51" s="32" t="s">
-        <v>903</v>
+        <v>889</v>
       </c>
       <c r="E51" s="12">
-        <v>68.954999999999998</v>
+        <v>17.965</v>
       </c>
       <c r="F51" s="12">
-        <v>65.5</v>
+        <v>17.05</v>
       </c>
       <c r="G51" s="12">
         <f t="shared" si="12"/>
-        <v>-5.01</v>
+        <v>-5.09</v>
       </c>
       <c r="H51" s="13" t="s">
-        <v>872</v>
-      </c>
-      <c r="I51" s="13">
-        <v>78</v>
+        <v>853</v>
+      </c>
+      <c r="I51" s="13" t="s">
+        <v>886</v>
       </c>
       <c r="J51" s="37" t="s">
         <v>784</v>
       </c>
       <c r="K51" s="13" t="s">
-        <v>757</v>
+        <v>887</v>
       </c>
     </row>
     <row r="52" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="12" t="s">
-        <v>823</v>
+        <v>107</v>
       </c>
       <c r="B52" s="32" t="s">
-        <v>731</v>
-      </c>
-      <c r="C52" s="16" t="s">
-        <v>852</v>
+        <v>867</v>
+      </c>
+      <c r="C52" s="16">
+        <v>45788</v>
       </c>
       <c r="D52" s="32" t="s">
-        <v>889</v>
+        <v>878</v>
       </c>
       <c r="E52" s="12">
-        <v>17.965</v>
+        <v>17.114000000000001</v>
       </c>
       <c r="F52" s="12">
-        <v>17.05</v>
+        <v>16.25</v>
       </c>
       <c r="G52" s="12">
         <f t="shared" si="12"/>
-        <v>-5.09</v>
+        <v>-5.05</v>
       </c>
       <c r="H52" s="13" t="s">
-        <v>853</v>
-      </c>
-      <c r="I52" s="13" t="s">
-        <v>886</v>
-      </c>
+        <v>868</v>
+      </c>
+      <c r="I52" s="13"/>
       <c r="J52" s="37" t="s">
         <v>784</v>
       </c>
       <c r="K52" s="13" t="s">
-        <v>887</v>
+        <v>874</v>
       </c>
     </row>
     <row r="53" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="12" t="s">
-        <v>107</v>
+        <v>13</v>
       </c>
       <c r="B53" s="32" t="s">
-        <v>867</v>
+        <v>686</v>
       </c>
       <c r="C53" s="16">
-        <v>45788</v>
+        <v>45727</v>
       </c>
       <c r="D53" s="32" t="s">
-        <v>878</v>
+        <v>870</v>
       </c>
       <c r="E53" s="12">
-        <v>17.114000000000001</v>
+        <v>40.131999999999998</v>
       </c>
       <c r="F53" s="12">
-        <v>16.25</v>
+        <v>39.049999999999997</v>
       </c>
       <c r="G53" s="12">
         <f t="shared" si="12"/>
-        <v>-5.05</v>
+        <v>-2.7</v>
       </c>
       <c r="H53" s="13" t="s">
-        <v>868</v>
-      </c>
-      <c r="I53" s="13"/>
+        <v>860</v>
+      </c>
+      <c r="I53" s="13">
+        <v>45.4</v>
+      </c>
       <c r="J53" s="37" t="s">
         <v>784</v>
       </c>
       <c r="K53" s="13" t="s">
-        <v>874</v>
+        <v>796</v>
       </c>
     </row>
     <row r="54" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="12" t="s">
-        <v>13</v>
+        <v>863</v>
       </c>
       <c r="B54" s="32" t="s">
-        <v>686</v>
+        <v>776</v>
       </c>
       <c r="C54" s="16">
-        <v>45727</v>
+        <v>45758</v>
       </c>
       <c r="D54" s="32" t="s">
         <v>870</v>
       </c>
       <c r="E54" s="12">
-        <v>40.131999999999998</v>
+        <v>25.971</v>
       </c>
       <c r="F54" s="12">
-        <v>39.049999999999997</v>
+        <v>25.45</v>
       </c>
       <c r="G54" s="12">
         <f t="shared" si="12"/>
-        <v>-2.7</v>
+        <v>-2.0099999999999998</v>
       </c>
       <c r="H54" s="13" t="s">
-        <v>860</v>
-      </c>
-      <c r="I54" s="13">
-        <v>45.4</v>
-      </c>
-      <c r="J54" s="37" t="s">
-        <v>784</v>
-      </c>
+        <v>760</v>
+      </c>
+      <c r="I54" s="13"/>
+      <c r="J54" s="37"/>
       <c r="K54" s="13" t="s">
-        <v>796</v>
+        <v>752</v>
       </c>
     </row>
     <row r="55" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="12" t="s">
-        <v>863</v>
+        <v>30</v>
       </c>
       <c r="B55" s="32" t="s">
-        <v>776</v>
-      </c>
-      <c r="C55" s="16">
-        <v>45758</v>
+        <v>510</v>
+      </c>
+      <c r="C55" s="16" t="s">
+        <v>836</v>
       </c>
       <c r="D55" s="32" t="s">
-        <v>870</v>
+        <v>862</v>
       </c>
       <c r="E55" s="12">
-        <v>25.971</v>
+        <v>35.078000000000003</v>
       </c>
       <c r="F55" s="12">
-        <v>25.45</v>
+        <v>33.299999999999997</v>
       </c>
       <c r="G55" s="12">
         <f t="shared" si="12"/>
-        <v>-2.0099999999999998</v>
+        <v>-5.07</v>
       </c>
       <c r="H55" s="13" t="s">
         <v>760</v>
       </c>
-      <c r="I55" s="13"/>
-      <c r="J55" s="37"/>
+      <c r="I55" s="13">
+        <v>38</v>
+      </c>
+      <c r="J55" s="37" t="s">
+        <v>784</v>
+      </c>
       <c r="K55" s="13" t="s">
-        <v>752</v>
+        <v>859</v>
+      </c>
+      <c r="L55" s="12" t="s">
+        <v>865</v>
       </c>
     </row>
     <row r="56" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="12" t="s">
-        <v>30</v>
+        <v>655</v>
       </c>
       <c r="B56" s="32" t="s">
-        <v>510</v>
+        <v>587</v>
       </c>
       <c r="C56" s="16" t="s">
         <v>836</v>
@@ -20699,398 +20879,395 @@
         <v>862</v>
       </c>
       <c r="E56" s="12">
-        <v>35.078000000000003</v>
+        <v>93.674999999999997</v>
       </c>
       <c r="F56" s="12">
-        <v>33.299999999999997</v>
+        <v>89</v>
       </c>
       <c r="G56" s="12">
         <f t="shared" si="12"/>
-        <v>-5.07</v>
-      </c>
-      <c r="H56" s="13" t="s">
-        <v>760</v>
-      </c>
+        <v>-4.99</v>
+      </c>
+      <c r="H56" s="13"/>
       <c r="I56" s="13">
-        <v>38</v>
+        <v>101</v>
       </c>
       <c r="J56" s="37" t="s">
         <v>784</v>
       </c>
       <c r="K56" s="13" t="s">
-        <v>859</v>
-      </c>
-      <c r="L56" s="12" t="s">
-        <v>865</v>
+        <v>858</v>
       </c>
     </row>
     <row r="57" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="12" t="s">
-        <v>655</v>
+        <v>37</v>
       </c>
       <c r="B57" s="32" t="s">
-        <v>587</v>
+        <v>846</v>
       </c>
       <c r="C57" s="16" t="s">
-        <v>836</v>
+        <v>845</v>
       </c>
       <c r="D57" s="32" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="E57" s="12">
-        <v>93.674999999999997</v>
+        <v>13.51</v>
       </c>
       <c r="F57" s="12">
-        <v>89</v>
+        <v>12.8</v>
       </c>
       <c r="G57" s="12">
         <f t="shared" si="12"/>
-        <v>-4.99</v>
-      </c>
-      <c r="H57" s="13"/>
-      <c r="I57" s="13">
-        <v>101</v>
-      </c>
+        <v>-5.26</v>
+      </c>
+      <c r="H57" s="13" t="s">
+        <v>847</v>
+      </c>
+      <c r="I57" s="13"/>
       <c r="J57" s="37" t="s">
         <v>784</v>
       </c>
       <c r="K57" s="13" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="B58" s="32" t="s">
-        <v>846</v>
-      </c>
-      <c r="C58" s="16" t="s">
-        <v>845</v>
-      </c>
-      <c r="D58" s="32" t="s">
-        <v>857</v>
-      </c>
-      <c r="E58" s="12">
-        <v>13.51</v>
-      </c>
-      <c r="F58" s="12">
-        <v>12.8</v>
-      </c>
-      <c r="G58" s="12">
-        <f t="shared" si="12"/>
-        <v>-5.26</v>
-      </c>
-      <c r="H58" s="13" t="s">
-        <v>847</v>
-      </c>
-      <c r="I58" s="13"/>
-      <c r="J58" s="37" t="s">
-        <v>784</v>
-      </c>
-      <c r="K58" s="13" t="s">
         <v>856</v>
       </c>
     </row>
-    <row r="59" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="10" t="s">
+    <row r="58" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="10" t="s">
         <v>823</v>
       </c>
-      <c r="B59" s="31" t="s">
+      <c r="B58" s="31" t="s">
         <v>824</v>
       </c>
-      <c r="C59" s="15" t="s">
+      <c r="C58" s="15" t="s">
         <v>820</v>
       </c>
-      <c r="D59" s="15" t="s">
+      <c r="D58" s="15" t="s">
         <v>850</v>
       </c>
-      <c r="E59" s="10">
+      <c r="E58" s="10">
         <v>16.559999999999999</v>
       </c>
-      <c r="F59" s="10">
+      <c r="F58" s="10">
         <v>17.75</v>
       </c>
-      <c r="G59" s="10">
+      <c r="G58" s="10">
         <f t="shared" si="12"/>
         <v>7.19</v>
       </c>
-      <c r="H59" s="7" t="s">
+      <c r="H58" s="7" t="s">
         <v>819</v>
       </c>
-      <c r="I59" s="7">
+      <c r="I58" s="7">
         <v>17.75</v>
       </c>
-      <c r="J59" s="38" t="s">
+      <c r="J58" s="38" t="s">
         <v>784</v>
       </c>
-      <c r="K59" s="7" t="s">
+      <c r="K58" s="7" t="s">
         <v>837</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="12" t="s">
+        <v>827</v>
+      </c>
+      <c r="B59" s="32" t="s">
+        <v>533</v>
+      </c>
+      <c r="C59" s="16" t="s">
+        <v>826</v>
+      </c>
+      <c r="D59" s="32" t="s">
+        <v>841</v>
+      </c>
+      <c r="E59" s="12">
+        <v>113.3</v>
+      </c>
+      <c r="F59" s="12">
+        <v>104</v>
+      </c>
+      <c r="G59" s="12">
+        <f t="shared" si="12"/>
+        <v>-8.2100000000000009</v>
+      </c>
+      <c r="H59" s="13" t="s">
+        <v>819</v>
+      </c>
+      <c r="I59" s="13"/>
+      <c r="J59" s="37" t="s">
+        <v>840</v>
+      </c>
+      <c r="K59" s="13" t="s">
+        <v>838</v>
       </c>
     </row>
     <row r="60" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="12" t="s">
-        <v>827</v>
+        <v>24</v>
       </c>
       <c r="B60" s="32" t="s">
-        <v>533</v>
+        <v>776</v>
       </c>
       <c r="C60" s="16" t="s">
-        <v>826</v>
+        <v>816</v>
       </c>
       <c r="D60" s="32" t="s">
-        <v>841</v>
+        <v>848</v>
       </c>
       <c r="E60" s="12">
-        <v>113.3</v>
+        <v>30.425000000000001</v>
       </c>
       <c r="F60" s="12">
-        <v>104</v>
+        <v>28.9</v>
       </c>
       <c r="G60" s="12">
-        <f t="shared" si="12"/>
-        <v>-8.2100000000000009</v>
+        <f t="shared" ref="G60" si="13">ROUND((F60 - E60) / E60 * 100, 2)</f>
+        <v>-5.01</v>
       </c>
       <c r="H60" s="13" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="I60" s="13"/>
       <c r="J60" s="37" t="s">
-        <v>840</v>
+        <v>784</v>
       </c>
       <c r="K60" s="13" t="s">
-        <v>838</v>
+        <v>833</v>
       </c>
     </row>
     <row r="61" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="12" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="B61" s="32" t="s">
-        <v>776</v>
+        <v>505</v>
       </c>
       <c r="C61" s="16" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="D61" s="32" t="s">
         <v>848</v>
       </c>
       <c r="E61" s="12">
-        <v>30.425000000000001</v>
+        <v>22.22</v>
       </c>
       <c r="F61" s="12">
-        <v>28.9</v>
+        <v>21.1</v>
       </c>
       <c r="G61" s="12">
-        <f t="shared" ref="G61" si="13">ROUND((F61 - E61) / E61 * 100, 2)</f>
-        <v>-5.01</v>
+        <f>ROUND((F61 - E61) / E61 * 100, 2)</f>
+        <v>-5.04</v>
       </c>
       <c r="H61" s="13" t="s">
-        <v>817</v>
-      </c>
-      <c r="I61" s="13"/>
+        <v>819</v>
+      </c>
+      <c r="I61" s="13">
+        <v>24.6</v>
+      </c>
       <c r="J61" s="37" t="s">
         <v>784</v>
       </c>
       <c r="K61" s="13" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
     </row>
     <row r="62" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="12" t="s">
-        <v>10</v>
-      </c>
+      <c r="A62" s="8"/>
       <c r="B62" s="32" t="s">
-        <v>505</v>
-      </c>
-      <c r="C62" s="16" t="s">
-        <v>820</v>
-      </c>
-      <c r="D62" s="32" t="s">
-        <v>848</v>
-      </c>
+        <v>792</v>
+      </c>
+      <c r="C62" s="16">
+        <v>45940</v>
+      </c>
+      <c r="D62" s="32"/>
       <c r="E62" s="12">
-        <v>22.22</v>
+        <v>15.863</v>
       </c>
       <c r="F62" s="12">
-        <v>21.1</v>
+        <v>15.05</v>
       </c>
       <c r="G62" s="12">
-        <f>ROUND((F62 - E62) / E62 * 100, 2)</f>
-        <v>-5.04</v>
+        <f t="shared" ref="G62" si="14">ROUND((F62 - E62) / E62 * 100, 2)</f>
+        <v>-5.13</v>
       </c>
       <c r="H62" s="13" t="s">
-        <v>819</v>
-      </c>
-      <c r="I62" s="13">
-        <v>24.6</v>
-      </c>
+        <v>793</v>
+      </c>
+      <c r="I62" s="13"/>
       <c r="J62" s="37" t="s">
         <v>784</v>
       </c>
       <c r="K62" s="13" t="s">
-        <v>834</v>
+        <v>812</v>
       </c>
     </row>
     <row r="63" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="8"/>
       <c r="B63" s="32" t="s">
-        <v>792</v>
+        <v>528</v>
       </c>
       <c r="C63" s="16">
-        <v>45940</v>
-      </c>
-      <c r="D63" s="32"/>
+        <v>45848</v>
+      </c>
+      <c r="D63" s="32" t="s">
+        <v>814</v>
+      </c>
       <c r="E63" s="12">
-        <v>15.863</v>
+        <v>12.484999999999999</v>
       </c>
       <c r="F63" s="12">
-        <v>15.05</v>
+        <v>11.8</v>
       </c>
       <c r="G63" s="12">
-        <f t="shared" ref="G63" si="14">ROUND((F63 - E63) / E63 * 100, 2)</f>
-        <v>-5.13</v>
+        <f>ROUND((F63 - E63) / E63 * 100, 2)</f>
+        <v>-5.49</v>
       </c>
       <c r="H63" s="13" t="s">
-        <v>793</v>
+        <v>760</v>
       </c>
       <c r="I63" s="13"/>
       <c r="J63" s="37" t="s">
-        <v>784</v>
+        <v>802</v>
       </c>
       <c r="K63" s="13" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="64" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="8"/>
+      <c r="A64" s="12" t="s">
+        <v>1</v>
+      </c>
       <c r="B64" s="32" t="s">
-        <v>528</v>
+        <v>777</v>
       </c>
       <c r="C64" s="16">
-        <v>45848</v>
+        <v>45818</v>
       </c>
       <c r="D64" s="32" t="s">
         <v>814</v>
       </c>
       <c r="E64" s="12">
-        <v>12.484999999999999</v>
+        <v>31.4</v>
       </c>
       <c r="F64" s="12">
-        <v>11.8</v>
+        <v>29.9</v>
       </c>
       <c r="G64" s="12">
-        <f>ROUND((F64 - E64) / E64 * 100, 2)</f>
-        <v>-5.49</v>
+        <f t="shared" ref="G64" si="15">ROUND((F64 - E64) / E64 * 100, 2)</f>
+        <v>-4.78</v>
       </c>
       <c r="H64" s="13" t="s">
-        <v>760</v>
-      </c>
-      <c r="I64" s="13"/>
+        <v>767</v>
+      </c>
+      <c r="I64" s="13">
+        <v>38.5</v>
+      </c>
       <c r="J64" s="37" t="s">
-        <v>802</v>
+        <v>784</v>
       </c>
       <c r="K64" s="13" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="65" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="12" t="s">
-        <v>1</v>
+        <v>780</v>
       </c>
       <c r="B65" s="32" t="s">
-        <v>777</v>
+        <v>488</v>
       </c>
       <c r="C65" s="16">
-        <v>45818</v>
+        <v>45698</v>
       </c>
       <c r="D65" s="32" t="s">
         <v>814</v>
       </c>
       <c r="E65" s="12">
-        <v>31.4</v>
+        <v>13.1</v>
       </c>
       <c r="F65" s="12">
-        <v>29.9</v>
+        <v>12.5</v>
       </c>
       <c r="G65" s="12">
-        <f t="shared" ref="G65" si="15">ROUND((F65 - E65) / E65 * 100, 2)</f>
-        <v>-4.78</v>
+        <f t="shared" ref="G65" si="16">ROUND((F65 - E65) / E65 * 100, 2)</f>
+        <v>-4.58</v>
       </c>
       <c r="H65" s="13" t="s">
         <v>767</v>
       </c>
       <c r="I65" s="13">
-        <v>38.5</v>
+        <v>14.9</v>
       </c>
       <c r="J65" s="37" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="K65" s="13" t="s">
-        <v>810</v>
+        <v>752</v>
       </c>
     </row>
     <row r="66" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="12" t="s">
-        <v>780</v>
+        <v>24</v>
       </c>
       <c r="B66" s="32" t="s">
         <v>488</v>
       </c>
-      <c r="C66" s="16">
-        <v>45698</v>
+      <c r="C66" s="16" t="s">
+        <v>744</v>
       </c>
       <c r="D66" s="32" t="s">
         <v>814</v>
       </c>
       <c r="E66" s="12">
-        <v>13.1</v>
+        <v>13.311</v>
       </c>
       <c r="F66" s="12">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="G66" s="12">
-        <f t="shared" ref="G66" si="16">ROUND((F66 - E66) / E66 * 100, 2)</f>
-        <v>-4.58</v>
+        <f t="shared" ref="G66" si="17">ROUND((F66 - E66) / E66 * 100, 2)</f>
+        <v>-2.34</v>
       </c>
       <c r="H66" s="13" t="s">
-        <v>767</v>
+        <v>747</v>
       </c>
       <c r="I66" s="13">
-        <v>14.9</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="J66" s="37" t="s">
-        <v>785</v>
+        <v>774</v>
       </c>
       <c r="K66" s="13" t="s">
-        <v>752</v>
+        <v>788</v>
       </c>
     </row>
     <row r="67" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="12" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="B67" s="32" t="s">
         <v>488</v>
       </c>
-      <c r="C67" s="16" t="s">
-        <v>744</v>
+      <c r="C67" s="16">
+        <v>45667</v>
       </c>
       <c r="D67" s="32" t="s">
         <v>814</v>
       </c>
       <c r="E67" s="12">
-        <v>13.311</v>
+        <v>14.1</v>
       </c>
       <c r="F67" s="12">
         <v>13</v>
       </c>
       <c r="G67" s="12">
-        <f t="shared" ref="G67" si="17">ROUND((F67 - E67) / E67 * 100, 2)</f>
-        <v>-2.34</v>
+        <f t="shared" ref="G67" si="18">ROUND((F67 - E67) / E67 * 100, 2)</f>
+        <v>-7.8</v>
       </c>
       <c r="H67" s="13" t="s">
-        <v>747</v>
+        <v>763</v>
       </c>
       <c r="I67" s="13">
         <v>16.399999999999999</v>
@@ -21104,38 +21281,38 @@
     </row>
     <row r="68" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="12" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B68" s="32" t="s">
-        <v>488</v>
+        <v>776</v>
       </c>
       <c r="C68" s="16">
-        <v>45667</v>
+        <v>45818</v>
       </c>
       <c r="D68" s="32" t="s">
         <v>814</v>
       </c>
       <c r="E68" s="12">
-        <v>14.1</v>
+        <v>27.422000000000001</v>
       </c>
       <c r="F68" s="12">
-        <v>13</v>
+        <v>26.05</v>
       </c>
       <c r="G68" s="12">
-        <f t="shared" ref="G68" si="18">ROUND((F68 - E68) / E68 * 100, 2)</f>
-        <v>-7.8</v>
+        <f t="shared" ref="G68" si="19">ROUND((F68 - E68) / E68 * 100, 2)</f>
+        <v>-5</v>
       </c>
       <c r="H68" s="13" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="I68" s="13">
-        <v>16.399999999999999</v>
+        <v>29.9</v>
       </c>
       <c r="J68" s="37" t="s">
-        <v>774</v>
+        <v>784</v>
       </c>
       <c r="K68" s="13" t="s">
-        <v>788</v>
+        <v>805</v>
       </c>
     </row>
     <row r="69" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
@@ -21143,205 +21320,203 @@
         <v>33</v>
       </c>
       <c r="B69" s="32" t="s">
-        <v>776</v>
-      </c>
-      <c r="C69" s="16">
-        <v>45818</v>
+        <v>718</v>
+      </c>
+      <c r="C69" s="16" t="s">
+        <v>759</v>
       </c>
       <c r="D69" s="32" t="s">
         <v>814</v>
       </c>
       <c r="E69" s="12">
-        <v>27.422000000000001</v>
+        <v>34</v>
       </c>
       <c r="F69" s="12">
-        <v>26.05</v>
+        <v>32.299999999999997</v>
       </c>
       <c r="G69" s="12">
-        <f t="shared" ref="G69" si="19">ROUND((F69 - E69) / E69 * 100, 2)</f>
+        <f t="shared" ref="G69" si="20">ROUND((F69 - E69) / E69 * 100, 2)</f>
         <v>-5</v>
       </c>
       <c r="H69" s="13" t="s">
-        <v>767</v>
+        <v>760</v>
       </c>
       <c r="I69" s="13">
-        <v>29.9</v>
-      </c>
-      <c r="J69" s="37" t="s">
-        <v>784</v>
+        <v>40.6</v>
+      </c>
+      <c r="J69" s="37">
+        <v>-5</v>
       </c>
       <c r="K69" s="13" t="s">
-        <v>805</v>
+        <v>553</v>
       </c>
     </row>
     <row r="70" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="12" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B70" s="32" t="s">
-        <v>718</v>
+        <v>754</v>
       </c>
       <c r="C70" s="16" t="s">
-        <v>759</v>
+        <v>753</v>
       </c>
       <c r="D70" s="32" t="s">
-        <v>814</v>
+        <v>766</v>
       </c>
       <c r="E70" s="12">
-        <v>34</v>
+        <v>15.061999999999999</v>
       </c>
       <c r="F70" s="12">
-        <v>32.299999999999997</v>
+        <v>14.15</v>
       </c>
       <c r="G70" s="12">
-        <f t="shared" ref="G70" si="20">ROUND((F70 - E70) / E70 * 100, 2)</f>
-        <v>-5</v>
+        <f>ROUND((F70 - E70) / E70 * 100, 2)</f>
+        <v>-6.05</v>
       </c>
       <c r="H70" s="13" t="s">
-        <v>760</v>
-      </c>
-      <c r="I70" s="13">
-        <v>40.6</v>
-      </c>
+        <v>755</v>
+      </c>
+      <c r="I70" s="13"/>
       <c r="J70" s="37">
-        <v>-5</v>
+        <v>14.15</v>
       </c>
       <c r="K70" s="13" t="s">
-        <v>553</v>
+        <v>765</v>
       </c>
     </row>
     <row r="71" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="12" t="s">
-        <v>12</v>
+        <v>396</v>
       </c>
       <c r="B71" s="32" t="s">
-        <v>754</v>
-      </c>
-      <c r="C71" s="16" t="s">
-        <v>753</v>
-      </c>
-      <c r="D71" s="32" t="s">
-        <v>766</v>
+        <v>488</v>
+      </c>
+      <c r="C71" s="16">
+        <v>46000</v>
+      </c>
+      <c r="D71" s="16" t="s">
+        <v>759</v>
       </c>
       <c r="E71" s="12">
-        <v>15.061999999999999</v>
+        <v>24.37</v>
       </c>
       <c r="F71" s="12">
-        <v>14.15</v>
+        <v>23.7</v>
       </c>
       <c r="G71" s="12">
-        <f>ROUND((F71 - E71) / E71 * 100, 2)</f>
-        <v>-6.05</v>
+        <f t="shared" ref="G71" si="21">ROUND((F71 - E71) / E71 * 100, 2)</f>
+        <v>-2.75</v>
       </c>
       <c r="H71" s="13" t="s">
-        <v>755</v>
+        <v>688</v>
       </c>
       <c r="I71" s="13"/>
       <c r="J71" s="37">
-        <v>14.15</v>
+        <v>-5</v>
       </c>
       <c r="K71" s="13" t="s">
-        <v>765</v>
+        <v>752</v>
+      </c>
+      <c r="L71" s="12" t="s">
+        <v>694</v>
       </c>
     </row>
     <row r="72" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="12" t="s">
-        <v>396</v>
+        <v>736</v>
       </c>
       <c r="B72" s="32" t="s">
-        <v>488</v>
-      </c>
-      <c r="C72" s="16">
-        <v>46000</v>
+        <v>528</v>
+      </c>
+      <c r="C72" s="16" t="s">
+        <v>700</v>
       </c>
       <c r="D72" s="16" t="s">
         <v>759</v>
       </c>
       <c r="E72" s="12">
-        <v>24.37</v>
+        <v>81.5</v>
       </c>
       <c r="F72" s="12">
-        <v>23.7</v>
+        <v>79</v>
       </c>
       <c r="G72" s="12">
-        <f t="shared" ref="G72" si="21">ROUND((F72 - E72) / E72 * 100, 2)</f>
-        <v>-2.75</v>
+        <f t="shared" ref="G72:G78" si="22">ROUND((F72 - E72) / E72 * 100, 2)</f>
+        <v>-3.07</v>
       </c>
       <c r="H72" s="13" t="s">
-        <v>688</v>
-      </c>
-      <c r="I72" s="13"/>
-      <c r="J72" s="37">
-        <v>-5</v>
+        <v>685</v>
+      </c>
+      <c r="I72" s="13">
+        <v>87.7</v>
+      </c>
+      <c r="J72" s="37" t="s">
+        <v>740</v>
       </c>
       <c r="K72" s="13" t="s">
-        <v>752</v>
-      </c>
-      <c r="L72" s="12" t="s">
-        <v>694</v>
+        <v>746</v>
       </c>
     </row>
     <row r="73" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="12" t="s">
-        <v>736</v>
+        <v>10</v>
       </c>
       <c r="B73" s="32" t="s">
-        <v>528</v>
+        <v>731</v>
       </c>
       <c r="C73" s="16" t="s">
-        <v>700</v>
+        <v>744</v>
       </c>
       <c r="D73" s="16" t="s">
         <v>759</v>
       </c>
       <c r="E73" s="12">
-        <v>81.5</v>
+        <v>60.15</v>
       </c>
       <c r="F73" s="12">
-        <v>79</v>
+        <v>57.1</v>
       </c>
       <c r="G73" s="12">
-        <f t="shared" ref="G73:G79" si="22">ROUND((F73 - E73) / E73 * 100, 2)</f>
-        <v>-3.07</v>
+        <f t="shared" si="22"/>
+        <v>-5.07</v>
       </c>
       <c r="H73" s="13" t="s">
-        <v>685</v>
-      </c>
-      <c r="I73" s="13">
-        <v>87.7</v>
-      </c>
-      <c r="J73" s="37" t="s">
-        <v>740</v>
+        <v>748</v>
+      </c>
+      <c r="I73" s="13"/>
+      <c r="J73" s="37">
+        <v>-5</v>
       </c>
       <c r="K73" s="13" t="s">
-        <v>746</v>
+        <v>752</v>
       </c>
     </row>
     <row r="74" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="12" t="s">
-        <v>10</v>
+        <v>704</v>
       </c>
       <c r="B74" s="32" t="s">
-        <v>731</v>
+        <v>737</v>
       </c>
       <c r="C74" s="16" t="s">
-        <v>744</v>
+        <v>738</v>
       </c>
       <c r="D74" s="16" t="s">
         <v>759</v>
       </c>
       <c r="E74" s="12">
-        <v>60.15</v>
+        <v>24.3</v>
       </c>
       <c r="F74" s="12">
-        <v>57.1</v>
+        <v>23.1</v>
       </c>
       <c r="G74" s="12">
         <f t="shared" si="22"/>
-        <v>-5.07</v>
+        <v>-4.9400000000000004</v>
       </c>
       <c r="H74" s="13" t="s">
-        <v>748</v>
+        <v>734</v>
       </c>
       <c r="I74" s="13"/>
       <c r="J74" s="37">
@@ -21353,67 +21528,67 @@
     </row>
     <row r="75" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="12" t="s">
-        <v>704</v>
+        <v>743</v>
       </c>
       <c r="B75" s="32" t="s">
-        <v>737</v>
+        <v>587</v>
       </c>
       <c r="C75" s="16" t="s">
-        <v>738</v>
+        <v>716</v>
       </c>
       <c r="D75" s="16" t="s">
-        <v>759</v>
+        <v>753</v>
       </c>
       <c r="E75" s="12">
-        <v>24.3</v>
+        <v>105</v>
       </c>
       <c r="F75" s="12">
-        <v>23.1</v>
+        <v>98.6</v>
       </c>
       <c r="G75" s="12">
         <f t="shared" si="22"/>
-        <v>-4.9400000000000004</v>
+        <v>-6.1</v>
       </c>
       <c r="H75" s="13" t="s">
-        <v>734</v>
+        <v>717</v>
       </c>
       <c r="I75" s="13"/>
       <c r="J75" s="37">
-        <v>-5</v>
+        <v>97.5</v>
       </c>
       <c r="K75" s="13" t="s">
-        <v>752</v>
+        <v>733</v>
       </c>
     </row>
     <row r="76" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="12" t="s">
-        <v>743</v>
+        <v>730</v>
       </c>
       <c r="B76" s="32" t="s">
-        <v>587</v>
+        <v>718</v>
       </c>
       <c r="C76" s="16" t="s">
         <v>716</v>
       </c>
       <c r="D76" s="16" t="s">
-        <v>753</v>
+        <v>738</v>
       </c>
       <c r="E76" s="12">
-        <v>105</v>
+        <v>34.35</v>
       </c>
       <c r="F76" s="12">
-        <v>98.6</v>
+        <v>32.700000000000003</v>
       </c>
       <c r="G76" s="12">
         <f t="shared" si="22"/>
-        <v>-6.1</v>
+        <v>-4.8</v>
       </c>
       <c r="H76" s="13" t="s">
         <v>717</v>
       </c>
       <c r="I76" s="13"/>
       <c r="J76" s="37">
-        <v>97.5</v>
+        <v>32.15</v>
       </c>
       <c r="K76" s="13" t="s">
         <v>733</v>
@@ -21421,10 +21596,10 @@
     </row>
     <row r="77" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="12" t="s">
-        <v>730</v>
+        <v>406</v>
       </c>
       <c r="B77" s="32" t="s">
-        <v>718</v>
+        <v>731</v>
       </c>
       <c r="C77" s="16" t="s">
         <v>716</v>
@@ -21433,510 +21608,511 @@
         <v>738</v>
       </c>
       <c r="E77" s="12">
-        <v>34.35</v>
+        <v>61.4</v>
       </c>
       <c r="F77" s="12">
-        <v>32.700000000000003</v>
+        <v>59.4</v>
       </c>
       <c r="G77" s="12">
         <f t="shared" si="22"/>
-        <v>-4.8</v>
+        <v>-3.26</v>
       </c>
       <c r="H77" s="13" t="s">
         <v>717</v>
       </c>
       <c r="I77" s="13"/>
       <c r="J77" s="37">
-        <v>32.15</v>
+        <v>58.7</v>
       </c>
       <c r="K77" s="13" t="s">
         <v>733</v>
       </c>
     </row>
-    <row r="78" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:12" s="12" customFormat="1" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A78" s="12" t="s">
-        <v>406</v>
+        <v>586</v>
       </c>
       <c r="B78" s="32" t="s">
-        <v>731</v>
-      </c>
-      <c r="C78" s="16" t="s">
-        <v>716</v>
-      </c>
-      <c r="D78" s="16" t="s">
-        <v>738</v>
-      </c>
+        <v>686</v>
+      </c>
+      <c r="C78" s="16">
+        <v>45970</v>
+      </c>
+      <c r="D78" s="32"/>
       <c r="E78" s="12">
-        <v>61.4</v>
+        <v>43.784999999999997</v>
       </c>
       <c r="F78" s="12">
-        <v>59.4</v>
+        <v>41.6</v>
       </c>
       <c r="G78" s="12">
         <f t="shared" si="22"/>
-        <v>-3.26</v>
+        <v>-4.99</v>
       </c>
       <c r="H78" s="13" t="s">
-        <v>717</v>
-      </c>
-      <c r="I78" s="13"/>
+        <v>693</v>
+      </c>
+      <c r="I78" s="13">
+        <v>48.2</v>
+      </c>
       <c r="J78" s="37">
-        <v>58.7</v>
+        <v>-5</v>
       </c>
       <c r="K78" s="13" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="79" spans="1:12" s="12" customFormat="1" ht="37.5" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="12" t="s">
-        <v>586</v>
+        <v>612</v>
       </c>
       <c r="B79" s="32" t="s">
-        <v>686</v>
+        <v>489</v>
       </c>
       <c r="C79" s="16">
-        <v>45970</v>
+        <v>46000</v>
       </c>
       <c r="D79" s="32"/>
       <c r="E79" s="12">
-        <v>43.784999999999997</v>
+        <v>24.02</v>
       </c>
       <c r="F79" s="12">
-        <v>41.6</v>
+        <v>22.8</v>
       </c>
       <c r="G79" s="12">
-        <f t="shared" si="22"/>
-        <v>-4.99</v>
+        <f t="shared" ref="G79:G110" si="23">ROUND((F79 - E79) / E79 * 100, 2)</f>
+        <v>-5.08</v>
       </c>
       <c r="H79" s="13" t="s">
-        <v>693</v>
-      </c>
-      <c r="I79" s="13">
-        <v>48.2</v>
-      </c>
+        <v>698</v>
+      </c>
+      <c r="I79" s="13"/>
       <c r="J79" s="37">
         <v>-5</v>
       </c>
       <c r="K79" s="13" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="80" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="12" t="s">
-        <v>612</v>
+        <v>13</v>
       </c>
       <c r="B80" s="32" t="s">
         <v>489</v>
       </c>
       <c r="C80" s="16">
-        <v>46000</v>
+        <v>45970</v>
       </c>
       <c r="D80" s="32"/>
       <c r="E80" s="12">
-        <v>24.02</v>
+        <v>23.12</v>
       </c>
       <c r="F80" s="12">
-        <v>22.8</v>
+        <v>22.1</v>
       </c>
       <c r="G80" s="12">
-        <f t="shared" ref="G80:G111" si="23">ROUND((F80 - E80) / E80 * 100, 2)</f>
-        <v>-5.08</v>
+        <f t="shared" si="23"/>
+        <v>-4.41</v>
       </c>
       <c r="H80" s="13" t="s">
-        <v>698</v>
-      </c>
-      <c r="I80" s="13"/>
+        <v>688</v>
+      </c>
+      <c r="I80" s="13">
+        <v>25.8</v>
+      </c>
       <c r="J80" s="37">
         <v>-5</v>
       </c>
       <c r="K80" s="13" t="s">
-        <v>720</v>
+        <v>553</v>
       </c>
     </row>
     <row r="81" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="12" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="B81" s="32" t="s">
-        <v>489</v>
+        <v>505</v>
       </c>
       <c r="C81" s="16">
-        <v>45970</v>
+        <v>45939</v>
       </c>
       <c r="D81" s="32"/>
       <c r="E81" s="12">
-        <v>23.12</v>
+        <v>29.1</v>
       </c>
       <c r="F81" s="12">
-        <v>22.1</v>
+        <v>28.25</v>
       </c>
       <c r="G81" s="12">
         <f t="shared" si="23"/>
-        <v>-4.41</v>
+        <v>-2.92</v>
       </c>
       <c r="H81" s="13" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="I81" s="13">
-        <v>25.8</v>
+        <v>31.4</v>
       </c>
       <c r="J81" s="37">
-        <v>-5</v>
+        <v>28.25</v>
       </c>
       <c r="K81" s="13" t="s">
-        <v>553</v>
+        <v>712</v>
       </c>
     </row>
     <row r="82" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="12" t="s">
-        <v>34</v>
+        <v>687</v>
       </c>
       <c r="B82" s="32" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="C82" s="16">
-        <v>45939</v>
+        <v>45970</v>
       </c>
       <c r="D82" s="32"/>
       <c r="E82" s="12">
-        <v>29.1</v>
+        <v>38.83</v>
       </c>
       <c r="F82" s="12">
-        <v>28.25</v>
+        <v>36.9</v>
       </c>
       <c r="G82" s="12">
         <f t="shared" si="23"/>
-        <v>-2.92</v>
+        <v>-4.97</v>
       </c>
       <c r="H82" s="13" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="I82" s="13">
-        <v>31.4</v>
+        <v>42.3</v>
       </c>
       <c r="J82" s="37">
-        <v>28.25</v>
+        <v>-5</v>
       </c>
       <c r="K82" s="13" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="83" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" s="12" customFormat="1" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A83" s="12" t="s">
-        <v>687</v>
+        <v>54</v>
       </c>
       <c r="B83" s="32" t="s">
-        <v>510</v>
+        <v>492</v>
       </c>
       <c r="C83" s="16">
-        <v>45970</v>
+        <v>45786</v>
       </c>
       <c r="D83" s="32"/>
       <c r="E83" s="12">
-        <v>38.83</v>
+        <v>28.05</v>
       </c>
       <c r="F83" s="12">
-        <v>36.9</v>
+        <v>25.75</v>
       </c>
       <c r="G83" s="12">
         <f t="shared" si="23"/>
-        <v>-4.97</v>
+        <v>-8.1999999999999993</v>
       </c>
       <c r="H83" s="13" t="s">
-        <v>688</v>
-      </c>
-      <c r="I83" s="13">
-        <v>42.3</v>
-      </c>
-      <c r="J83" s="37">
-        <v>-5</v>
-      </c>
+        <v>665</v>
+      </c>
+      <c r="I83" s="13"/>
+      <c r="J83" s="37"/>
       <c r="K83" s="13" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="84" spans="1:12" s="12" customFormat="1" ht="37.5" x14ac:dyDescent="0.25">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="12" t="s">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="B84" s="32" t="s">
-        <v>492</v>
-      </c>
-      <c r="C84" s="16">
-        <v>45786</v>
+        <v>489</v>
+      </c>
+      <c r="C84" s="12" t="s">
+        <v>627</v>
       </c>
       <c r="D84" s="32"/>
       <c r="E84" s="12">
-        <v>28.05</v>
+        <v>24.92</v>
       </c>
       <c r="F84" s="12">
-        <v>25.75</v>
+        <v>23.7</v>
       </c>
       <c r="G84" s="12">
         <f t="shared" si="23"/>
-        <v>-8.1999999999999993</v>
-      </c>
-      <c r="H84" s="13" t="s">
-        <v>665</v>
-      </c>
+        <v>-4.9000000000000004</v>
+      </c>
+      <c r="H84" s="13"/>
       <c r="I84" s="13"/>
-      <c r="J84" s="37"/>
+      <c r="J84" s="37">
+        <v>-5</v>
+      </c>
       <c r="K84" s="13" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="85" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="12" t="s">
-        <v>7</v>
+        <v>664</v>
       </c>
       <c r="B85" s="32" t="s">
-        <v>489</v>
+        <v>625</v>
       </c>
       <c r="C85" s="12" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="D85" s="32"/>
       <c r="E85" s="12">
-        <v>24.92</v>
+        <v>50.741</v>
       </c>
       <c r="F85" s="12">
-        <v>23.7</v>
+        <v>50.5</v>
       </c>
       <c r="G85" s="12">
         <f t="shared" si="23"/>
-        <v>-4.9000000000000004</v>
+        <v>-0.47</v>
       </c>
       <c r="H85" s="13"/>
-      <c r="I85" s="13"/>
-      <c r="J85" s="37">
-        <v>-5</v>
+      <c r="I85" s="13">
+        <v>58</v>
+      </c>
+      <c r="J85" s="37" t="s">
+        <v>674</v>
       </c>
       <c r="K85" s="13" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="86" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="12" t="s">
-        <v>664</v>
-      </c>
-      <c r="B86" s="32" t="s">
-        <v>625</v>
-      </c>
-      <c r="C86" s="12" t="s">
-        <v>623</v>
-      </c>
-      <c r="D86" s="32"/>
-      <c r="E86" s="12">
-        <v>50.741</v>
-      </c>
-      <c r="F86" s="12">
-        <v>50.5</v>
-      </c>
-      <c r="G86" s="12">
+        <v>629</v>
+      </c>
+      <c r="B86" s="31" t="s">
+        <v>620</v>
+      </c>
+      <c r="C86" s="10" t="s">
+        <v>619</v>
+      </c>
+      <c r="D86" s="31"/>
+      <c r="E86" s="10">
+        <v>26.86</v>
+      </c>
+      <c r="F86" s="10">
+        <v>32.200000000000003</v>
+      </c>
+      <c r="G86" s="10">
         <f t="shared" si="23"/>
-        <v>-0.47</v>
-      </c>
-      <c r="H86" s="13"/>
-      <c r="I86" s="13">
-        <v>58</v>
-      </c>
-      <c r="J86" s="37" t="s">
-        <v>674</v>
-      </c>
-      <c r="K86" s="13" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="87" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.25">
+        <v>19.88</v>
+      </c>
+      <c r="H86" s="7"/>
+      <c r="I86" s="7">
+        <v>38.5</v>
+      </c>
+      <c r="J86" s="38">
+        <v>32.200000000000003</v>
+      </c>
+      <c r="K86" s="7" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" s="10" customFormat="1" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A87" s="12" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="B87" s="31" t="s">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="C87" s="10" t="s">
-        <v>619</v>
+        <v>627</v>
       </c>
       <c r="D87" s="31"/>
       <c r="E87" s="10">
-        <v>26.86</v>
+        <v>23.27</v>
       </c>
       <c r="F87" s="10">
-        <v>32.200000000000003</v>
+        <v>25</v>
       </c>
       <c r="G87" s="10">
         <f t="shared" si="23"/>
-        <v>19.88</v>
+        <v>7.43</v>
       </c>
       <c r="H87" s="7"/>
-      <c r="I87" s="7">
-        <v>38.5</v>
-      </c>
+      <c r="I87" s="7"/>
       <c r="J87" s="38">
-        <v>32.200000000000003</v>
+        <v>25</v>
       </c>
       <c r="K87" s="7" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="88" spans="1:12" s="10" customFormat="1" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A88" s="12" t="s">
-        <v>624</v>
-      </c>
-      <c r="B88" s="31" t="s">
-        <v>628</v>
-      </c>
-      <c r="C88" s="10" t="s">
-        <v>627</v>
-      </c>
-      <c r="D88" s="31"/>
-      <c r="E88" s="10">
-        <v>23.27</v>
-      </c>
-      <c r="F88" s="10">
-        <v>25</v>
-      </c>
-      <c r="G88" s="10">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B88" s="32" t="s">
+        <v>607</v>
+      </c>
+      <c r="C88" s="16" t="s">
+        <v>605</v>
+      </c>
+      <c r="D88" s="32"/>
+      <c r="E88" s="12">
+        <v>16.263000000000002</v>
+      </c>
+      <c r="F88" s="12">
+        <v>16.149999999999999</v>
+      </c>
+      <c r="G88" s="12">
         <f t="shared" si="23"/>
-        <v>7.43</v>
-      </c>
-      <c r="H88" s="7"/>
-      <c r="I88" s="7"/>
-      <c r="J88" s="38">
-        <v>25</v>
-      </c>
-      <c r="K88" s="7" t="s">
-        <v>671</v>
+        <v>-0.69</v>
+      </c>
+      <c r="H88" s="13"/>
+      <c r="I88" s="13"/>
+      <c r="J88" s="37" t="s">
+        <v>661</v>
+      </c>
+      <c r="K88" s="13" t="s">
+        <v>635</v>
       </c>
     </row>
     <row r="89" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="10" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="B89" s="32" t="s">
-        <v>607</v>
-      </c>
-      <c r="C89" s="16" t="s">
-        <v>605</v>
+        <v>510</v>
+      </c>
+      <c r="C89" s="12" t="s">
+        <v>623</v>
       </c>
       <c r="D89" s="32"/>
       <c r="E89" s="12">
-        <v>16.263000000000002</v>
+        <v>39</v>
       </c>
       <c r="F89" s="12">
-        <v>16.149999999999999</v>
+        <v>39</v>
       </c>
       <c r="G89" s="12">
         <f t="shared" si="23"/>
-        <v>-0.69</v>
+        <v>0</v>
       </c>
       <c r="H89" s="13"/>
-      <c r="I89" s="13"/>
+      <c r="I89" s="13">
+        <v>45</v>
+      </c>
       <c r="J89" s="37" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="K89" s="13" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="90" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="10" t="s">
-        <v>10</v>
+      <c r="A90" s="12" t="s">
+        <v>606</v>
       </c>
       <c r="B90" s="32" t="s">
-        <v>510</v>
+        <v>625</v>
       </c>
       <c r="C90" s="12" t="s">
-        <v>623</v>
+        <v>634</v>
       </c>
       <c r="D90" s="32"/>
       <c r="E90" s="12">
-        <v>39</v>
+        <v>40.9</v>
       </c>
       <c r="F90" s="12">
-        <v>39</v>
+        <v>38.9</v>
       </c>
       <c r="G90" s="12">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-4.8899999999999997</v>
       </c>
       <c r="H90" s="13"/>
-      <c r="I90" s="13">
-        <v>45</v>
-      </c>
-      <c r="J90" s="37" t="s">
-        <v>662</v>
+      <c r="I90" s="13"/>
+      <c r="J90" s="37">
+        <v>-5</v>
       </c>
       <c r="K90" s="13" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="91" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="12" t="s">
-        <v>606</v>
-      </c>
-      <c r="B91" s="32" t="s">
-        <v>625</v>
-      </c>
-      <c r="C91" s="12" t="s">
-        <v>634</v>
-      </c>
-      <c r="D91" s="32"/>
-      <c r="E91" s="12">
-        <v>40.9</v>
-      </c>
-      <c r="F91" s="12">
-        <v>38.9</v>
-      </c>
-      <c r="G91" s="12">
-        <f t="shared" si="23"/>
-        <v>-4.8899999999999997</v>
-      </c>
-      <c r="H91" s="13"/>
-      <c r="I91" s="13"/>
-      <c r="J91" s="37">
-        <v>-5</v>
-      </c>
-      <c r="K91" s="13" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="92" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="12" t="s">
         <v>396</v>
       </c>
-      <c r="B92" s="31" t="s">
+      <c r="B91" s="31" t="s">
         <v>528</v>
       </c>
-      <c r="C92" s="10" t="s">
+      <c r="C91" s="10" t="s">
         <v>619</v>
       </c>
-      <c r="D92" s="31"/>
-      <c r="E92" s="10">
+      <c r="D91" s="31"/>
+      <c r="E91" s="10">
         <v>62</v>
       </c>
-      <c r="F92" s="10">
+      <c r="F91" s="10">
         <v>62.5</v>
       </c>
-      <c r="G92" s="10">
+      <c r="G91" s="10">
         <f t="shared" si="23"/>
         <v>0.81</v>
       </c>
-      <c r="H92" s="7"/>
-      <c r="I92" s="7"/>
-      <c r="J92" s="38">
+      <c r="H91" s="7"/>
+      <c r="I91" s="7"/>
+      <c r="J91" s="38">
         <v>-5</v>
       </c>
-      <c r="K92" s="7" t="s">
+      <c r="K91" s="7" t="s">
         <v>631</v>
       </c>
     </row>
+    <row r="92" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B92" s="32" t="s">
+        <v>620</v>
+      </c>
+      <c r="C92" s="12" t="s">
+        <v>610</v>
+      </c>
+      <c r="D92" s="32"/>
+      <c r="E92" s="12">
+        <v>23.22</v>
+      </c>
+      <c r="F92" s="12">
+        <v>21.85</v>
+      </c>
+      <c r="G92" s="12">
+        <f t="shared" si="23"/>
+        <v>-5.9</v>
+      </c>
+      <c r="H92" s="13"/>
+      <c r="I92" s="13">
+        <v>30.5</v>
+      </c>
+      <c r="J92" s="37">
+        <v>22.4</v>
+      </c>
+      <c r="K92" s="13" t="s">
+        <v>615</v>
+      </c>
+      <c r="L92" s="12" t="s">
+        <v>618</v>
+      </c>
+    </row>
     <row r="93" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="12" t="s">
-        <v>30</v>
+      <c r="A93" s="10" t="s">
+        <v>612</v>
       </c>
       <c r="B93" s="32" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C93" s="12" t="s">
         <v>610</v>
@@ -21946,11 +22122,11 @@
         <v>23.22</v>
       </c>
       <c r="F93" s="12">
-        <v>21.85</v>
+        <v>22.4</v>
       </c>
       <c r="G93" s="12">
         <f t="shared" si="23"/>
-        <v>-5.9</v>
+        <v>-3.53</v>
       </c>
       <c r="H93" s="13"/>
       <c r="I93" s="13">
@@ -21967,1942 +22143,1907 @@
       </c>
     </row>
     <row r="94" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="10" t="s">
-        <v>612</v>
+      <c r="A94" s="12" t="s">
+        <v>10</v>
       </c>
       <c r="B94" s="32" t="s">
-        <v>621</v>
-      </c>
-      <c r="C94" s="12" t="s">
-        <v>610</v>
+        <v>580</v>
+      </c>
+      <c r="C94" s="16">
+        <v>45755</v>
       </c>
       <c r="D94" s="32"/>
       <c r="E94" s="12">
-        <v>23.22</v>
+        <v>8.0359999999999996</v>
       </c>
       <c r="F94" s="12">
-        <v>22.4</v>
+        <v>7.6</v>
       </c>
       <c r="G94" s="12">
         <f t="shared" si="23"/>
-        <v>-3.53</v>
+        <v>-5.43</v>
       </c>
       <c r="H94" s="13"/>
       <c r="I94" s="13">
-        <v>30.5</v>
+        <v>9.5</v>
       </c>
       <c r="J94" s="37">
-        <v>22.4</v>
+        <v>-5</v>
       </c>
       <c r="K94" s="13" t="s">
-        <v>615</v>
-      </c>
-      <c r="L94" s="12" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="95" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A95" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B95" s="32" t="s">
-        <v>580</v>
-      </c>
-      <c r="C95" s="16">
-        <v>45755</v>
-      </c>
-      <c r="D95" s="32"/>
-      <c r="E95" s="12">
-        <v>8.0359999999999996</v>
-      </c>
-      <c r="F95" s="12">
-        <v>7.6</v>
-      </c>
-      <c r="G95" s="12">
+      <c r="B95" s="31" t="s">
+        <v>529</v>
+      </c>
+      <c r="C95" s="10" t="s">
+        <v>519</v>
+      </c>
+      <c r="D95" s="31"/>
+      <c r="E95" s="10">
+        <v>11.573</v>
+      </c>
+      <c r="F95" s="10">
+        <v>15.2</v>
+      </c>
+      <c r="G95" s="10">
         <f t="shared" si="23"/>
-        <v>-5.43</v>
-      </c>
-      <c r="H95" s="13"/>
-      <c r="I95" s="13">
-        <v>9.5</v>
-      </c>
-      <c r="J95" s="37">
-        <v>-5</v>
-      </c>
-      <c r="K95" s="13" t="s">
-        <v>611</v>
+        <v>31.34</v>
+      </c>
+      <c r="H95" s="7"/>
+      <c r="I95" s="7">
+        <v>15.2</v>
+      </c>
+      <c r="J95" s="38">
+        <v>12.3</v>
+      </c>
+      <c r="K95" s="7" t="s">
+        <v>609</v>
+      </c>
+      <c r="L95" s="10" t="s">
+        <v>562</v>
       </c>
     </row>
     <row r="96" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A96" s="12" t="s">
-        <v>10</v>
+        <v>550</v>
       </c>
       <c r="B96" s="31" t="s">
-        <v>529</v>
-      </c>
-      <c r="C96" s="10" t="s">
+        <v>520</v>
+      </c>
+      <c r="C96" s="15" t="s">
         <v>519</v>
       </c>
       <c r="D96" s="31"/>
       <c r="E96" s="10">
-        <v>11.573</v>
+        <v>11.464</v>
       </c>
       <c r="F96" s="10">
-        <v>15.2</v>
+        <v>14.75</v>
       </c>
       <c r="G96" s="10">
         <f t="shared" si="23"/>
-        <v>31.34</v>
+        <v>28.66</v>
       </c>
       <c r="H96" s="7"/>
       <c r="I96" s="7">
-        <v>15.2</v>
-      </c>
-      <c r="J96" s="38">
-        <v>12.3</v>
+        <v>17.55</v>
+      </c>
+      <c r="J96" s="38" t="s">
+        <v>592</v>
       </c>
       <c r="K96" s="7" t="s">
-        <v>609</v>
-      </c>
-      <c r="L96" s="10" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="97" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="12" t="s">
-        <v>550</v>
-      </c>
-      <c r="B97" s="31" t="s">
-        <v>520</v>
-      </c>
-      <c r="C97" s="15" t="s">
-        <v>519</v>
-      </c>
-      <c r="D97" s="31"/>
-      <c r="E97" s="10">
-        <v>11.464</v>
-      </c>
-      <c r="F97" s="10">
-        <v>14.75</v>
-      </c>
-      <c r="G97" s="10">
-        <f t="shared" si="23"/>
-        <v>28.66</v>
-      </c>
-      <c r="H97" s="7"/>
-      <c r="I97" s="7">
-        <v>17.55</v>
-      </c>
-      <c r="J97" s="38" t="s">
-        <v>592</v>
-      </c>
-      <c r="K97" s="7" t="s">
         <v>590</v>
       </c>
     </row>
-    <row r="98" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="10" t="s">
+    <row r="97" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B98" s="32" t="s">
+      <c r="B97" s="32" t="s">
         <v>587</v>
       </c>
-      <c r="C98" s="16">
+      <c r="C97" s="16">
         <v>45999</v>
       </c>
-      <c r="D98" s="32"/>
-      <c r="E98" s="12">
+      <c r="D97" s="32"/>
+      <c r="E97" s="12">
         <v>37.18</v>
       </c>
-      <c r="F98" s="12">
+      <c r="F97" s="12">
         <v>35.299999999999997</v>
       </c>
-      <c r="G98" s="12">
+      <c r="G97" s="12">
         <f t="shared" si="23"/>
         <v>-5.0599999999999996</v>
       </c>
-      <c r="H98" s="13"/>
-      <c r="I98" s="13"/>
-      <c r="J98" s="37">
+      <c r="H97" s="13"/>
+      <c r="I97" s="13"/>
+      <c r="J97" s="37">
         <v>-5</v>
       </c>
-      <c r="K98" s="13" t="s">
+      <c r="K97" s="13" t="s">
         <v>594</v>
       </c>
     </row>
+    <row r="98" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B98" s="31" t="s">
+        <v>493</v>
+      </c>
+      <c r="C98" s="15" t="s">
+        <v>458</v>
+      </c>
+      <c r="D98" s="31"/>
+      <c r="E98" s="10">
+        <v>18.5</v>
+      </c>
+      <c r="F98" s="10">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="G98" s="10">
+        <f t="shared" si="23"/>
+        <v>7.57</v>
+      </c>
+      <c r="H98" s="7"/>
+      <c r="I98" s="7">
+        <v>32</v>
+      </c>
+      <c r="J98" s="38" t="s">
+        <v>597</v>
+      </c>
+      <c r="K98" s="7" t="s">
+        <v>598</v>
+      </c>
+    </row>
     <row r="99" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="10" t="s">
-        <v>33</v>
+      <c r="A99" s="12" t="s">
+        <v>586</v>
       </c>
       <c r="B99" s="31" t="s">
-        <v>493</v>
-      </c>
-      <c r="C99" s="15" t="s">
-        <v>458</v>
+        <v>533</v>
+      </c>
+      <c r="C99" s="15">
+        <v>45785</v>
       </c>
       <c r="D99" s="31"/>
       <c r="E99" s="10">
-        <v>18.5</v>
+        <v>27.071999999999999</v>
       </c>
       <c r="F99" s="10">
-        <v>19.899999999999999</v>
+        <v>29</v>
       </c>
       <c r="G99" s="10">
         <f t="shared" si="23"/>
-        <v>7.57</v>
+        <v>7.12</v>
       </c>
       <c r="H99" s="7"/>
       <c r="I99" s="7">
-        <v>32</v>
-      </c>
-      <c r="J99" s="38" t="s">
-        <v>597</v>
+        <v>29</v>
+      </c>
+      <c r="J99" s="38">
+        <v>-5</v>
       </c>
       <c r="K99" s="7" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="100" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="12" t="s">
-        <v>586</v>
-      </c>
-      <c r="B100" s="31" t="s">
-        <v>533</v>
-      </c>
-      <c r="C100" s="15">
-        <v>45785</v>
-      </c>
-      <c r="D100" s="31"/>
-      <c r="E100" s="10">
-        <v>27.071999999999999</v>
-      </c>
-      <c r="F100" s="10">
-        <v>29</v>
-      </c>
-      <c r="G100" s="10">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="10" t="s">
+        <v>460</v>
+      </c>
+      <c r="B100" s="32" t="s">
+        <v>510</v>
+      </c>
+      <c r="C100" s="12" t="s">
+        <v>549</v>
+      </c>
+      <c r="D100" s="32"/>
+      <c r="E100" s="12">
+        <v>44</v>
+      </c>
+      <c r="F100" s="12">
+        <v>40.5</v>
+      </c>
+      <c r="G100" s="12">
         <f t="shared" si="23"/>
-        <v>7.12</v>
-      </c>
-      <c r="H100" s="7"/>
-      <c r="I100" s="7">
-        <v>29</v>
-      </c>
-      <c r="J100" s="38">
-        <v>-5</v>
-      </c>
-      <c r="K100" s="7" t="s">
-        <v>576</v>
+        <v>-7.95</v>
+      </c>
+      <c r="H100" s="13"/>
+      <c r="I100" s="13"/>
+      <c r="J100" s="37">
+        <v>40.5</v>
+      </c>
+      <c r="K100" s="13" t="s">
+        <v>567</v>
       </c>
     </row>
     <row r="101" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A101" s="10" t="s">
-        <v>460</v>
+        <v>572</v>
       </c>
       <c r="B101" s="32" t="s">
-        <v>510</v>
+        <v>545</v>
       </c>
       <c r="C101" s="12" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="D101" s="32"/>
       <c r="E101" s="12">
-        <v>44</v>
+        <v>77.400000000000006</v>
       </c>
       <c r="F101" s="12">
-        <v>40.5</v>
+        <v>72.5</v>
       </c>
       <c r="G101" s="12">
         <f t="shared" si="23"/>
-        <v>-7.95</v>
+        <v>-6.33</v>
       </c>
       <c r="H101" s="13"/>
       <c r="I101" s="13"/>
       <c r="J101" s="37">
-        <v>40.5</v>
+        <v>72.5</v>
       </c>
       <c r="K101" s="13" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="102" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="10" t="s">
-        <v>572</v>
-      </c>
-      <c r="B102" s="32" t="s">
-        <v>545</v>
-      </c>
-      <c r="C102" s="12" t="s">
-        <v>544</v>
-      </c>
-      <c r="D102" s="32"/>
-      <c r="E102" s="12">
-        <v>77.400000000000006</v>
-      </c>
-      <c r="F102" s="12">
-        <v>72.5</v>
-      </c>
-      <c r="G102" s="12">
-        <f t="shared" si="23"/>
-        <v>-6.33</v>
-      </c>
-      <c r="H102" s="13"/>
-      <c r="I102" s="13"/>
-      <c r="J102" s="37">
-        <v>72.5</v>
-      </c>
-      <c r="K102" s="13" t="s">
         <v>556</v>
       </c>
     </row>
-    <row r="103" spans="1:12" s="10" customFormat="1" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A103" s="12" t="s">
+    <row r="102" spans="1:12" s="10" customFormat="1" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A102" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="B103" s="31" t="s">
+      <c r="B102" s="31" t="s">
         <v>492</v>
       </c>
-      <c r="C103" s="15" t="s">
+      <c r="C102" s="15" t="s">
         <v>453</v>
       </c>
-      <c r="D103" s="31"/>
-      <c r="E103" s="10">
+      <c r="D102" s="31"/>
+      <c r="E102" s="10">
         <v>102.35</v>
       </c>
-      <c r="F103" s="10">
+      <c r="F102" s="10">
         <v>105.8</v>
       </c>
-      <c r="G103" s="10">
+      <c r="G102" s="10">
         <f t="shared" si="23"/>
         <v>3.37</v>
       </c>
-      <c r="H103" s="7"/>
-      <c r="I103" s="7"/>
-      <c r="J103" s="38">
+      <c r="H102" s="7"/>
+      <c r="I102" s="7"/>
+      <c r="J102" s="38">
         <v>104</v>
       </c>
-      <c r="K103" s="7" t="s">
+      <c r="K102" s="7" t="s">
         <v>552</v>
       </c>
-      <c r="L103" s="7" t="s">
+      <c r="L102" s="7" t="s">
         <v>555</v>
       </c>
     </row>
+    <row r="103" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="12" t="s">
+        <v>464</v>
+      </c>
+      <c r="B103" s="32" t="s">
+        <v>533</v>
+      </c>
+      <c r="C103" s="12" t="s">
+        <v>532</v>
+      </c>
+      <c r="D103" s="32"/>
+      <c r="E103" s="12">
+        <v>80</v>
+      </c>
+      <c r="F103" s="12">
+        <v>71</v>
+      </c>
+      <c r="G103" s="12">
+        <f t="shared" si="23"/>
+        <v>-11.25</v>
+      </c>
+      <c r="H103" s="13"/>
+      <c r="I103" s="13"/>
+      <c r="J103" s="37">
+        <v>71</v>
+      </c>
+      <c r="K103" s="13" t="s">
+        <v>554</v>
+      </c>
+      <c r="L103" s="12" t="s">
+        <v>559</v>
+      </c>
+    </row>
     <row r="104" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="12" t="s">
-        <v>464</v>
+      <c r="A104" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="B104" s="32" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="C104" s="12" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="D104" s="32"/>
       <c r="E104" s="12">
-        <v>80</v>
+        <v>39.731999999999999</v>
       </c>
       <c r="F104" s="12">
-        <v>71</v>
+        <v>37.700000000000003</v>
       </c>
       <c r="G104" s="12">
         <f t="shared" si="23"/>
-        <v>-11.25</v>
+        <v>-5.1100000000000003</v>
       </c>
       <c r="H104" s="13"/>
       <c r="I104" s="13"/>
       <c r="J104" s="37">
-        <v>71</v>
+        <v>-5</v>
       </c>
       <c r="K104" s="13" t="s">
-        <v>554</v>
-      </c>
-      <c r="L104" s="12" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="105" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="10" t="s">
-        <v>19</v>
+        <v>553</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" s="12" customFormat="1" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A105" s="12" t="s">
+        <v>531</v>
       </c>
       <c r="B105" s="32" t="s">
-        <v>528</v>
+        <v>492</v>
       </c>
       <c r="C105" s="12" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="D105" s="32"/>
       <c r="E105" s="12">
-        <v>39.731999999999999</v>
+        <v>128.1</v>
       </c>
       <c r="F105" s="12">
-        <v>37.700000000000003</v>
+        <v>119</v>
       </c>
       <c r="G105" s="12">
         <f t="shared" si="23"/>
-        <v>-5.1100000000000003</v>
+        <v>-7.1</v>
       </c>
       <c r="H105" s="13"/>
       <c r="I105" s="13"/>
       <c r="J105" s="37">
-        <v>-5</v>
+        <v>119</v>
       </c>
       <c r="K105" s="13" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="106" spans="1:12" s="12" customFormat="1" ht="37.5" x14ac:dyDescent="0.25">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="12" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="B106" s="32" t="s">
-        <v>492</v>
-      </c>
-      <c r="C106" s="12" t="s">
-        <v>519</v>
+        <v>505</v>
+      </c>
+      <c r="C106" s="16">
+        <v>45937</v>
       </c>
       <c r="D106" s="32"/>
       <c r="E106" s="12">
-        <v>128.1</v>
+        <v>20.77</v>
       </c>
       <c r="F106" s="12">
-        <v>119</v>
+        <v>20.55</v>
       </c>
       <c r="G106" s="12">
         <f t="shared" si="23"/>
-        <v>-7.1</v>
-      </c>
-      <c r="H106" s="13"/>
-      <c r="I106" s="13"/>
+        <v>-1.06</v>
+      </c>
+      <c r="H106" s="13" t="s">
+        <v>518</v>
+      </c>
+      <c r="I106" s="13">
+        <v>22.25</v>
+      </c>
       <c r="J106" s="37">
-        <v>119</v>
+        <v>-5</v>
       </c>
       <c r="K106" s="13" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="107" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
+        <v>482</v>
+      </c>
+      <c r="L106" s="12" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12" s="10" customFormat="1" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A107" s="12" t="s">
-        <v>527</v>
-      </c>
-      <c r="B107" s="32" t="s">
-        <v>505</v>
-      </c>
-      <c r="C107" s="16">
-        <v>45937</v>
-      </c>
-      <c r="D107" s="32"/>
-      <c r="E107" s="12">
-        <v>20.77</v>
-      </c>
-      <c r="F107" s="12">
-        <v>20.55</v>
-      </c>
-      <c r="G107" s="12">
+        <v>406</v>
+      </c>
+      <c r="B107" s="31">
+        <v>4200</v>
+      </c>
+      <c r="C107" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="D107" s="31"/>
+      <c r="E107" s="10">
+        <v>15.4</v>
+      </c>
+      <c r="F107" s="10">
+        <v>20</v>
+      </c>
+      <c r="G107" s="10">
         <f t="shared" si="23"/>
-        <v>-1.06</v>
-      </c>
-      <c r="H107" s="13" t="s">
-        <v>518</v>
-      </c>
-      <c r="I107" s="13">
-        <v>22.25</v>
-      </c>
-      <c r="J107" s="37">
-        <v>-5</v>
-      </c>
-      <c r="K107" s="13" t="s">
-        <v>482</v>
-      </c>
-      <c r="L107" s="12" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="108" spans="1:12" s="10" customFormat="1" ht="56.25" x14ac:dyDescent="0.25">
+        <v>29.87</v>
+      </c>
+      <c r="H107" s="7" t="s">
+        <v>516</v>
+      </c>
+      <c r="I107" s="7">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="J107" s="38" t="s">
+        <v>522</v>
+      </c>
+      <c r="K107" s="7" t="s">
+        <v>524</v>
+      </c>
+      <c r="L107" s="7" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A108" s="12" t="s">
-        <v>406</v>
-      </c>
-      <c r="B108" s="31">
-        <v>4200</v>
-      </c>
-      <c r="C108" s="15" t="s">
-        <v>115</v>
+        <v>34</v>
+      </c>
+      <c r="B108" s="31" t="s">
+        <v>489</v>
+      </c>
+      <c r="C108" s="15">
+        <v>45967</v>
       </c>
       <c r="D108" s="31"/>
       <c r="E108" s="10">
-        <v>15.4</v>
+        <v>15.871</v>
       </c>
       <c r="F108" s="10">
-        <v>20</v>
+        <v>18.8</v>
       </c>
       <c r="G108" s="10">
         <f t="shared" si="23"/>
-        <v>29.87</v>
-      </c>
-      <c r="H108" s="7" t="s">
-        <v>516</v>
-      </c>
+        <v>18.46</v>
+      </c>
+      <c r="H108" s="7"/>
       <c r="I108" s="7">
-        <v>19.899999999999999</v>
-      </c>
-      <c r="J108" s="38" t="s">
-        <v>522</v>
+        <v>18.8</v>
+      </c>
+      <c r="J108" s="38">
+        <v>16.649999999999999</v>
       </c>
       <c r="K108" s="7" t="s">
-        <v>524</v>
-      </c>
-      <c r="L108" s="7" t="s">
-        <v>457</v>
+        <v>480</v>
       </c>
     </row>
     <row r="109" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="12" t="s">
-        <v>34</v>
+      <c r="A109" s="10" t="s">
+        <v>10</v>
       </c>
       <c r="B109" s="31" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C109" s="15">
         <v>45967</v>
       </c>
       <c r="D109" s="31"/>
       <c r="E109" s="10">
-        <v>15.871</v>
+        <v>14.074999999999999</v>
       </c>
       <c r="F109" s="10">
-        <v>18.8</v>
+        <v>15</v>
       </c>
       <c r="G109" s="10">
         <f t="shared" si="23"/>
-        <v>18.46</v>
+        <v>6.57</v>
       </c>
       <c r="H109" s="7"/>
       <c r="I109" s="7">
-        <v>18.8</v>
-      </c>
-      <c r="J109" s="38">
-        <v>16.649999999999999</v>
+        <v>17.5</v>
+      </c>
+      <c r="J109" s="38" t="s">
+        <v>513</v>
       </c>
       <c r="K109" s="7" t="s">
-        <v>480</v>
+        <v>507</v>
       </c>
     </row>
     <row r="110" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="10" t="s">
-        <v>10</v>
+        <v>420</v>
       </c>
       <c r="B110" s="31" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="C110" s="15">
-        <v>45967</v>
+        <v>45997</v>
       </c>
       <c r="D110" s="31"/>
       <c r="E110" s="10">
-        <v>14.074999999999999</v>
+        <v>18.215</v>
       </c>
       <c r="F110" s="10">
-        <v>15</v>
+        <v>20.3</v>
       </c>
       <c r="G110" s="10">
         <f t="shared" si="23"/>
-        <v>6.57</v>
+        <v>11.45</v>
       </c>
       <c r="H110" s="7"/>
       <c r="I110" s="7">
-        <v>17.5</v>
+        <v>20.3</v>
       </c>
       <c r="J110" s="38" t="s">
-        <v>513</v>
+        <v>494</v>
       </c>
       <c r="K110" s="7" t="s">
-        <v>507</v>
+        <v>496</v>
       </c>
     </row>
     <row r="111" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A111" s="10" t="s">
-        <v>420</v>
+        <v>1</v>
       </c>
       <c r="B111" s="31" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C111" s="15">
-        <v>45997</v>
+        <v>45936</v>
       </c>
       <c r="D111" s="31"/>
       <c r="E111" s="10">
-        <v>18.215</v>
+        <v>10.909000000000001</v>
       </c>
       <c r="F111" s="10">
-        <v>20.3</v>
+        <v>12.75</v>
       </c>
       <c r="G111" s="10">
-        <f t="shared" si="23"/>
-        <v>11.45</v>
+        <f t="shared" ref="G111:G142" si="24">ROUND((F111 - E111) / E111 * 100, 2)</f>
+        <v>16.88</v>
       </c>
       <c r="H111" s="7"/>
       <c r="I111" s="7">
-        <v>20.3</v>
-      </c>
-      <c r="J111" s="38" t="s">
-        <v>494</v>
+        <v>12.75</v>
+      </c>
+      <c r="J111" s="38">
+        <v>11.6</v>
       </c>
       <c r="K111" s="7" t="s">
-        <v>496</v>
+        <v>481</v>
       </c>
     </row>
     <row r="112" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A112" s="10" t="s">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="B112" s="31" t="s">
-        <v>490</v>
-      </c>
-      <c r="C112" s="15">
-        <v>45936</v>
+        <v>492</v>
+      </c>
+      <c r="C112" s="15" t="s">
+        <v>465</v>
       </c>
       <c r="D112" s="31"/>
       <c r="E112" s="10">
-        <v>10.909000000000001</v>
+        <v>35.979999999999997</v>
       </c>
       <c r="F112" s="10">
-        <v>12.75</v>
+        <v>38.299999999999997</v>
       </c>
       <c r="G112" s="10">
-        <f t="shared" ref="G112:G143" si="24">ROUND((F112 - E112) / E112 * 100, 2)</f>
-        <v>16.88</v>
-      </c>
-      <c r="H112" s="7"/>
+        <f t="shared" si="24"/>
+        <v>6.45</v>
+      </c>
+      <c r="H112" s="7" t="s">
+        <v>498</v>
+      </c>
       <c r="I112" s="7">
-        <v>12.75</v>
-      </c>
-      <c r="J112" s="38">
-        <v>11.6</v>
+        <v>38.299999999999997</v>
+      </c>
+      <c r="J112" s="38" t="s">
+        <v>478</v>
       </c>
       <c r="K112" s="7" t="s">
-        <v>481</v>
+        <v>497</v>
       </c>
     </row>
     <row r="113" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A113" s="10" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="B113" s="31" t="s">
-        <v>492</v>
-      </c>
-      <c r="C113" s="15" t="s">
-        <v>465</v>
+        <v>510</v>
+      </c>
+      <c r="C113" s="15">
+        <v>45936</v>
       </c>
       <c r="D113" s="31"/>
       <c r="E113" s="10">
-        <v>35.979999999999997</v>
+        <v>22.350999999999999</v>
       </c>
       <c r="F113" s="10">
-        <v>38.299999999999997</v>
+        <v>23.4</v>
       </c>
       <c r="G113" s="10">
         <f t="shared" si="24"/>
-        <v>6.45</v>
-      </c>
-      <c r="H113" s="7" t="s">
-        <v>498</v>
-      </c>
+        <v>4.6900000000000004</v>
+      </c>
+      <c r="H113" s="7"/>
       <c r="I113" s="7">
-        <v>38.299999999999997</v>
-      </c>
-      <c r="J113" s="38" t="s">
-        <v>478</v>
-      </c>
+        <v>23.4</v>
+      </c>
+      <c r="J113" s="38"/>
       <c r="K113" s="7" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="114" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.25">
+        <v>441</v>
+      </c>
+      <c r="L113" s="10" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A114" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="B114" s="31" t="s">
-        <v>510</v>
-      </c>
-      <c r="C114" s="15">
-        <v>45936</v>
-      </c>
-      <c r="D114" s="31"/>
-      <c r="E114" s="10">
-        <v>22.350999999999999</v>
-      </c>
-      <c r="F114" s="10">
-        <v>23.4</v>
-      </c>
-      <c r="G114" s="10">
+        <v>463</v>
+      </c>
+      <c r="B114" s="32"/>
+      <c r="C114" s="16" t="s">
+        <v>429</v>
+      </c>
+      <c r="D114" s="32"/>
+      <c r="E114" s="12">
+        <v>20.48</v>
+      </c>
+      <c r="F114" s="12">
+        <v>19.95</v>
+      </c>
+      <c r="G114" s="12">
         <f t="shared" si="24"/>
-        <v>4.6900000000000004</v>
-      </c>
-      <c r="H114" s="7"/>
-      <c r="I114" s="7">
-        <v>23.4</v>
-      </c>
-      <c r="J114" s="38"/>
-      <c r="K114" s="7" t="s">
-        <v>441</v>
-      </c>
-      <c r="L114" s="10" t="s">
-        <v>473</v>
+        <v>-2.59</v>
+      </c>
+      <c r="H114" s="13"/>
+      <c r="I114" s="13">
+        <v>22.75</v>
+      </c>
+      <c r="J114" s="37">
+        <v>-5</v>
+      </c>
+      <c r="K114" s="13" t="s">
+        <v>461</v>
+      </c>
+      <c r="L114" s="12" t="s">
+        <v>466</v>
       </c>
     </row>
     <row r="115" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A115" s="10" t="s">
-        <v>463</v>
+        <v>422</v>
       </c>
       <c r="B115" s="32"/>
-      <c r="C115" s="16" t="s">
-        <v>429</v>
+      <c r="C115" s="16">
+        <v>45967</v>
       </c>
       <c r="D115" s="32"/>
       <c r="E115" s="12">
-        <v>20.48</v>
+        <v>14.361000000000001</v>
       </c>
       <c r="F115" s="12">
-        <v>19.95</v>
+        <v>14.25</v>
       </c>
       <c r="G115" s="12">
         <f t="shared" si="24"/>
-        <v>-2.59</v>
+        <v>-0.77</v>
       </c>
       <c r="H115" s="13"/>
       <c r="I115" s="13">
-        <v>22.75</v>
-      </c>
-      <c r="J115" s="37">
-        <v>-5</v>
+        <v>17</v>
+      </c>
+      <c r="J115" s="37" t="s">
+        <v>456</v>
       </c>
       <c r="K115" s="13" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="L115" s="12" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="116" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="B116" s="32"/>
-      <c r="C116" s="16">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B116" s="31"/>
+      <c r="C116" s="15">
         <v>45967</v>
       </c>
-      <c r="D116" s="32"/>
-      <c r="E116" s="12">
-        <v>14.361000000000001</v>
-      </c>
-      <c r="F116" s="12">
-        <v>14.25</v>
-      </c>
-      <c r="G116" s="12">
+      <c r="D116" s="31"/>
+      <c r="E116" s="10">
+        <v>34.1</v>
+      </c>
+      <c r="F116" s="10">
+        <v>37.1</v>
+      </c>
+      <c r="G116" s="10">
         <f t="shared" si="24"/>
-        <v>-0.77</v>
-      </c>
-      <c r="H116" s="13"/>
-      <c r="I116" s="13">
-        <v>17</v>
-      </c>
-      <c r="J116" s="37" t="s">
-        <v>456</v>
-      </c>
-      <c r="K116" s="13" t="s">
-        <v>455</v>
-      </c>
-      <c r="L116" s="12" t="s">
-        <v>459</v>
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="H116" s="7"/>
+      <c r="I116" s="7">
+        <v>37.1</v>
+      </c>
+      <c r="J116" s="38" t="s">
+        <v>443</v>
+      </c>
+      <c r="K116" s="7" t="s">
+        <v>450</v>
       </c>
     </row>
     <row r="117" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A117" s="12" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B117" s="31"/>
       <c r="C117" s="15">
-        <v>45967</v>
+        <v>45722</v>
       </c>
       <c r="D117" s="31"/>
       <c r="E117" s="10">
-        <v>34.1</v>
+        <v>34.4</v>
       </c>
       <c r="F117" s="10">
-        <v>37.1</v>
+        <v>39.15</v>
       </c>
       <c r="G117" s="10">
         <f t="shared" si="24"/>
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="H117" s="7"/>
+        <v>13.81</v>
+      </c>
+      <c r="H117" s="7" t="s">
+        <v>399</v>
+      </c>
       <c r="I117" s="7">
-        <v>37.1</v>
+        <v>38.799999999999997</v>
       </c>
       <c r="J117" s="38" t="s">
-        <v>443</v>
+        <v>415</v>
       </c>
       <c r="K117" s="7" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="118" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="B118" s="31"/>
-      <c r="C118" s="15">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B118" s="32"/>
+      <c r="C118" s="16">
         <v>45722</v>
       </c>
-      <c r="D118" s="31"/>
-      <c r="E118" s="10">
-        <v>34.4</v>
-      </c>
-      <c r="F118" s="10">
-        <v>39.15</v>
-      </c>
-      <c r="G118" s="10">
+      <c r="D118" s="32"/>
+      <c r="E118" s="12">
+        <v>55.844999999999999</v>
+      </c>
+      <c r="F118" s="12">
+        <v>55.1</v>
+      </c>
+      <c r="G118" s="12">
         <f t="shared" si="24"/>
-        <v>13.81</v>
-      </c>
-      <c r="H118" s="7" t="s">
-        <v>399</v>
-      </c>
-      <c r="I118" s="7">
-        <v>38.799999999999997</v>
-      </c>
-      <c r="J118" s="38" t="s">
-        <v>415</v>
-      </c>
-      <c r="K118" s="7" t="s">
-        <v>419</v>
+        <v>-1.33</v>
+      </c>
+      <c r="H118" s="13"/>
+      <c r="I118" s="13">
+        <v>60.6</v>
+      </c>
+      <c r="J118" s="37" t="s">
+        <v>416</v>
+      </c>
+      <c r="K118" s="13" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="119" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A119" s="10" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B119" s="32"/>
-      <c r="C119" s="16">
-        <v>45722</v>
+      <c r="C119" s="16" t="s">
+        <v>117</v>
       </c>
       <c r="D119" s="32"/>
       <c r="E119" s="12">
-        <v>55.844999999999999</v>
+        <v>14.114000000000001</v>
       </c>
       <c r="F119" s="12">
-        <v>55.1</v>
+        <v>14</v>
       </c>
       <c r="G119" s="12">
         <f t="shared" si="24"/>
-        <v>-1.33</v>
-      </c>
-      <c r="H119" s="13"/>
+        <v>-0.81</v>
+      </c>
+      <c r="H119" s="13" t="s">
+        <v>118</v>
+      </c>
       <c r="I119" s="13">
-        <v>60.6</v>
+        <v>16.2</v>
       </c>
       <c r="J119" s="37" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="K119" s="13" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="120" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B120" s="32"/>
-      <c r="C120" s="16" t="s">
-        <v>117</v>
-      </c>
-      <c r="D120" s="32"/>
-      <c r="E120" s="12">
-        <v>14.114000000000001</v>
-      </c>
-      <c r="F120" s="12">
-        <v>14</v>
-      </c>
-      <c r="G120" s="12">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="120" spans="1:12" s="10" customFormat="1" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A120" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B120" s="31"/>
+      <c r="C120" s="15">
+        <v>45965</v>
+      </c>
+      <c r="D120" s="31"/>
+      <c r="E120" s="10">
+        <v>23.4</v>
+      </c>
+      <c r="F120" s="10">
+        <v>35.15</v>
+      </c>
+      <c r="G120" s="10">
         <f t="shared" si="24"/>
-        <v>-0.81</v>
-      </c>
-      <c r="H120" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="I120" s="13">
-        <v>16.2</v>
-      </c>
-      <c r="J120" s="37" t="s">
-        <v>417</v>
-      </c>
-      <c r="K120" s="13" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="121" spans="1:12" s="10" customFormat="1" ht="37.5" x14ac:dyDescent="0.25">
+        <v>50.21</v>
+      </c>
+      <c r="H120" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="I120" s="7">
+        <v>38.200000000000003</v>
+      </c>
+      <c r="J120" s="38">
+        <v>35.15</v>
+      </c>
+      <c r="K120" s="7" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A121" s="12" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="B121" s="31"/>
-      <c r="C121" s="15">
-        <v>45965</v>
+      <c r="C121" s="15" t="s">
+        <v>100</v>
       </c>
       <c r="D121" s="31"/>
       <c r="E121" s="10">
-        <v>23.4</v>
+        <v>22</v>
       </c>
       <c r="F121" s="10">
-        <v>35.15</v>
+        <v>25.4</v>
       </c>
       <c r="G121" s="10">
         <f t="shared" si="24"/>
-        <v>50.21</v>
+        <v>15.45</v>
       </c>
       <c r="H121" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="I121" s="7">
-        <v>38.200000000000003</v>
+        <v>124</v>
+      </c>
+      <c r="I121" s="7" t="s">
+        <v>395</v>
       </c>
       <c r="J121" s="38">
-        <v>35.15</v>
+        <v>25.4</v>
       </c>
       <c r="K121" s="7" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="122" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="B122" s="31"/>
-      <c r="C122" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="D122" s="31"/>
-      <c r="E122" s="10">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="122" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="F122" s="10">
-        <v>25.4</v>
-      </c>
-      <c r="G122" s="10">
-        <f t="shared" si="24"/>
-        <v>15.45</v>
-      </c>
-      <c r="H122" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="I122" s="7" t="s">
-        <v>395</v>
-      </c>
-      <c r="J122" s="38">
-        <v>25.4</v>
-      </c>
-      <c r="K122" s="7" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="123" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="B123" s="32"/>
-      <c r="C123" s="16">
+      <c r="B122" s="32"/>
+      <c r="C122" s="16">
         <v>45722</v>
       </c>
-      <c r="D123" s="32"/>
-      <c r="E123" s="12">
+      <c r="D122" s="32"/>
+      <c r="E122" s="12">
         <v>28.623000000000001</v>
       </c>
-      <c r="F123" s="12">
+      <c r="F122" s="12">
         <v>27.2</v>
       </c>
-      <c r="G123" s="12">
+      <c r="G122" s="12">
         <f t="shared" si="24"/>
         <v>-4.97</v>
       </c>
-      <c r="H123" s="13" t="s">
+      <c r="H122" s="13" t="s">
         <v>400</v>
       </c>
-      <c r="I123" s="13">
+      <c r="I122" s="13">
         <v>31.1</v>
       </c>
-      <c r="J123" s="37">
+      <c r="J122" s="37">
         <v>-5</v>
       </c>
-      <c r="K123" s="13" t="s">
+      <c r="K122" s="13" t="s">
         <v>409</v>
       </c>
     </row>
+    <row r="123" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B123" s="31"/>
+      <c r="C123" s="15">
+        <v>45874</v>
+      </c>
+      <c r="D123" s="31"/>
+      <c r="E123" s="10">
+        <v>12.45</v>
+      </c>
+      <c r="F123" s="10">
+        <v>13.6</v>
+      </c>
+      <c r="G123" s="10">
+        <f t="shared" si="24"/>
+        <v>9.24</v>
+      </c>
+      <c r="H123" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="I123" s="7">
+        <v>13.65</v>
+      </c>
+      <c r="J123" s="38">
+        <v>5</v>
+      </c>
+      <c r="K123" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
     <row r="124" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="10" t="s">
-        <v>7</v>
+      <c r="A124" s="12" t="s">
+        <v>396</v>
       </c>
       <c r="B124" s="31"/>
-      <c r="C124" s="15">
-        <v>45874</v>
+      <c r="C124" s="15" t="s">
+        <v>103</v>
       </c>
       <c r="D124" s="31"/>
       <c r="E124" s="10">
-        <v>12.45</v>
+        <v>21.4</v>
       </c>
       <c r="F124" s="10">
-        <v>13.6</v>
+        <v>21.55</v>
       </c>
       <c r="G124" s="10">
         <f t="shared" si="24"/>
-        <v>9.24</v>
+        <v>0.7</v>
       </c>
       <c r="H124" s="7" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="I124" s="7">
-        <v>13.65</v>
+        <v>23</v>
       </c>
       <c r="J124" s="38">
         <v>5</v>
       </c>
       <c r="K124" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="125" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="12" t="s">
-        <v>396</v>
-      </c>
-      <c r="B125" s="31"/>
-      <c r="C125" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="D125" s="31"/>
-      <c r="E125" s="10">
-        <v>21.4</v>
-      </c>
-      <c r="F125" s="10">
-        <v>21.55</v>
-      </c>
-      <c r="G125" s="10">
-        <f t="shared" si="24"/>
-        <v>0.7</v>
-      </c>
-      <c r="H125" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="I125" s="7">
-        <v>23</v>
-      </c>
-      <c r="J125" s="38">
-        <v>5</v>
-      </c>
-      <c r="K125" s="7" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="126" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="10" t="s">
+    <row r="125" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="B126" s="32"/>
-      <c r="C126" s="16" t="s">
+      <c r="B125" s="32"/>
+      <c r="C125" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="D126" s="32"/>
-      <c r="E126" s="12">
+      <c r="D125" s="32"/>
+      <c r="E125" s="12">
         <v>13.411</v>
       </c>
-      <c r="F126" s="12">
+      <c r="F125" s="12">
         <v>13.1</v>
       </c>
-      <c r="G126" s="12">
+      <c r="G125" s="12">
         <f t="shared" si="24"/>
         <v>-2.3199999999999998</v>
       </c>
-      <c r="H126" s="13" t="s">
+      <c r="H125" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="I126" s="13"/>
-      <c r="J126" s="37"/>
-      <c r="K126" s="13" t="s">
+      <c r="I125" s="13"/>
+      <c r="J125" s="37"/>
+      <c r="K125" s="13" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="127" spans="1:12" s="10" customFormat="1" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A127" s="10" t="s">
+    <row r="126" spans="1:12" s="10" customFormat="1" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A126" s="10" t="s">
         <v>102</v>
+      </c>
+      <c r="B126" s="31"/>
+      <c r="C126" s="15">
+        <v>45965</v>
+      </c>
+      <c r="D126" s="31"/>
+      <c r="E126" s="10">
+        <v>4.16</v>
+      </c>
+      <c r="F126" s="10">
+        <v>4.4800000000000004</v>
+      </c>
+      <c r="G126" s="10">
+        <f t="shared" si="24"/>
+        <v>7.69</v>
+      </c>
+      <c r="H126" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="I126" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="J126" s="38">
+        <v>5</v>
+      </c>
+      <c r="K126" s="7" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="127" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="12" t="s">
+        <v>29</v>
       </c>
       <c r="B127" s="31"/>
       <c r="C127" s="15">
-        <v>45965</v>
+        <v>45905</v>
       </c>
       <c r="D127" s="31"/>
       <c r="E127" s="10">
-        <v>4.16</v>
+        <v>34.94</v>
       </c>
       <c r="F127" s="10">
-        <v>4.4800000000000004</v>
+        <v>38.200000000000003</v>
       </c>
       <c r="G127" s="10">
         <f t="shared" si="24"/>
-        <v>7.69</v>
+        <v>9.33</v>
       </c>
       <c r="H127" s="7" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="I127" s="7">
-        <v>4.5</v>
+        <v>38.200000000000003</v>
       </c>
       <c r="J127" s="38">
         <v>5</v>
       </c>
       <c r="K127" s="7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="128" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="12" t="s">
-        <v>29</v>
+      <c r="A128" s="10" t="s">
+        <v>41</v>
       </c>
       <c r="B128" s="31"/>
       <c r="C128" s="15">
-        <v>45905</v>
+        <v>45782</v>
       </c>
       <c r="D128" s="31"/>
       <c r="E128" s="10">
-        <v>34.94</v>
+        <v>21.67</v>
       </c>
       <c r="F128" s="10">
-        <v>38.200000000000003</v>
+        <v>22.45</v>
       </c>
       <c r="G128" s="10">
         <f t="shared" si="24"/>
-        <v>9.33</v>
-      </c>
-      <c r="H128" s="7" t="s">
-        <v>111</v>
-      </c>
+        <v>3.6</v>
+      </c>
+      <c r="H128" s="7"/>
       <c r="I128" s="7">
-        <v>38.200000000000003</v>
+        <v>22.7</v>
       </c>
       <c r="J128" s="38">
         <v>5</v>
       </c>
       <c r="K128" s="7" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
     </row>
     <row r="129" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A129" s="10" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="B129" s="31"/>
       <c r="C129" s="15">
-        <v>45782</v>
+        <v>45813</v>
       </c>
       <c r="D129" s="31"/>
       <c r="E129" s="10">
-        <v>21.67</v>
+        <v>27.45</v>
       </c>
       <c r="F129" s="10">
-        <v>22.45</v>
+        <v>29.4</v>
       </c>
       <c r="G129" s="10">
         <f t="shared" si="24"/>
-        <v>3.6</v>
-      </c>
-      <c r="H129" s="7"/>
-      <c r="I129" s="7">
-        <v>22.7</v>
-      </c>
+        <v>7.1</v>
+      </c>
+      <c r="H129" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="I129" s="7"/>
       <c r="J129" s="38">
         <v>5</v>
       </c>
       <c r="K129" s="7" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="130" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11" s="10" customFormat="1" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A130" s="10" t="s">
-        <v>30</v>
+        <v>104</v>
       </c>
       <c r="B130" s="31"/>
-      <c r="C130" s="15">
-        <v>45813</v>
+      <c r="C130" s="15" t="s">
+        <v>100</v>
       </c>
       <c r="D130" s="31"/>
       <c r="E130" s="10">
-        <v>27.45</v>
+        <v>11.3</v>
       </c>
       <c r="F130" s="10">
-        <v>29.4</v>
+        <v>12.6</v>
       </c>
       <c r="G130" s="10">
         <f t="shared" si="24"/>
-        <v>7.1</v>
+        <v>11.5</v>
       </c>
       <c r="H130" s="7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I130" s="7"/>
-      <c r="J130" s="38">
-        <v>5</v>
-      </c>
+      <c r="J130" s="38"/>
       <c r="K130" s="7" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="131" spans="1:11" s="10" customFormat="1" ht="37.5" x14ac:dyDescent="0.25">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A131" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="B131" s="31"/>
-      <c r="C131" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="D131" s="31"/>
-      <c r="E131" s="10">
-        <v>11.3</v>
-      </c>
-      <c r="F131" s="10">
-        <v>12.6</v>
-      </c>
-      <c r="G131" s="10">
-        <f t="shared" si="24"/>
-        <v>11.5</v>
-      </c>
-      <c r="H131" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="I131" s="7"/>
-      <c r="J131" s="38"/>
-      <c r="K131" s="7" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="132" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="B132" s="32"/>
-      <c r="C132" s="16">
+      <c r="B131" s="32"/>
+      <c r="C131" s="16">
         <v>45905</v>
       </c>
-      <c r="D132" s="32"/>
-      <c r="E132" s="12">
+      <c r="D131" s="32"/>
+      <c r="E131" s="12">
         <v>92.4</v>
       </c>
-      <c r="F132" s="12">
+      <c r="F131" s="12">
         <v>88.9</v>
       </c>
-      <c r="G132" s="12">
+      <c r="G131" s="12">
         <f t="shared" si="24"/>
         <v>-3.79</v>
       </c>
-      <c r="H132" s="13" t="s">
+      <c r="H131" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="I132" s="13"/>
-      <c r="J132" s="37">
+      <c r="I131" s="13"/>
+      <c r="J131" s="37">
         <v>5</v>
       </c>
-      <c r="K132" s="13" t="s">
+      <c r="K131" s="13" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="133" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="10" t="s">
+    <row r="132" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A132" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B133" s="31"/>
-      <c r="C133" s="15" t="s">
+      <c r="B132" s="31"/>
+      <c r="C132" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="D133" s="31"/>
-      <c r="E133" s="10">
+      <c r="D132" s="31"/>
+      <c r="E132" s="10">
         <v>31.832000000000001</v>
       </c>
-      <c r="F133" s="10">
+      <c r="F132" s="10">
         <v>34</v>
       </c>
-      <c r="G133" s="10">
+      <c r="G132" s="10">
         <f t="shared" si="24"/>
         <v>6.81</v>
       </c>
-      <c r="H133" s="7"/>
-      <c r="I133" s="7">
+      <c r="H132" s="7"/>
+      <c r="I132" s="7">
         <v>34</v>
       </c>
-      <c r="J133" s="38">
+      <c r="J132" s="38">
         <v>5</v>
       </c>
-      <c r="K133" s="7"/>
+      <c r="K132" s="7"/>
+    </row>
+    <row r="133" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A133" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B133" s="32"/>
+      <c r="C133" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="D133" s="32"/>
+      <c r="E133" s="12">
+        <v>12.05</v>
+      </c>
+      <c r="F133" s="12">
+        <v>11.75</v>
+      </c>
+      <c r="G133" s="12">
+        <f t="shared" si="24"/>
+        <v>-2.4900000000000002</v>
+      </c>
+      <c r="H133" s="13"/>
+      <c r="I133" s="13">
+        <v>12.95</v>
+      </c>
+      <c r="J133" s="37">
+        <v>5</v>
+      </c>
+      <c r="K133" s="13" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="134" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="12" t="s">
-        <v>11</v>
+      <c r="A134" s="10" t="s">
+        <v>28</v>
       </c>
       <c r="B134" s="32"/>
       <c r="C134" s="16" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D134" s="32"/>
       <c r="E134" s="12">
-        <v>12.05</v>
+        <v>62</v>
       </c>
       <c r="F134" s="12">
-        <v>11.75</v>
+        <v>58.6</v>
       </c>
       <c r="G134" s="12">
         <f t="shared" si="24"/>
-        <v>-2.4900000000000002</v>
-      </c>
-      <c r="H134" s="13"/>
-      <c r="I134" s="13">
-        <v>12.95</v>
-      </c>
-      <c r="J134" s="37">
-        <v>5</v>
-      </c>
+        <v>-5.48</v>
+      </c>
+      <c r="H134" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="I134" s="13"/>
+      <c r="J134" s="37"/>
       <c r="K134" s="13" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="135" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B135" s="32"/>
-      <c r="C135" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="D135" s="32"/>
-      <c r="E135" s="12">
-        <v>62</v>
-      </c>
-      <c r="F135" s="12">
-        <v>58.6</v>
-      </c>
-      <c r="G135" s="12">
-        <f t="shared" si="24"/>
-        <v>-5.48</v>
-      </c>
-      <c r="H135" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="I135" s="13"/>
-      <c r="J135" s="37"/>
-      <c r="K135" s="13" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="136" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="12" t="s">
+    <row r="135" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A135" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="B136" s="31"/>
-      <c r="C136" s="15">
+      <c r="B135" s="31"/>
+      <c r="C135" s="15">
         <v>45965</v>
       </c>
-      <c r="D136" s="31"/>
-      <c r="E136" s="10">
+      <c r="D135" s="31"/>
+      <c r="E135" s="10">
         <v>83.9</v>
       </c>
-      <c r="F136" s="10">
+      <c r="F135" s="10">
         <v>91.2</v>
       </c>
-      <c r="G136" s="10">
+      <c r="G135" s="10">
         <f t="shared" si="24"/>
         <v>8.6999999999999993</v>
       </c>
-      <c r="H136" s="7" t="s">
+      <c r="H135" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="I136" s="7"/>
-      <c r="J136" s="38"/>
-      <c r="K136" s="7" t="s">
+      <c r="I135" s="7"/>
+      <c r="J135" s="38"/>
+      <c r="K135" s="7" t="s">
         <v>90</v>
       </c>
     </row>
+    <row r="136" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A136" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B136" s="32"/>
+      <c r="C136" s="16">
+        <v>45965</v>
+      </c>
+      <c r="D136" s="32"/>
+      <c r="E136" s="12">
+        <v>15.365</v>
+      </c>
+      <c r="F136" s="12">
+        <v>14.8</v>
+      </c>
+      <c r="G136" s="12">
+        <f t="shared" si="24"/>
+        <v>-3.68</v>
+      </c>
+      <c r="H136" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="I136" s="13"/>
+      <c r="J136" s="37"/>
+      <c r="K136" s="13" t="s">
+        <v>93</v>
+      </c>
+    </row>
     <row r="137" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A137" s="12" t="s">
-        <v>15</v>
+      <c r="A137" s="10" t="s">
+        <v>11</v>
       </c>
       <c r="B137" s="32"/>
-      <c r="C137" s="16">
-        <v>45965</v>
+      <c r="C137" s="16" t="s">
+        <v>87</v>
       </c>
       <c r="D137" s="32"/>
       <c r="E137" s="12">
-        <v>15.365</v>
+        <v>31.8</v>
       </c>
       <c r="F137" s="12">
-        <v>14.8</v>
+        <v>30.3</v>
       </c>
       <c r="G137" s="12">
         <f t="shared" si="24"/>
-        <v>-3.68</v>
+        <v>-4.72</v>
       </c>
       <c r="H137" s="13" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="I137" s="13"/>
       <c r="J137" s="37"/>
       <c r="K137" s="13" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="138" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A138" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B138" s="32"/>
-      <c r="C138" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="D138" s="32"/>
-      <c r="E138" s="12">
-        <v>31.8</v>
-      </c>
-      <c r="F138" s="12">
-        <v>30.3</v>
-      </c>
-      <c r="G138" s="12">
-        <f t="shared" si="24"/>
-        <v>-4.72</v>
-      </c>
-      <c r="H138" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="I138" s="13"/>
-      <c r="J138" s="37"/>
-      <c r="K138" s="13" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="139" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="12" t="s">
+    <row r="138" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A138" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B139" s="31"/>
-      <c r="C139" s="15">
+      <c r="B138" s="31"/>
+      <c r="C138" s="15">
         <v>45965</v>
       </c>
-      <c r="D139" s="31"/>
-      <c r="E139" s="10">
+      <c r="D138" s="31"/>
+      <c r="E138" s="10">
         <v>11.7</v>
       </c>
-      <c r="F139" s="10">
+      <c r="F138" s="10">
         <v>13</v>
       </c>
-      <c r="G139" s="10">
+      <c r="G138" s="10">
         <f t="shared" si="24"/>
         <v>11.11</v>
       </c>
-      <c r="H139" s="7" t="s">
+      <c r="H138" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="I139" s="7"/>
-      <c r="J139" s="38"/>
-      <c r="K139" s="7" t="s">
+      <c r="I138" s="7"/>
+      <c r="J138" s="38"/>
+      <c r="K138" s="7" t="s">
         <v>89</v>
       </c>
     </row>
+    <row r="139" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A139" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B139" s="32"/>
+      <c r="C139" s="16">
+        <v>45965</v>
+      </c>
+      <c r="D139" s="32"/>
+      <c r="E139" s="12">
+        <v>2.6669999999999998</v>
+      </c>
+      <c r="F139" s="12">
+        <v>2.5099999999999998</v>
+      </c>
+      <c r="G139" s="12">
+        <f t="shared" si="24"/>
+        <v>-5.89</v>
+      </c>
+      <c r="H139" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="I139" s="13"/>
+      <c r="J139" s="37"/>
+      <c r="K139" s="13"/>
+    </row>
     <row r="140" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="12" t="s">
-        <v>14</v>
+      <c r="A140" s="10" t="s">
+        <v>66</v>
       </c>
       <c r="B140" s="32"/>
       <c r="C140" s="16">
-        <v>45965</v>
+        <v>45661</v>
       </c>
       <c r="D140" s="32"/>
       <c r="E140" s="12">
-        <v>2.6669999999999998</v>
+        <v>4.55</v>
       </c>
       <c r="F140" s="12">
-        <v>2.5099999999999998</v>
+        <v>4.53</v>
       </c>
       <c r="G140" s="12">
         <f t="shared" si="24"/>
-        <v>-5.89</v>
+        <v>-0.44</v>
       </c>
       <c r="H140" s="13" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="I140" s="13"/>
       <c r="J140" s="37"/>
-      <c r="K140" s="13"/>
+      <c r="K140" s="13" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="141" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="10" t="s">
-        <v>66</v>
+      <c r="A141" s="12" t="s">
+        <v>31</v>
       </c>
       <c r="B141" s="32"/>
-      <c r="C141" s="16">
-        <v>45661</v>
-      </c>
       <c r="D141" s="32"/>
       <c r="E141" s="12">
-        <v>4.55</v>
+        <v>24.45</v>
       </c>
       <c r="F141" s="12">
-        <v>4.53</v>
+        <v>23.9</v>
       </c>
       <c r="G141" s="12">
         <f t="shared" si="24"/>
-        <v>-0.44</v>
+        <v>-2.25</v>
       </c>
       <c r="H141" s="13" t="s">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="I141" s="13"/>
       <c r="J141" s="37"/>
       <c r="K141" s="13" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="142" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="142" spans="1:11" s="12" customFormat="1" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A142" s="12" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="B142" s="32"/>
+      <c r="C142" s="16">
+        <v>45692</v>
+      </c>
       <c r="D142" s="32"/>
       <c r="E142" s="12">
-        <v>24.45</v>
+        <v>13</v>
       </c>
       <c r="F142" s="12">
-        <v>23.9</v>
+        <v>12.95</v>
       </c>
       <c r="G142" s="12">
         <f t="shared" si="24"/>
-        <v>-2.25</v>
+        <v>-0.38</v>
       </c>
       <c r="H142" s="13" t="s">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="I142" s="13"/>
       <c r="J142" s="37"/>
       <c r="K142" s="13" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="143" spans="1:11" s="12" customFormat="1" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A143" s="12" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B143" s="32"/>
-      <c r="C143" s="16">
-        <v>45692</v>
-      </c>
       <c r="D143" s="32"/>
       <c r="E143" s="12">
-        <v>13</v>
+        <v>11.7</v>
       </c>
       <c r="F143" s="12">
-        <v>12.95</v>
-      </c>
-      <c r="G143" s="12">
-        <f t="shared" si="24"/>
-        <v>-0.38</v>
+        <v>11.6</v>
+      </c>
+      <c r="G143" s="13">
+        <f t="shared" ref="G143:G156" si="25">ROUND((F143 - E143) / E143 * 100, 2)</f>
+        <v>-0.85</v>
       </c>
       <c r="H143" s="13" t="s">
-        <v>79</v>
+        <v>49</v>
       </c>
       <c r="I143" s="13"/>
       <c r="J143" s="37"/>
       <c r="K143" s="13" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="144" spans="1:11" s="12" customFormat="1" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A144" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="B144" s="32"/>
-      <c r="D144" s="32"/>
-      <c r="E144" s="12">
-        <v>11.7</v>
-      </c>
-      <c r="F144" s="12">
-        <v>11.6</v>
-      </c>
-      <c r="G144" s="13">
-        <f t="shared" ref="G144:G157" si="25">ROUND((F144 - E144) / E144 * 100, 2)</f>
-        <v>-0.85</v>
-      </c>
-      <c r="H144" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="I144" s="13"/>
-      <c r="J144" s="37"/>
-      <c r="K144" s="13" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="145" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="12"/>
-      <c r="B145" s="31"/>
-      <c r="C145" s="10" t="s">
+    <row r="144" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A144" s="12"/>
+      <c r="B144" s="31"/>
+      <c r="C144" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="D145" s="31"/>
-      <c r="E145" s="10">
+      <c r="D144" s="31"/>
+      <c r="E144" s="10">
         <v>51.2</v>
       </c>
-      <c r="F145" s="10">
+      <c r="F144" s="10">
         <v>51.5</v>
       </c>
-      <c r="G145" s="10">
+      <c r="G144" s="10">
         <f t="shared" si="25"/>
         <v>0.59</v>
       </c>
-      <c r="H145" s="7" t="s">
+      <c r="H144" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="I145" s="7"/>
-      <c r="J145" s="38"/>
-      <c r="K145" s="7" t="s">
+      <c r="I144" s="7"/>
+      <c r="J144" s="38"/>
+      <c r="K144" s="7" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="146" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A146" s="12" t="s">
+    <row r="145" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A145" s="12" t="s">
         <v>9</v>
+      </c>
+      <c r="B145" s="32"/>
+      <c r="D145" s="32"/>
+      <c r="E145" s="12">
+        <v>12.6</v>
+      </c>
+      <c r="F145" s="12">
+        <v>12.5</v>
+      </c>
+      <c r="G145" s="12">
+        <f t="shared" si="25"/>
+        <v>-0.79</v>
+      </c>
+      <c r="H145" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="I145" s="13"/>
+      <c r="J145" s="37"/>
+      <c r="K145" s="13" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="146" spans="1:11" s="12" customFormat="1" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A146" s="10" t="s">
+        <v>65</v>
       </c>
       <c r="B146" s="32"/>
       <c r="D146" s="32"/>
       <c r="E146" s="12">
-        <v>12.6</v>
+        <v>69.3</v>
       </c>
       <c r="F146" s="12">
-        <v>12.5</v>
-      </c>
-      <c r="G146" s="12">
+        <v>66</v>
+      </c>
+      <c r="G146" s="13">
         <f t="shared" si="25"/>
-        <v>-0.79</v>
-      </c>
-      <c r="H146" s="13" t="s">
-        <v>68</v>
-      </c>
+        <v>-4.76</v>
+      </c>
+      <c r="H146" s="13"/>
       <c r="I146" s="13"/>
       <c r="J146" s="37"/>
       <c r="K146" s="13" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="147" spans="1:11" s="12" customFormat="1" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A147" s="10" t="s">
-        <v>65</v>
+      <c r="A147" s="12" t="s">
+        <v>66</v>
       </c>
       <c r="B147" s="32"/>
+      <c r="C147" s="12" t="s">
+        <v>70</v>
+      </c>
       <c r="D147" s="32"/>
       <c r="E147" s="12">
-        <v>69.3</v>
+        <v>16.05</v>
       </c>
       <c r="F147" s="12">
-        <v>66</v>
-      </c>
-      <c r="G147" s="13">
+        <v>15.25</v>
+      </c>
+      <c r="G147" s="12">
         <f t="shared" si="25"/>
-        <v>-4.76</v>
-      </c>
-      <c r="H147" s="13"/>
+        <v>-4.9800000000000004</v>
+      </c>
+      <c r="H147" s="13" t="s">
+        <v>71</v>
+      </c>
       <c r="I147" s="13"/>
       <c r="J147" s="37"/>
       <c r="K147" s="13" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="148" spans="1:11" s="12" customFormat="1" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A148" s="12" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="B148" s="32"/>
       <c r="C148" s="12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D148" s="32"/>
       <c r="E148" s="12">
-        <v>16.05</v>
+        <v>78.7</v>
       </c>
       <c r="F148" s="12">
-        <v>15.25</v>
+        <v>77.8</v>
       </c>
       <c r="G148" s="12">
         <f t="shared" si="25"/>
-        <v>-4.9800000000000004</v>
+        <v>-1.1399999999999999</v>
       </c>
       <c r="H148" s="13" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="I148" s="13"/>
       <c r="J148" s="37"/>
       <c r="K148" s="13" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="149" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="149" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A149" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="B149" s="32"/>
-      <c r="C149" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="D149" s="32"/>
-      <c r="E149" s="12">
-        <v>78.7</v>
-      </c>
-      <c r="F149" s="12">
-        <v>77.8</v>
-      </c>
-      <c r="G149" s="12">
-        <f t="shared" si="25"/>
-        <v>-1.1399999999999999</v>
-      </c>
-      <c r="H149" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="I149" s="13"/>
-      <c r="J149" s="37"/>
-      <c r="K149" s="13" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="150" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A150" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="B150" s="31"/>
-      <c r="C150" s="10" t="s">
+      <c r="B149" s="31"/>
+      <c r="C149" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="D150" s="31"/>
-      <c r="E150" s="10">
+      <c r="D149" s="31"/>
+      <c r="E149" s="10">
         <v>23.85</v>
       </c>
-      <c r="F150" s="10">
+      <c r="F149" s="10">
         <v>23.95</v>
       </c>
-      <c r="G150" s="10">
+      <c r="G149" s="10">
         <f t="shared" si="25"/>
         <v>0.42</v>
       </c>
-      <c r="H150" s="7" t="s">
+      <c r="H149" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="I150" s="7"/>
-      <c r="J150" s="38"/>
-      <c r="K150" s="7" t="s">
+      <c r="I149" s="7"/>
+      <c r="J149" s="38"/>
+      <c r="K149" s="7" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="151" spans="1:11" s="12" customFormat="1" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A151" s="12" t="s">
+    <row r="150" spans="1:11" s="12" customFormat="1" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A150" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="B151" s="32"/>
-      <c r="D151" s="32"/>
-      <c r="E151" s="12">
+      <c r="B150" s="32"/>
+      <c r="D150" s="32"/>
+      <c r="E150" s="12">
         <v>20.76</v>
       </c>
-      <c r="F151" s="12">
+      <c r="F150" s="12">
         <v>19.899999999999999</v>
       </c>
-      <c r="G151" s="12">
+      <c r="G150" s="12">
         <f t="shared" si="25"/>
         <v>-4.1399999999999997</v>
       </c>
-      <c r="H151" s="13" t="s">
+      <c r="H150" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="I151" s="13"/>
-      <c r="J151" s="37"/>
-      <c r="K151" s="13" t="s">
+      <c r="I150" s="13"/>
+      <c r="J150" s="37"/>
+      <c r="K150" s="13" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="152" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="10" t="s">
+    <row r="151" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A151" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B152" s="31"/>
-      <c r="D152" s="31"/>
-      <c r="E152" s="10">
+      <c r="B151" s="31"/>
+      <c r="D151" s="31"/>
+      <c r="E151" s="10">
         <v>17.75</v>
       </c>
-      <c r="F152" s="10">
+      <c r="F151" s="10">
         <v>20</v>
       </c>
-      <c r="G152" s="10">
+      <c r="G151" s="10">
         <f t="shared" si="25"/>
         <v>12.68</v>
       </c>
-      <c r="H152" s="7" t="s">
+      <c r="H151" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="I152" s="7"/>
-      <c r="J152" s="38"/>
-      <c r="K152" s="7" t="s">
+      <c r="I151" s="7"/>
+      <c r="J151" s="38"/>
+      <c r="K151" s="7" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="153" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="12" t="s">
+    <row r="152" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A152" s="12" t="s">
         <v>10</v>
       </c>
+      <c r="B152" s="32"/>
+      <c r="D152" s="32"/>
+      <c r="E152" s="12">
+        <v>99</v>
+      </c>
+      <c r="F152" s="12">
+        <v>96.2</v>
+      </c>
+      <c r="G152" s="13">
+        <f t="shared" si="25"/>
+        <v>-2.83</v>
+      </c>
+      <c r="H152" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="I152" s="13"/>
+      <c r="J152" s="37"/>
+      <c r="K152" s="13" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="153" spans="1:11" s="12" customFormat="1" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A153" s="10" t="s">
+        <v>16</v>
+      </c>
       <c r="B153" s="32"/>
+      <c r="C153" s="12" t="s">
+        <v>62</v>
+      </c>
       <c r="D153" s="32"/>
       <c r="E153" s="12">
-        <v>99</v>
+        <v>29.5</v>
       </c>
       <c r="F153" s="12">
-        <v>96.2</v>
+        <v>29.4</v>
       </c>
       <c r="G153" s="13">
         <f t="shared" si="25"/>
-        <v>-2.83</v>
+        <v>-0.34</v>
       </c>
       <c r="H153" s="13" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="I153" s="13"/>
       <c r="J153" s="37"/>
       <c r="K153" s="13" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="154" spans="1:11" s="12" customFormat="1" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A154" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="B154" s="32"/>
-      <c r="C154" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="D154" s="32"/>
-      <c r="E154" s="12">
-        <v>29.5</v>
-      </c>
-      <c r="F154" s="12">
-        <v>29.4</v>
-      </c>
-      <c r="G154" s="13">
-        <f t="shared" si="25"/>
-        <v>-0.34</v>
-      </c>
-      <c r="H154" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="I154" s="13"/>
-      <c r="J154" s="37"/>
-      <c r="K154" s="13" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="155" spans="1:11" s="10" customFormat="1" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="A155" s="12" t="s">
+    <row r="154" spans="1:11" s="10" customFormat="1" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A154" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="B155" s="31"/>
-      <c r="D155" s="31"/>
-      <c r="E155" s="10">
+      <c r="B154" s="31"/>
+      <c r="D154" s="31"/>
+      <c r="E154" s="10">
         <v>10.5</v>
       </c>
-      <c r="F155" s="10">
+      <c r="F154" s="10">
         <v>12.45</v>
       </c>
-      <c r="G155" s="10">
+      <c r="G154" s="10">
         <f t="shared" si="25"/>
         <v>18.57</v>
       </c>
-      <c r="H155" s="7" t="s">
+      <c r="H154" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="I155" s="7"/>
-      <c r="J155" s="38"/>
-      <c r="K155" s="7" t="s">
+      <c r="I154" s="7"/>
+      <c r="J154" s="38"/>
+      <c r="K154" s="7" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="156" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A156" s="12" t="s">
+    <row r="155" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A155" s="12" t="s">
         <v>54</v>
+      </c>
+      <c r="B155" s="32"/>
+      <c r="D155" s="32"/>
+      <c r="E155" s="12">
+        <v>18.7</v>
+      </c>
+      <c r="F155" s="12">
+        <v>18.3</v>
+      </c>
+      <c r="G155" s="13">
+        <f t="shared" si="25"/>
+        <v>-2.14</v>
+      </c>
+      <c r="H155" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="I155" s="13"/>
+      <c r="J155" s="37"/>
+      <c r="K155" s="13" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="156" spans="1:11" s="12" customFormat="1" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A156" s="10" t="s">
+        <v>25</v>
       </c>
       <c r="B156" s="32"/>
       <c r="D156" s="32"/>
       <c r="E156" s="12">
-        <v>18.7</v>
+        <v>51.9</v>
       </c>
       <c r="F156" s="12">
-        <v>18.3</v>
+        <v>51.6</v>
       </c>
       <c r="G156" s="13">
         <f t="shared" si="25"/>
-        <v>-2.14</v>
+        <v>-0.57999999999999996</v>
       </c>
       <c r="H156" s="13" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I156" s="13"/>
       <c r="J156" s="37"/>
       <c r="K156" s="13" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="157" spans="1:11" s="12" customFormat="1" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A157" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="B157" s="32"/>
-      <c r="D157" s="32"/>
-      <c r="E157" s="12">
-        <v>51.9</v>
-      </c>
-      <c r="F157" s="12">
-        <v>51.6</v>
-      </c>
-      <c r="G157" s="13">
-        <f t="shared" si="25"/>
-        <v>-0.57999999999999996</v>
-      </c>
-      <c r="H157" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="I157" s="13"/>
-      <c r="J157" s="37"/>
-      <c r="K157" s="13" t="s">
         <v>47</v>
+      </c>
+    </row>
+    <row r="157" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A157" s="12" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="158" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A158" s="12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A159" s="12" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="166" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B166" s="33"/>
-      <c r="C166" s="11"/>
-      <c r="D166" s="33"/>
-      <c r="E166" s="11"/>
-      <c r="F166" s="11"/>
-      <c r="G166" s="11"/>
-      <c r="H166" s="14"/>
-      <c r="I166" s="14"/>
-      <c r="J166" s="39"/>
-      <c r="K166" s="14"/>
-      <c r="L166" s="11"/>
-      <c r="M166" s="11"/>
-      <c r="N166" s="11"/>
-      <c r="O166" s="11"/>
-    </row>
-    <row r="168" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A168" s="11"/>
+    <row r="165" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B165" s="33"/>
+      <c r="C165" s="11"/>
+      <c r="D165" s="33"/>
+      <c r="E165" s="11"/>
+      <c r="F165" s="11"/>
+      <c r="G165" s="11"/>
+      <c r="H165" s="14"/>
+      <c r="I165" s="14"/>
+      <c r="J165" s="39"/>
+      <c r="K165" s="14"/>
+      <c r="L165" s="11"/>
+      <c r="M165" s="11"/>
+      <c r="N165" s="11"/>
+      <c r="O165" s="11"/>
+    </row>
+    <row r="167" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A167" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -24217,12 +24358,12 @@
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B62" s="20" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B63" s="20" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
@@ -24232,7 +24373,7 @@
     </row>
     <row r="65" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B65" s="20" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="66" spans="2:2" x14ac:dyDescent="0.25">
